--- a/data/publications/monthly-rbi-bulletin/financial-markets/table-29-commercial-paper.xlsx
+++ b/data/publications/monthly-rbi-bulletin/financial-markets/table-29-commercial-paper.xlsx
@@ -266,11 +266,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:F377"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="5" width="20.8466173333333" customWidth="1"/>
     <col min="6" max="6" width="20.85042" customWidth="1"/>
+    <col min="7" max="7" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -328,662 +329,662 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B8" s="6">
-        <v>46112</v>
+        <v>46265</v>
       </c>
       <c r="C8" s="7">
-        <v>460151.55</v>
+        <v>639856.7</v>
       </c>
       <c r="D8" s="7">
-        <v>77688.35</v>
+        <v>91579.05</v>
       </c>
       <c r="E8" s="8">
-        <v>5.9155</v>
+        <v>6.2896</v>
       </c>
       <c r="F8" s="8">
-        <v>14.4011</v>
+        <v>14.0955</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B9" s="6">
-        <v>46096</v>
+        <v>46249</v>
       </c>
       <c r="C9" s="9">
-        <v>476150.85</v>
+        <v>618019.65</v>
       </c>
       <c r="D9" s="9">
-        <v>100794.6</v>
+        <v>88890.5</v>
       </c>
       <c r="E9" s="10">
-        <v>6.2702</v>
+        <v>4.9901</v>
       </c>
       <c r="F9" s="10">
-        <v>12.0003</v>
+        <v>12.6681</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B10" s="6">
-        <v>46081</v>
+        <v>46234</v>
       </c>
       <c r="C10" s="7">
-        <v>478434.45</v>
+        <v>586897.4</v>
       </c>
       <c r="D10" s="7">
-        <v>79734.2</v>
+        <v>59083.65</v>
       </c>
       <c r="E10" s="8">
-        <v>5.9624</v>
+        <v>6.2287</v>
       </c>
       <c r="F10" s="8">
-        <v>11.1794</v>
+        <v>13.9102</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B11" s="6">
-        <v>46068</v>
+        <v>46218</v>
       </c>
       <c r="C11" s="9">
-        <v>481234.6</v>
+        <v>565904.95</v>
       </c>
       <c r="D11" s="9">
-        <v>110283.75</v>
+        <v>62526.35</v>
       </c>
       <c r="E11" s="10">
-        <v>6.0631</v>
+        <v>6.0184</v>
       </c>
       <c r="F11" s="10">
-        <v>13.5649</v>
+        <v>10.607</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B12" s="6">
-        <v>46053</v>
+        <v>46203</v>
       </c>
       <c r="C12" s="7">
-        <v>438787.05</v>
+        <v>541805.35</v>
       </c>
       <c r="D12" s="7">
-        <v>41076.2</v>
+        <v>96188.65</v>
       </c>
       <c r="E12" s="8">
-        <v>6.1822</v>
+        <v>6.267</v>
       </c>
       <c r="F12" s="8">
-        <v>14.465</v>
+        <v>14.1829</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B13" s="6">
-        <v>46037</v>
+        <v>46188</v>
       </c>
       <c r="C13" s="9">
-        <v>453838.55</v>
+        <v>557704.55</v>
       </c>
       <c r="D13" s="9">
-        <v>26659.2</v>
+        <v>158714.4</v>
       </c>
       <c r="E13" s="10">
-        <v>5.9221</v>
+        <v>6.1344</v>
       </c>
       <c r="F13" s="10">
-        <v>13.4239</v>
+        <v>14.1572</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B14" s="6">
-        <v>46022</v>
+        <v>46173</v>
       </c>
       <c r="C14" s="7">
-        <v>451053.35</v>
+        <v>536186.35</v>
       </c>
       <c r="D14" s="7">
-        <v>59006.25</v>
+        <v>74982.4</v>
       </c>
       <c r="E14" s="8">
-        <v>5.9922</v>
+        <v>5.8824</v>
       </c>
       <c r="F14" s="8">
-        <v>13.5279</v>
+        <v>13.3022</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B15" s="6">
-        <v>46006</v>
+        <v>46157</v>
       </c>
       <c r="C15" s="9">
-        <v>473476.3</v>
+        <v>539318.4</v>
       </c>
       <c r="D15" s="9">
-        <v>79654</v>
+        <v>62963.15</v>
       </c>
       <c r="E15" s="10">
-        <v>5.8143</v>
+        <v>6.2289</v>
       </c>
       <c r="F15" s="10">
-        <v>12.1224</v>
+        <v>12.0791</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B16" s="6">
-        <v>45991</v>
+        <v>46142</v>
       </c>
       <c r="C16" s="7">
-        <v>501649.2</v>
+        <v>560941.15</v>
       </c>
       <c r="D16" s="7">
-        <v>69177.7</v>
+        <v>65227.35</v>
       </c>
       <c r="E16" s="8">
-        <v>5.79</v>
+        <v>5.5363</v>
       </c>
       <c r="F16" s="8">
-        <v>11.49</v>
+        <v>13.3022</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B17" s="6">
-        <v>45976</v>
+        <v>46127</v>
       </c>
       <c r="C17" s="9">
-        <v>501658</v>
+        <v>526603.7</v>
       </c>
       <c r="D17" s="9">
-        <v>66525.85</v>
+        <v>79682.25</v>
       </c>
       <c r="E17" s="10">
-        <v>5.86</v>
+        <v>5.565</v>
       </c>
       <c r="F17" s="10">
-        <v>9.7117</v>
+        <v>9.7169</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B18" s="6">
-        <v>45961</v>
+        <v>46112</v>
       </c>
       <c r="C18" s="7">
-        <v>479629.5</v>
+        <v>460151.55</v>
       </c>
       <c r="D18" s="7">
-        <v>52397.55</v>
+        <v>77688.35</v>
       </c>
       <c r="E18" s="8">
-        <v>5.79</v>
+        <v>5.9155</v>
       </c>
       <c r="F18" s="8">
-        <v>14.93</v>
+        <v>14.4011</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B19" s="6">
-        <v>45945</v>
+        <v>46096</v>
       </c>
       <c r="C19" s="9">
-        <v>495678.6</v>
+        <v>476150.85</v>
       </c>
       <c r="D19" s="9">
-        <v>30794.65</v>
+        <v>100794.6</v>
       </c>
       <c r="E19" s="10">
-        <v>5.71</v>
+        <v>6.2702</v>
       </c>
       <c r="F19" s="10">
-        <v>12.49</v>
+        <v>12.0003</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B20" s="6">
-        <v>45930</v>
+        <v>46081</v>
       </c>
       <c r="C20" s="7">
-        <v>488262.8</v>
+        <v>478434.45</v>
       </c>
       <c r="D20" s="7">
-        <v>70288</v>
+        <v>79734.2</v>
       </c>
       <c r="E20" s="8">
-        <v>5.7269</v>
+        <v>5.9624</v>
       </c>
       <c r="F20" s="8">
-        <v>12.3382</v>
+        <v>11.1794</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B21" s="6">
-        <v>45915</v>
+        <v>46068</v>
       </c>
       <c r="C21" s="9">
-        <v>526704.3</v>
+        <v>481234.6</v>
       </c>
       <c r="D21" s="9">
-        <v>99422.2</v>
+        <v>110283.75</v>
       </c>
       <c r="E21" s="10">
-        <v>5.7173</v>
+        <v>6.0631</v>
       </c>
       <c r="F21" s="10">
-        <v>11.9658</v>
+        <v>13.5649</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B22" s="6">
-        <v>45900</v>
+        <v>46053</v>
       </c>
       <c r="C22" s="7">
-        <v>543870.1</v>
+        <v>438787.05</v>
       </c>
       <c r="D22" s="7">
-        <v>60807.6</v>
+        <v>41076.2</v>
       </c>
       <c r="E22" s="8">
-        <v>5.7173</v>
+        <v>6.1822</v>
       </c>
       <c r="F22" s="8">
-        <v>13.8301</v>
+        <v>14.465</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B23" s="6">
-        <v>45884</v>
+        <v>46037</v>
       </c>
       <c r="C23" s="9">
-        <v>554479.7</v>
+        <v>453838.55</v>
       </c>
       <c r="D23" s="9">
-        <v>56758.35</v>
+        <v>26659.2</v>
       </c>
       <c r="E23" s="10">
-        <v>5.683</v>
+        <v>5.9221</v>
       </c>
       <c r="F23" s="10">
-        <v>12.6681</v>
+        <v>13.4239</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B24" s="6">
-        <v>45869</v>
+        <v>46022</v>
       </c>
       <c r="C24" s="7">
-        <v>547229.3</v>
+        <v>451053.35</v>
       </c>
       <c r="D24" s="7">
-        <v>73858.5</v>
+        <v>59006.25</v>
       </c>
       <c r="E24" s="8">
-        <v>5.57</v>
+        <v>5.9922</v>
       </c>
       <c r="F24" s="8">
-        <v>13.84</v>
+        <v>13.5279</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B25" s="6">
-        <v>45853</v>
+        <v>46006</v>
       </c>
       <c r="C25" s="9">
-        <v>534009.15</v>
+        <v>473476.3</v>
       </c>
       <c r="D25" s="9">
-        <v>79530.05</v>
+        <v>79654</v>
       </c>
       <c r="E25" s="10">
-        <v>5.51</v>
+        <v>5.8143</v>
       </c>
       <c r="F25" s="10">
-        <v>12.67</v>
+        <v>12.1224</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B26" s="6">
-        <v>45838</v>
+        <v>45991</v>
       </c>
       <c r="C26" s="7">
-        <v>500000.6</v>
+        <v>501649.2</v>
       </c>
       <c r="D26" s="7">
-        <v>58021.75</v>
+        <v>69177.7</v>
       </c>
       <c r="E26" s="8">
-        <v>5.7085</v>
+        <v>5.79</v>
       </c>
       <c r="F26" s="8">
-        <v>13.8408</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B27" s="6">
-        <v>45823</v>
+        <v>45976</v>
       </c>
       <c r="C27" s="9">
-        <v>549258.3</v>
+        <v>501658</v>
       </c>
       <c r="D27" s="9">
-        <v>102447</v>
+        <v>66525.85</v>
       </c>
       <c r="E27" s="10">
-        <v>5.6687</v>
+        <v>5.86</v>
       </c>
       <c r="F27" s="10">
-        <v>11.6256</v>
+        <v>9.7117</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B28" s="6">
-        <v>45808</v>
+        <v>45961</v>
       </c>
       <c r="C28" s="7">
-        <v>553874.25</v>
+        <v>479629.5</v>
       </c>
       <c r="D28" s="7">
-        <v>81053.8</v>
+        <v>52397.55</v>
       </c>
       <c r="E28" s="8">
-        <v>5.97</v>
+        <v>5.79</v>
       </c>
       <c r="F28" s="8">
-        <v>12.23</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B29" s="6">
-        <v>45792</v>
+        <v>45945</v>
       </c>
       <c r="C29" s="9">
-        <v>541591.1</v>
+        <v>495678.6</v>
       </c>
       <c r="D29" s="9">
-        <v>48973.55</v>
+        <v>30794.65</v>
       </c>
       <c r="E29" s="10">
-        <v>6.44</v>
+        <v>5.71</v>
       </c>
       <c r="F29" s="10">
-        <v>10.14</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B30" s="6">
-        <v>45777</v>
+        <v>45930</v>
       </c>
       <c r="C30" s="7">
-        <v>545586.95</v>
+        <v>488262.8</v>
       </c>
       <c r="D30" s="7">
-        <v>72418.9</v>
+        <v>70288</v>
       </c>
       <c r="E30" s="8">
-        <v>6.2581</v>
+        <v>5.7269</v>
       </c>
       <c r="F30" s="8">
-        <v>13.0015</v>
+        <v>12.3382</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B31" s="6">
-        <v>45762</v>
+        <v>45915</v>
       </c>
       <c r="C31" s="9">
-        <v>521558.1</v>
+        <v>526704.3</v>
       </c>
       <c r="D31" s="9">
-        <v>91006.4</v>
+        <v>99422.2</v>
       </c>
       <c r="E31" s="10">
-        <v>6.3071</v>
+        <v>5.7173</v>
       </c>
       <c r="F31" s="10">
-        <v>11.6515</v>
+        <v>11.9658</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B32" s="6">
-        <v>45747</v>
+        <v>45900</v>
       </c>
       <c r="C32" s="7">
-        <v>442892.7</v>
+        <v>543870.1</v>
       </c>
       <c r="D32" s="7">
-        <v>77133.85</v>
+        <v>60807.6</v>
       </c>
       <c r="E32" s="8">
-        <v>7</v>
+        <v>5.7173</v>
       </c>
       <c r="F32" s="8">
-        <v>14.46</v>
+        <v>13.8301</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B33" s="6">
-        <v>45731</v>
+        <v>45884</v>
       </c>
       <c r="C33" s="9">
-        <v>457051.3</v>
+        <v>554479.7</v>
       </c>
       <c r="D33" s="9">
-        <v>107624.2</v>
+        <v>56758.35</v>
       </c>
       <c r="E33" s="10">
-        <v>6.67</v>
+        <v>5.683</v>
       </c>
       <c r="F33" s="10">
-        <v>11.78</v>
+        <v>12.6681</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B34" s="6">
-        <v>45716</v>
+        <v>45869</v>
       </c>
       <c r="C34" s="7">
-        <v>465926.95</v>
+        <v>547229.3</v>
       </c>
       <c r="D34" s="7">
-        <v>64880.85</v>
+        <v>73858.5</v>
       </c>
       <c r="E34" s="8">
-        <v>6.7752</v>
+        <v>5.57</v>
       </c>
       <c r="F34" s="8">
-        <v>12.2399</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B35" s="6">
-        <v>45703</v>
+        <v>45853</v>
       </c>
       <c r="C35" s="9">
-        <v>479257.25</v>
+        <v>534009.15</v>
       </c>
       <c r="D35" s="9">
-        <v>80693.35</v>
+        <v>79530.05</v>
       </c>
       <c r="E35" s="10">
-        <v>6.9732</v>
+        <v>5.51</v>
       </c>
       <c r="F35" s="10">
-        <v>12.404</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B36" s="6">
-        <v>45688</v>
+        <v>45838</v>
       </c>
       <c r="C36" s="7">
-        <v>456483.15</v>
+        <v>500000.6</v>
       </c>
       <c r="D36" s="7">
-        <v>69001.15</v>
+        <v>58021.75</v>
       </c>
       <c r="E36" s="8">
-        <v>7.12</v>
+        <v>5.7085</v>
       </c>
       <c r="F36" s="8">
-        <v>13.77</v>
+        <v>13.8408</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B37" s="6">
-        <v>45672</v>
+        <v>45823</v>
       </c>
       <c r="C37" s="9">
-        <v>450242.05</v>
+        <v>549258.3</v>
       </c>
       <c r="D37" s="9">
-        <v>39647.3</v>
+        <v>102447</v>
       </c>
       <c r="E37" s="10">
-        <v>7.06</v>
+        <v>5.6687</v>
       </c>
       <c r="F37" s="10">
-        <v>12.12</v>
+        <v>11.6256</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B38" s="6">
-        <v>45657</v>
+        <v>45808</v>
       </c>
       <c r="C38" s="7">
-        <v>435779.45</v>
+        <v>553874.25</v>
       </c>
       <c r="D38" s="7">
-        <v>51524.05</v>
+        <v>81053.8</v>
       </c>
       <c r="E38" s="8">
-        <v>6.98</v>
+        <v>5.97</v>
       </c>
       <c r="F38" s="8">
-        <v>12</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B39" s="6">
-        <v>45641</v>
+        <v>45792</v>
       </c>
       <c r="C39" s="9">
-        <v>463801.3</v>
+        <v>541591.1</v>
       </c>
       <c r="D39" s="9">
-        <v>98956.25</v>
+        <v>48973.55</v>
       </c>
       <c r="E39" s="10">
-        <v>7</v>
+        <v>6.44</v>
       </c>
       <c r="F39" s="10">
-        <v>11.89</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B40" s="6">
-        <v>45626</v>
+        <v>45777</v>
       </c>
       <c r="C40" s="7">
-        <v>445122.05</v>
+        <v>545586.95</v>
       </c>
       <c r="D40" s="7">
-        <v>64504.65</v>
+        <v>72418.9</v>
       </c>
       <c r="E40" s="8">
-        <v>7</v>
+        <v>6.2581</v>
       </c>
       <c r="F40" s="8">
-        <v>12.61</v>
+        <v>13.0015</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B41" s="6">
-        <v>45611</v>
+        <v>45762</v>
       </c>
       <c r="C41" s="9">
-        <v>448862.8</v>
+        <v>521558.1</v>
       </c>
       <c r="D41" s="9">
-        <v>50771.85</v>
+        <v>91006.4</v>
       </c>
       <c r="E41" s="10">
-        <v>6.99</v>
+        <v>6.3071</v>
       </c>
       <c r="F41" s="10">
-        <v>13.77</v>
+        <v>11.6515</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B42" s="6">
-        <v>45596</v>
+        <v>45747</v>
       </c>
       <c r="C42" s="7">
-        <v>445104.9</v>
+        <v>442892.7</v>
       </c>
       <c r="D42" s="7">
-        <v>66159.85</v>
+        <v>77133.85</v>
       </c>
       <c r="E42" s="8">
-        <v>6.988</v>
+        <v>7</v>
       </c>
       <c r="F42" s="8">
-        <v>12.5313</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B43" s="6">
-        <v>45580</v>
+        <v>45731</v>
       </c>
       <c r="C43" s="9">
-        <v>438134.2</v>
+        <v>457051.3</v>
       </c>
       <c r="D43" s="9">
-        <v>48517.65</v>
+        <v>107624.2</v>
       </c>
       <c r="E43" s="10">
-        <v>6.95</v>
+        <v>6.67</v>
       </c>
       <c r="F43" s="10">
-        <v>12.6</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B44" s="6">
-        <v>45565</v>
+        <v>45716</v>
       </c>
       <c r="C44" s="7">
-        <v>397590.45</v>
+        <v>465926.95</v>
       </c>
       <c r="D44" s="7">
-        <v>48447.9</v>
+        <v>64880.85</v>
       </c>
       <c r="E44" s="8">
-        <v>7.07</v>
+        <v>6.7752</v>
       </c>
       <c r="F44" s="8">
-        <v>14.72</v>
+        <v>12.2399</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B45" s="6">
-        <v>45550</v>
+        <v>45703</v>
       </c>
       <c r="C45" s="9">
-        <v>440945.45</v>
+        <v>479257.25</v>
       </c>
       <c r="D45" s="9">
-        <v>78418.6</v>
+        <v>80693.35</v>
       </c>
       <c r="E45" s="10">
-        <v>7.09</v>
+        <v>6.9732</v>
       </c>
       <c r="F45" s="10">
-        <v>12.88</v>
+        <v>12.404</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B46" s="6">
-        <v>45535</v>
+        <v>45688</v>
       </c>
       <c r="C46" s="7">
-        <v>471121.5</v>
+        <v>456483.15</v>
       </c>
       <c r="D46" s="7">
-        <v>78270.05</v>
+        <v>69001.15</v>
       </c>
       <c r="E46" s="8">
-        <v>6.9</v>
+        <v>7.12</v>
       </c>
       <c r="F46" s="8">
         <v>13.77</v>
@@ -991,1087 +992,1087 @@
     </row>
     <row r="47" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B47" s="6">
-        <v>45519</v>
+        <v>45672</v>
       </c>
       <c r="C47" s="9">
-        <v>473153.85</v>
+        <v>450242.05</v>
       </c>
       <c r="D47" s="9">
-        <v>63925.5</v>
+        <v>39647.3</v>
       </c>
       <c r="E47" s="10">
-        <v>6.97</v>
+        <v>7.06</v>
       </c>
       <c r="F47" s="10">
-        <v>11.69</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B48" s="6">
-        <v>45504</v>
+        <v>45657</v>
       </c>
       <c r="C48" s="7">
-        <v>458911.05</v>
+        <v>435779.45</v>
       </c>
       <c r="D48" s="7">
-        <v>67966.95</v>
+        <v>51524.05</v>
       </c>
       <c r="E48" s="8">
-        <v>6.89</v>
+        <v>6.98</v>
       </c>
       <c r="F48" s="8">
-        <v>12.07</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B49" s="6">
-        <v>45488</v>
+        <v>45641</v>
       </c>
       <c r="C49" s="9">
-        <v>440818.85</v>
+        <v>463801.3</v>
       </c>
       <c r="D49" s="9">
-        <v>37452.1</v>
+        <v>98956.25</v>
       </c>
       <c r="E49" s="10">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="F49" s="10">
-        <v>11.69</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B50" s="6">
-        <v>45473</v>
+        <v>45626</v>
       </c>
       <c r="C50" s="7">
-        <v>422447.45</v>
+        <v>445122.05</v>
       </c>
       <c r="D50" s="7">
-        <v>56023.85</v>
+        <v>64504.65</v>
       </c>
       <c r="E50" s="8">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="F50" s="8">
-        <v>15.06</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B51" s="6">
-        <v>45458</v>
+        <v>45611</v>
       </c>
       <c r="C51" s="9">
-        <v>431100.55</v>
+        <v>448862.8</v>
       </c>
       <c r="D51" s="9">
-        <v>106920.7</v>
+        <v>50771.85</v>
       </c>
       <c r="E51" s="10">
-        <v>6.95</v>
+        <v>6.99</v>
       </c>
       <c r="F51" s="10">
-        <v>12.08</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B52" s="6">
-        <v>45443</v>
+        <v>45596</v>
       </c>
       <c r="C52" s="7">
-        <v>403970</v>
+        <v>445104.9</v>
       </c>
       <c r="D52" s="7">
-        <v>80921.75</v>
+        <v>66159.85</v>
       </c>
       <c r="E52" s="8">
-        <v>7.05</v>
+        <v>6.988</v>
       </c>
       <c r="F52" s="8">
-        <v>13.92</v>
+        <v>12.5313</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B53" s="6">
-        <v>45427</v>
+        <v>45580</v>
       </c>
       <c r="C53" s="9">
-        <v>421150.9</v>
+        <v>438134.2</v>
       </c>
       <c r="D53" s="9">
-        <v>52596.55</v>
+        <v>48517.65</v>
       </c>
       <c r="E53" s="10">
-        <v>7.06</v>
+        <v>6.95</v>
       </c>
       <c r="F53" s="10">
-        <v>11.96</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B54" s="6">
-        <v>45412</v>
+        <v>45565</v>
       </c>
       <c r="C54" s="7">
-        <v>411533.6</v>
+        <v>397590.45</v>
       </c>
       <c r="D54" s="7">
-        <v>60407.45</v>
+        <v>48447.9</v>
       </c>
       <c r="E54" s="8">
-        <v>6.89</v>
+        <v>7.07</v>
       </c>
       <c r="F54" s="8">
-        <v>12.59</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B55" s="6">
-        <v>45397</v>
+        <v>45550</v>
       </c>
       <c r="C55" s="9">
-        <v>397251</v>
+        <v>440945.45</v>
       </c>
       <c r="D55" s="9">
-        <v>23663</v>
+        <v>78418.6</v>
       </c>
       <c r="E55" s="10">
-        <v>6.9</v>
+        <v>7.09</v>
       </c>
       <c r="F55" s="10">
-        <v>13.85</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B56" s="6">
-        <v>45382</v>
+        <v>45535</v>
       </c>
       <c r="C56" s="7">
-        <v>388559.2</v>
+        <v>471121.5</v>
       </c>
       <c r="D56" s="7">
-        <v>57334.1</v>
+        <v>78270.05</v>
       </c>
       <c r="E56" s="8">
-        <v>7.07</v>
+        <v>6.9</v>
       </c>
       <c r="F56" s="8">
-        <v>14.2</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B57" s="6">
-        <v>45366</v>
+        <v>45519</v>
       </c>
       <c r="C57" s="9">
-        <v>406182.5</v>
+        <v>473153.85</v>
       </c>
       <c r="D57" s="9">
-        <v>93685.95</v>
+        <v>63925.5</v>
       </c>
       <c r="E57" s="10">
-        <v>7.09</v>
+        <v>6.97</v>
       </c>
       <c r="F57" s="10">
-        <v>13.92</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B58" s="6">
-        <v>45351</v>
+        <v>45504</v>
       </c>
       <c r="C58" s="7">
-        <v>408048.25</v>
+        <v>458911.05</v>
       </c>
       <c r="D58" s="7">
-        <v>82067.8</v>
+        <v>67966.95</v>
       </c>
       <c r="E58" s="8">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
       <c r="F58" s="8">
-        <v>11.91</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B59" s="6">
-        <v>45337</v>
+        <v>45488</v>
       </c>
       <c r="C59" s="9">
-        <v>395262.1</v>
+        <v>440818.85</v>
       </c>
       <c r="D59" s="9">
-        <v>57899.85</v>
+        <v>37452.1</v>
       </c>
       <c r="E59" s="10">
-        <v>7.38</v>
+        <v>6.93</v>
       </c>
       <c r="F59" s="10">
-        <v>12.74</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B60" s="6">
-        <v>45322</v>
+        <v>45473</v>
       </c>
       <c r="C60" s="7">
-        <v>377707.2</v>
+        <v>422447.45</v>
       </c>
       <c r="D60" s="7">
-        <v>53532.05</v>
+        <v>56023.85</v>
       </c>
       <c r="E60" s="8">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="F60" s="8">
-        <v>14.74</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B61" s="6">
-        <v>45306</v>
+        <v>45458</v>
       </c>
       <c r="C61" s="9">
-        <v>378628.1</v>
+        <v>431100.55</v>
       </c>
       <c r="D61" s="9">
-        <v>34492.95</v>
+        <v>106920.7</v>
       </c>
       <c r="E61" s="10">
-        <v>7.12</v>
+        <v>6.95</v>
       </c>
       <c r="F61" s="10">
-        <v>12.34</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B62" s="6">
-        <v>45291</v>
+        <v>45443</v>
       </c>
       <c r="C62" s="7">
-        <v>364181.25</v>
+        <v>403970</v>
       </c>
       <c r="D62" s="7">
-        <v>42874.35</v>
+        <v>80921.75</v>
       </c>
       <c r="E62" s="8">
-        <v>7.02</v>
+        <v>7.05</v>
       </c>
       <c r="F62" s="8">
-        <v>12.13</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B63" s="6">
-        <v>45275</v>
+        <v>45427</v>
       </c>
       <c r="C63" s="9">
-        <v>387266.65</v>
+        <v>421150.9</v>
       </c>
       <c r="D63" s="9">
-        <v>68393.55</v>
+        <v>52596.55</v>
       </c>
       <c r="E63" s="10">
-        <v>7.17</v>
+        <v>7.06</v>
       </c>
       <c r="F63" s="10">
-        <v>11.77</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B64" s="6">
-        <v>45260</v>
+        <v>45412</v>
       </c>
       <c r="C64" s="7">
-        <v>394967.95</v>
+        <v>411533.6</v>
       </c>
       <c r="D64" s="7">
-        <v>59808.25</v>
+        <v>60407.45</v>
       </c>
       <c r="E64" s="8">
-        <v>6.99</v>
+        <v>6.89</v>
       </c>
       <c r="F64" s="8">
-        <v>14.34</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B65" s="6">
-        <v>45245</v>
+        <v>45397</v>
       </c>
       <c r="C65" s="9">
-        <v>417630.65</v>
+        <v>397251</v>
       </c>
       <c r="D65" s="9">
-        <v>41107.05</v>
+        <v>23663</v>
       </c>
       <c r="E65" s="10">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="F65" s="10">
-        <v>12</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B66" s="6">
-        <v>45230</v>
+        <v>45382</v>
       </c>
       <c r="C66" s="7">
-        <v>413685.3</v>
+        <v>388559.2</v>
       </c>
       <c r="D66" s="7">
-        <v>50039.65</v>
+        <v>57334.1</v>
       </c>
       <c r="E66" s="8">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="F66" s="8">
-        <v>11.89</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B67" s="6">
-        <v>45214</v>
+        <v>45366</v>
       </c>
       <c r="C67" s="9">
-        <v>418804.1</v>
+        <v>406182.5</v>
       </c>
       <c r="D67" s="9">
-        <v>25039.05</v>
+        <v>93685.95</v>
       </c>
       <c r="E67" s="10">
-        <v>6.91</v>
+        <v>7.09</v>
       </c>
       <c r="F67" s="10">
-        <v>16.41</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B68" s="6">
-        <v>45199</v>
+        <v>45351</v>
       </c>
       <c r="C68" s="7">
-        <v>412234.35</v>
+        <v>408048.25</v>
       </c>
       <c r="D68" s="7">
-        <v>49675.85</v>
+        <v>82067.8</v>
       </c>
       <c r="E68" s="8">
-        <v>6.89</v>
+        <v>7.05</v>
       </c>
       <c r="F68" s="8">
-        <v>11.36</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B69" s="6">
-        <v>45184</v>
+        <v>45337</v>
       </c>
       <c r="C69" s="9">
-        <v>432568.65</v>
+        <v>395262.1</v>
       </c>
       <c r="D69" s="9">
-        <v>71469.15</v>
+        <v>57899.85</v>
       </c>
       <c r="E69" s="10">
-        <v>6.8429</v>
+        <v>7.38</v>
       </c>
       <c r="F69" s="10">
-        <v>12.5012</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B70" s="6">
-        <v>45169</v>
+        <v>45322</v>
       </c>
       <c r="C70" s="7">
-        <v>450064.05</v>
+        <v>377707.2</v>
       </c>
       <c r="D70" s="7">
-        <v>73816.05</v>
+        <v>53532.05</v>
       </c>
       <c r="E70" s="8">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="F70" s="8">
-        <v>16.55</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B71" s="6">
-        <v>45153</v>
+        <v>45306</v>
       </c>
       <c r="C71" s="9">
-        <v>447570.85</v>
+        <v>378628.1</v>
       </c>
       <c r="D71" s="9">
-        <v>41800.2</v>
+        <v>34492.95</v>
       </c>
       <c r="E71" s="10">
-        <v>6.81</v>
+        <v>7.12</v>
       </c>
       <c r="F71" s="10">
-        <v>12.55</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B72" s="6">
-        <v>45138</v>
+        <v>45291</v>
       </c>
       <c r="C72" s="7">
-        <v>444567.6</v>
+        <v>364181.25</v>
       </c>
       <c r="D72" s="7">
-        <v>65987.7</v>
+        <v>42874.35</v>
       </c>
       <c r="E72" s="8">
-        <v>6.75</v>
+        <v>7.02</v>
       </c>
       <c r="F72" s="8">
-        <v>12.23</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B73" s="6">
-        <v>45122</v>
+        <v>45275</v>
       </c>
       <c r="C73" s="9">
-        <v>434827.8</v>
+        <v>387266.65</v>
       </c>
       <c r="D73" s="9">
-        <v>26230.4</v>
+        <v>68393.55</v>
       </c>
       <c r="E73" s="10">
-        <v>6.72</v>
+        <v>7.17</v>
       </c>
       <c r="F73" s="10">
-        <v>13.1</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B74" s="6">
-        <v>45107</v>
+        <v>45260</v>
       </c>
       <c r="C74" s="7">
-        <v>433212.15</v>
+        <v>394967.95</v>
       </c>
       <c r="D74" s="7">
-        <v>67287.35</v>
+        <v>59808.25</v>
       </c>
       <c r="E74" s="8">
-        <v>6.77</v>
+        <v>6.99</v>
       </c>
       <c r="F74" s="8">
-        <v>12.37</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B75" s="6">
-        <v>45092</v>
+        <v>45245</v>
       </c>
       <c r="C75" s="9">
-        <v>446509.9</v>
+        <v>417630.65</v>
       </c>
       <c r="D75" s="9">
-        <v>83468.3</v>
+        <v>41107.05</v>
       </c>
       <c r="E75" s="10">
-        <v>6.7147</v>
+        <v>7.1</v>
       </c>
       <c r="F75" s="10">
-        <v>11.7971</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B76" s="6">
-        <v>45077</v>
+        <v>45230</v>
       </c>
       <c r="C76" s="7">
-        <v>433543.35</v>
+        <v>413685.3</v>
       </c>
       <c r="D76" s="7">
-        <v>81179.55</v>
+        <v>50039.65</v>
       </c>
       <c r="E76" s="8">
-        <v>6.7278</v>
+        <v>7</v>
       </c>
       <c r="F76" s="8">
-        <v>16.3087</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B77" s="6">
-        <v>45061</v>
+        <v>45214</v>
       </c>
       <c r="C77" s="9">
-        <v>421454.4</v>
+        <v>418804.1</v>
       </c>
       <c r="D77" s="9">
-        <v>37178.35</v>
+        <v>25039.05</v>
       </c>
       <c r="E77" s="10">
-        <v>7.008</v>
+        <v>6.91</v>
       </c>
       <c r="F77" s="10">
-        <v>13.8402</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B78" s="6">
-        <v>45046</v>
+        <v>45199</v>
       </c>
       <c r="C78" s="7">
-        <v>421736.55</v>
+        <v>412234.35</v>
       </c>
       <c r="D78" s="7">
-        <v>58226.95</v>
+        <v>49675.85</v>
       </c>
       <c r="E78" s="8">
-        <v>6.7506</v>
+        <v>6.89</v>
       </c>
       <c r="F78" s="8">
-        <v>13.8402</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B79" s="6">
-        <v>45031</v>
+        <v>45184</v>
       </c>
       <c r="C79" s="9">
-        <v>391420.9</v>
+        <v>432568.65</v>
       </c>
       <c r="D79" s="9">
-        <v>52791.25</v>
+        <v>71469.15</v>
       </c>
       <c r="E79" s="10">
-        <v>6.7336</v>
+        <v>6.8429</v>
       </c>
       <c r="F79" s="10">
-        <v>13.8402</v>
+        <v>12.5012</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B80" s="6">
-        <v>45016</v>
+        <v>45169</v>
       </c>
       <c r="C80" s="7">
-        <v>353688.25</v>
+        <v>450064.05</v>
       </c>
       <c r="D80" s="7">
-        <v>61469.1</v>
+        <v>73816.05</v>
       </c>
       <c r="E80" s="8">
-        <v>6.88</v>
+        <v>6.93</v>
       </c>
       <c r="F80" s="8">
-        <v>12.6725</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B81" s="6">
-        <v>45000</v>
+        <v>45153</v>
       </c>
       <c r="C81" s="9">
-        <v>371326.7</v>
+        <v>447570.85</v>
       </c>
       <c r="D81" s="9">
-        <v>65488.9</v>
+        <v>41800.2</v>
       </c>
       <c r="E81" s="10">
-        <v>6.924</v>
+        <v>6.81</v>
       </c>
       <c r="F81" s="10">
-        <v>10.7756</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B82" s="6">
-        <v>44985</v>
+        <v>45138</v>
       </c>
       <c r="C82" s="7">
-        <v>364530.1</v>
+        <v>444567.6</v>
       </c>
       <c r="D82" s="7">
-        <v>58975.35</v>
+        <v>65987.7</v>
       </c>
       <c r="E82" s="8">
-        <v>6.7696</v>
+        <v>6.75</v>
       </c>
       <c r="F82" s="8">
-        <v>12.5107</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B83" s="6">
-        <v>44972</v>
+        <v>45122</v>
       </c>
       <c r="C83" s="9">
-        <v>368908.25</v>
+        <v>434827.8</v>
       </c>
       <c r="D83" s="9">
-        <v>43347.15</v>
+        <v>26230.4</v>
       </c>
       <c r="E83" s="10">
-        <v>6.6951</v>
+        <v>6.72</v>
       </c>
       <c r="F83" s="10">
-        <v>16.3087</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B84" s="6">
-        <v>44957</v>
+        <v>45107</v>
       </c>
       <c r="C84" s="7">
-        <v>363889.15</v>
+        <v>433212.15</v>
       </c>
       <c r="D84" s="7">
-        <v>51481.6</v>
+        <v>67287.35</v>
       </c>
       <c r="E84" s="8">
-        <v>6.5562</v>
+        <v>6.77</v>
       </c>
       <c r="F84" s="8">
-        <v>13.0958</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B85" s="6">
-        <v>44941</v>
+        <v>45092</v>
       </c>
       <c r="C85" s="9">
-        <v>381154.85</v>
+        <v>446509.9</v>
       </c>
       <c r="D85" s="9">
-        <v>45026.9</v>
+        <v>83468.3</v>
       </c>
       <c r="E85" s="10">
-        <v>6.3659</v>
+        <v>6.7147</v>
       </c>
       <c r="F85" s="10">
-        <v>12.7452</v>
+        <v>11.7971</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B86" s="6">
-        <v>44926</v>
+        <v>45077</v>
       </c>
       <c r="C86" s="7">
-        <v>359673.3</v>
+        <v>433543.35</v>
       </c>
       <c r="D86" s="7">
-        <v>54575.6</v>
+        <v>81179.55</v>
       </c>
       <c r="E86" s="8">
-        <v>6.5777</v>
+        <v>6.7278</v>
       </c>
       <c r="F86" s="8">
-        <v>13.7499</v>
+        <v>16.3087</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B87" s="6">
-        <v>44910</v>
+        <v>45061</v>
       </c>
       <c r="C87" s="9">
-        <v>363736.15</v>
+        <v>421454.4</v>
       </c>
       <c r="D87" s="9">
-        <v>65701.7</v>
+        <v>37178.35</v>
       </c>
       <c r="E87" s="10">
-        <v>6.3406</v>
+        <v>7.008</v>
       </c>
       <c r="F87" s="10">
-        <v>13.7489</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B88" s="6">
-        <v>44895</v>
+        <v>45046</v>
       </c>
       <c r="C88" s="7">
-        <v>362307.65</v>
+        <v>421736.55</v>
       </c>
       <c r="D88" s="7">
-        <v>66918.15</v>
+        <v>58226.95</v>
       </c>
       <c r="E88" s="8">
-        <v>6.5013</v>
+        <v>6.7506</v>
       </c>
       <c r="F88" s="8">
-        <v>12.0126</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B89" s="6">
-        <v>44880</v>
+        <v>45031</v>
       </c>
       <c r="C89" s="9">
-        <v>381455.7</v>
+        <v>391420.9</v>
       </c>
       <c r="D89" s="9">
-        <v>55158.95</v>
+        <v>52791.25</v>
       </c>
       <c r="E89" s="10">
-        <v>6.2147</v>
+        <v>6.7336</v>
       </c>
       <c r="F89" s="10">
-        <v>13.7767</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B90" s="6">
-        <v>44865</v>
+        <v>45016</v>
       </c>
       <c r="C90" s="7">
-        <v>373332.25</v>
+        <v>353688.25</v>
       </c>
       <c r="D90" s="7">
-        <v>39745.2</v>
+        <v>61469.1</v>
       </c>
       <c r="E90" s="8">
-        <v>6.3976</v>
+        <v>6.88</v>
       </c>
       <c r="F90" s="8">
-        <v>13.7196</v>
+        <v>12.6725</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B91" s="6">
-        <v>44849</v>
+        <v>45000</v>
       </c>
       <c r="C91" s="9">
-        <v>415849.4</v>
+        <v>371326.7</v>
       </c>
       <c r="D91" s="9">
-        <v>33906.35</v>
+        <v>65488.9</v>
       </c>
       <c r="E91" s="10">
-        <v>5.9234</v>
+        <v>6.924</v>
       </c>
       <c r="F91" s="10">
-        <v>11.977</v>
+        <v>10.7756</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B92" s="6">
-        <v>44834</v>
+        <v>44985</v>
       </c>
       <c r="C92" s="7">
-        <v>400866.35</v>
+        <v>364530.1</v>
       </c>
       <c r="D92" s="7">
-        <v>62062.8</v>
+        <v>58975.35</v>
       </c>
       <c r="E92" s="8">
-        <v>5.9095</v>
+        <v>6.7696</v>
       </c>
       <c r="F92" s="8">
-        <v>12.2577</v>
+        <v>12.5107</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B93" s="6">
-        <v>44819</v>
+        <v>44972</v>
       </c>
       <c r="C93" s="9">
-        <v>438644.65</v>
+        <v>368908.25</v>
       </c>
       <c r="D93" s="9">
-        <v>76371.55</v>
+        <v>43347.15</v>
       </c>
       <c r="E93" s="10">
-        <v>5.6552</v>
+        <v>6.6951</v>
       </c>
       <c r="F93" s="10">
-        <v>13.018</v>
+        <v>16.3087</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B94" s="6">
-        <v>44804</v>
+        <v>44957</v>
       </c>
       <c r="C94" s="7">
-        <v>410076.8</v>
+        <v>363889.15</v>
       </c>
       <c r="D94" s="7">
-        <v>87514.55</v>
+        <v>51481.6</v>
       </c>
       <c r="E94" s="8">
-        <v>5.6419</v>
+        <v>6.5562</v>
       </c>
       <c r="F94" s="8">
-        <v>13.658</v>
+        <v>13.0958</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B95" s="6">
-        <v>44788</v>
+        <v>44941</v>
       </c>
       <c r="C95" s="9">
-        <v>411152.1</v>
+        <v>381154.85</v>
       </c>
       <c r="D95" s="9">
-        <v>63123.35</v>
+        <v>45026.9</v>
       </c>
       <c r="E95" s="10">
-        <v>5.5132</v>
+        <v>6.3659</v>
       </c>
       <c r="F95" s="10">
-        <v>13.6888</v>
+        <v>12.7452</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B96" s="6">
-        <v>44773</v>
+        <v>44926</v>
       </c>
       <c r="C96" s="7">
-        <v>374226.45</v>
+        <v>359673.3</v>
       </c>
       <c r="D96" s="7">
-        <v>48380.15</v>
+        <v>54575.6</v>
       </c>
       <c r="E96" s="8">
-        <v>5.0497</v>
+        <v>6.5777</v>
       </c>
       <c r="F96" s="8">
-        <v>12.4036</v>
+        <v>13.7499</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B97" s="6">
-        <v>44757</v>
+        <v>44910</v>
       </c>
       <c r="C97" s="9">
-        <v>381468.7</v>
+        <v>363736.15</v>
       </c>
       <c r="D97" s="9">
-        <v>46218.5</v>
+        <v>65701.7</v>
       </c>
       <c r="E97" s="10">
-        <v>4.9454</v>
+        <v>6.3406</v>
       </c>
       <c r="F97" s="10">
-        <v>12.1283</v>
+        <v>13.7489</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B98" s="6">
-        <v>44742</v>
+        <v>44895</v>
       </c>
       <c r="C98" s="7">
-        <v>372542.35</v>
+        <v>362307.65</v>
       </c>
       <c r="D98" s="7">
-        <v>67595.3</v>
+        <v>66918.15</v>
       </c>
       <c r="E98" s="8">
-        <v>4.8837</v>
+        <v>6.5013</v>
       </c>
       <c r="F98" s="8">
-        <v>12.3782</v>
+        <v>12.0126</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B99" s="6">
-        <v>44727</v>
+        <v>44880</v>
       </c>
       <c r="C99" s="9">
-        <v>389282</v>
+        <v>381455.7</v>
       </c>
       <c r="D99" s="9">
-        <v>55172.75</v>
+        <v>55158.95</v>
       </c>
       <c r="E99" s="10">
-        <v>4.6892</v>
+        <v>6.2147</v>
       </c>
       <c r="F99" s="10">
-        <v>13.5229</v>
+        <v>13.7767</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B100" s="6">
-        <v>44712</v>
+        <v>44865</v>
       </c>
       <c r="C100" s="7">
-        <v>384544</v>
+        <v>373332.25</v>
       </c>
       <c r="D100" s="7">
-        <v>72437.6</v>
+        <v>39745.2</v>
       </c>
       <c r="E100" s="8">
-        <v>4.4817</v>
+        <v>6.3976</v>
       </c>
       <c r="F100" s="8">
-        <v>12.305</v>
+        <v>13.7196</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B101" s="6">
-        <v>44696</v>
+        <v>44849</v>
       </c>
       <c r="C101" s="9">
-        <v>384417.4</v>
+        <v>415849.4</v>
       </c>
       <c r="D101" s="9">
-        <v>44342.95</v>
+        <v>33906.35</v>
       </c>
       <c r="E101" s="10">
-        <v>3.9101</v>
+        <v>5.9234</v>
       </c>
       <c r="F101" s="10">
-        <v>10.5891</v>
+        <v>11.977</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B102" s="6">
-        <v>44681</v>
+        <v>44834</v>
       </c>
       <c r="C102" s="7">
-        <v>364999.65</v>
+        <v>400866.35</v>
       </c>
       <c r="D102" s="7">
-        <v>64930.35</v>
+        <v>62062.8</v>
       </c>
       <c r="E102" s="8">
-        <v>3.7706</v>
+        <v>5.9095</v>
       </c>
       <c r="F102" s="8">
-        <v>13.4069</v>
+        <v>12.2577</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B103" s="6">
-        <v>44666</v>
+        <v>44819</v>
       </c>
       <c r="C103" s="9">
-        <v>351642.1</v>
+        <v>438644.65</v>
       </c>
       <c r="D103" s="9">
-        <v>43499.3</v>
+        <v>76371.55</v>
       </c>
       <c r="E103" s="10">
-        <v>3.7011</v>
+        <v>5.6552</v>
       </c>
       <c r="F103" s="10">
-        <v>12.1102</v>
+        <v>13.018</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B104" s="6">
-        <v>44651</v>
+        <v>44804</v>
       </c>
       <c r="C104" s="7">
-        <v>352292.55</v>
+        <v>410076.8</v>
       </c>
       <c r="D104" s="7">
-        <v>71015.75</v>
+        <v>87514.55</v>
       </c>
       <c r="E104" s="8">
-        <v>3.7934</v>
+        <v>5.6419</v>
       </c>
       <c r="F104" s="8">
-        <v>12.1707</v>
+        <v>13.658</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B105" s="6">
-        <v>44635</v>
+        <v>44788</v>
       </c>
       <c r="C105" s="9">
-        <v>368090.45</v>
+        <v>411152.1</v>
       </c>
       <c r="D105" s="9">
-        <v>44531.6</v>
+        <v>63123.35</v>
       </c>
       <c r="E105" s="10">
-        <v>3.8395</v>
+        <v>5.5132</v>
       </c>
       <c r="F105" s="10">
-        <v>12.1463</v>
+        <v>13.6888</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B106" s="6">
-        <v>44620</v>
+        <v>44773</v>
       </c>
       <c r="C106" s="7">
-        <v>364645.3</v>
+        <v>374226.45</v>
       </c>
       <c r="D106" s="7">
-        <v>44435.25</v>
+        <v>48380.15</v>
       </c>
       <c r="E106" s="8">
-        <v>3.6362</v>
+        <v>5.0497</v>
       </c>
       <c r="F106" s="8">
-        <v>11.5076</v>
+        <v>12.4036</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B107" s="6">
-        <v>44607</v>
+        <v>44757</v>
       </c>
       <c r="C107" s="9">
-        <v>389950.7</v>
+        <v>381468.7</v>
       </c>
       <c r="D107" s="9">
-        <v>64232.7</v>
+        <v>46218.5</v>
       </c>
       <c r="E107" s="10">
-        <v>3.6696</v>
+        <v>4.9454</v>
       </c>
       <c r="F107" s="10">
-        <v>12.287</v>
+        <v>12.1283</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B108" s="6">
-        <v>44592</v>
+        <v>44742</v>
       </c>
       <c r="C108" s="7">
-        <v>395881</v>
+        <v>372542.35</v>
       </c>
       <c r="D108" s="7">
-        <v>71201.95</v>
+        <v>67595.3</v>
       </c>
       <c r="E108" s="8">
-        <v>3.4721</v>
+        <v>4.8837</v>
       </c>
       <c r="F108" s="8">
-        <v>12.3176</v>
+        <v>12.3782</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B109" s="6">
-        <v>44576</v>
+        <v>44727</v>
       </c>
       <c r="C109" s="9">
-        <v>386159.9</v>
+        <v>389282</v>
       </c>
       <c r="D109" s="9">
-        <v>64665.3</v>
+        <v>55172.75</v>
       </c>
       <c r="E109" s="10">
-        <v>3.3928</v>
+        <v>4.6892</v>
       </c>
       <c r="F109" s="10">
-        <v>13.4516</v>
+        <v>13.5229</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B110" s="6">
-        <v>44561</v>
+        <v>44712</v>
       </c>
       <c r="C110" s="7">
-        <v>350068.65</v>
+        <v>384544</v>
       </c>
       <c r="D110" s="7">
-        <v>87182.55</v>
+        <v>72437.6</v>
       </c>
       <c r="E110" s="8">
-        <v>3.4962</v>
+        <v>4.4817</v>
       </c>
       <c r="F110" s="8">
         <v>12.305</v>
@@ -2079,3144 +2080,3144 @@
     </row>
     <row r="111" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B111" s="6">
-        <v>44545</v>
+        <v>44696</v>
       </c>
       <c r="C111" s="9">
-        <v>446975.4</v>
+        <v>384417.4</v>
       </c>
       <c r="D111" s="9">
-        <v>161701.6</v>
+        <v>44342.95</v>
       </c>
       <c r="E111" s="10">
-        <v>3.3841</v>
+        <v>3.9101</v>
       </c>
       <c r="F111" s="10">
-        <v>12.3439</v>
+        <v>10.5891</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B112" s="6">
-        <v>44530</v>
+        <v>44681</v>
       </c>
       <c r="C112" s="7">
-        <v>388363.05</v>
+        <v>364999.65</v>
       </c>
       <c r="D112" s="7">
-        <v>115234.25</v>
+        <v>64930.35</v>
       </c>
       <c r="E112" s="8">
-        <v>3.3804</v>
+        <v>3.7706</v>
       </c>
       <c r="F112" s="8">
-        <v>12.763</v>
+        <v>13.4069</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B113" s="6">
-        <v>44515</v>
+        <v>44666</v>
       </c>
       <c r="C113" s="9">
-        <v>450890.7</v>
+        <v>351642.1</v>
       </c>
       <c r="D113" s="9">
-        <v>172504</v>
+        <v>43499.3</v>
       </c>
       <c r="E113" s="10">
-        <v>3.3804</v>
+        <v>3.7011</v>
       </c>
       <c r="F113" s="10">
-        <v>10.4429</v>
+        <v>12.1102</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B114" s="6">
-        <v>44500</v>
+        <v>44651</v>
       </c>
       <c r="C114" s="7">
-        <v>379278.3</v>
+        <v>352292.55</v>
       </c>
       <c r="D114" s="7">
-        <v>56178.95</v>
+        <v>71015.75</v>
       </c>
       <c r="E114" s="8">
-        <v>3.3194</v>
+        <v>3.7934</v>
       </c>
       <c r="F114" s="8">
-        <v>12.7106</v>
+        <v>12.1707</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B115" s="6">
-        <v>44484</v>
+        <v>44635</v>
       </c>
       <c r="C115" s="9">
-        <v>399720.05</v>
+        <v>368090.45</v>
       </c>
       <c r="D115" s="9">
-        <v>55664.1</v>
+        <v>44531.6</v>
       </c>
       <c r="E115" s="10">
-        <v>3.3841</v>
+        <v>3.8395</v>
       </c>
       <c r="F115" s="10">
-        <v>8.4664</v>
+        <v>12.1463</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B116" s="6">
-        <v>44469</v>
+        <v>44620</v>
       </c>
       <c r="C116" s="7">
-        <v>370982.1</v>
+        <v>364645.3</v>
       </c>
       <c r="D116" s="7">
-        <v>59167.05</v>
+        <v>44435.25</v>
       </c>
       <c r="E116" s="8">
-        <v>3.2589</v>
+        <v>3.6362</v>
       </c>
       <c r="F116" s="8">
-        <v>12.8346</v>
+        <v>11.5076</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B117" s="6">
-        <v>44454</v>
+        <v>44607</v>
       </c>
       <c r="C117" s="9">
-        <v>401221.25</v>
+        <v>389950.7</v>
       </c>
       <c r="D117" s="9">
-        <v>74402.55</v>
+        <v>64232.7</v>
       </c>
       <c r="E117" s="10">
-        <v>3.144</v>
+        <v>3.6696</v>
       </c>
       <c r="F117" s="10">
-        <v>13.4184</v>
+        <v>12.287</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B118" s="6">
-        <v>44439</v>
+        <v>44592</v>
       </c>
       <c r="C118" s="7">
-        <v>391504.85</v>
+        <v>395881</v>
       </c>
       <c r="D118" s="7">
-        <v>73288.65</v>
+        <v>71201.95</v>
       </c>
       <c r="E118" s="8">
-        <v>3.1474</v>
+        <v>3.4721</v>
       </c>
       <c r="F118" s="8">
-        <v>12.8346</v>
+        <v>12.3176</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B119" s="6">
-        <v>44423</v>
+        <v>44576</v>
       </c>
       <c r="C119" s="9">
-        <v>419726</v>
+        <v>386159.9</v>
       </c>
       <c r="D119" s="9">
-        <v>148470.35</v>
+        <v>64665.3</v>
       </c>
       <c r="E119" s="10">
-        <v>3.2558</v>
+        <v>3.3928</v>
       </c>
       <c r="F119" s="10">
-        <v>12.0106</v>
+        <v>13.4516</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B120" s="6">
-        <v>44408</v>
+        <v>44561</v>
       </c>
       <c r="C120" s="7">
-        <v>414981.65</v>
+        <v>350068.65</v>
       </c>
       <c r="D120" s="7">
-        <v>149052.15</v>
+        <v>87182.55</v>
       </c>
       <c r="E120" s="8">
-        <v>3.3811</v>
+        <v>3.4962</v>
       </c>
       <c r="F120" s="8">
-        <v>12.9355</v>
+        <v>12.305</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B121" s="6">
-        <v>44392</v>
+        <v>44545</v>
       </c>
       <c r="C121" s="9">
-        <v>471218</v>
+        <v>446975.4</v>
       </c>
       <c r="D121" s="9">
-        <v>117197.2</v>
+        <v>161701.6</v>
       </c>
       <c r="E121" s="10">
-        <v>3.3185</v>
+        <v>3.3841</v>
       </c>
       <c r="F121" s="10">
-        <v>12.7989</v>
+        <v>12.3439</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B122" s="6">
-        <v>44377</v>
+        <v>44530</v>
       </c>
       <c r="C122" s="7">
-        <v>376117.85</v>
+        <v>388363.05</v>
       </c>
       <c r="D122" s="7">
-        <v>97928</v>
+        <v>115234.25</v>
       </c>
       <c r="E122" s="8">
-        <v>3.4306</v>
+        <v>3.3804</v>
       </c>
       <c r="F122" s="8">
-        <v>13.0317</v>
+        <v>12.763</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B123" s="6">
-        <v>44362</v>
+        <v>44515</v>
       </c>
       <c r="C123" s="9">
-        <v>404804.9</v>
+        <v>450890.7</v>
       </c>
       <c r="D123" s="9">
-        <v>73440.4</v>
+        <v>172504</v>
       </c>
       <c r="E123" s="10">
-        <v>3.3641</v>
+        <v>3.3804</v>
       </c>
       <c r="F123" s="10">
-        <v>11.3226</v>
+        <v>10.4429</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B124" s="6">
-        <v>44347</v>
+        <v>44500</v>
       </c>
       <c r="C124" s="7">
-        <v>388707.25</v>
+        <v>379278.3</v>
       </c>
       <c r="D124" s="7">
-        <v>61593.9</v>
+        <v>56178.95</v>
       </c>
       <c r="E124" s="8">
-        <v>3.3628</v>
+        <v>3.3194</v>
       </c>
       <c r="F124" s="8">
-        <v>12.8666</v>
+        <v>12.7106</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B125" s="6">
-        <v>44331</v>
+        <v>44484</v>
       </c>
       <c r="C125" s="9">
-        <v>404445.55</v>
+        <v>399720.05</v>
       </c>
       <c r="D125" s="9">
-        <v>66560.6</v>
+        <v>55664.1</v>
       </c>
       <c r="E125" s="10">
-        <v>3.1892</v>
+        <v>3.3841</v>
       </c>
       <c r="F125" s="10">
-        <v>11.6903</v>
+        <v>8.4664</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B126" s="6">
-        <v>44316</v>
+        <v>44469</v>
       </c>
       <c r="C126" s="7">
-        <v>374846.75</v>
+        <v>370982.1</v>
       </c>
       <c r="D126" s="7">
-        <v>53838.6</v>
+        <v>59167.05</v>
       </c>
       <c r="E126" s="8">
-        <v>3.2054</v>
+        <v>3.2589</v>
       </c>
       <c r="F126" s="8">
-        <v>13.0225</v>
+        <v>12.8346</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B127" s="6">
-        <v>44301</v>
+        <v>44454</v>
       </c>
       <c r="C127" s="9">
-        <v>382838.15</v>
+        <v>401221.25</v>
       </c>
       <c r="D127" s="9">
-        <v>35737.15</v>
+        <v>74402.55</v>
       </c>
       <c r="E127" s="10">
-        <v>3.1654</v>
+        <v>3.144</v>
       </c>
       <c r="F127" s="10">
-        <v>13.0885</v>
+        <v>13.4184</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B128" s="6">
-        <v>44286</v>
+        <v>44439</v>
       </c>
       <c r="C128" s="7">
-        <v>364374.3</v>
+        <v>391504.85</v>
       </c>
       <c r="D128" s="7">
-        <v>96417.25</v>
+        <v>73288.65</v>
       </c>
       <c r="E128" s="8">
-        <v>3.3227</v>
+        <v>3.1474</v>
       </c>
       <c r="F128" s="8">
-        <v>13.3656</v>
+        <v>12.8346</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B129" s="6">
-        <v>44270</v>
+        <v>44423</v>
       </c>
       <c r="C129" s="9">
-        <v>403442.7</v>
+        <v>419726</v>
       </c>
       <c r="D129" s="9">
-        <v>127121</v>
+        <v>148470.35</v>
       </c>
       <c r="E129" s="10">
-        <v>3.1644</v>
+        <v>3.2558</v>
       </c>
       <c r="F129" s="10">
-        <v>12.5153</v>
+        <v>12.0106</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B130" s="6">
-        <v>44255</v>
+        <v>44408</v>
       </c>
       <c r="C130" s="7">
-        <v>390852.95</v>
+        <v>414981.65</v>
       </c>
       <c r="D130" s="7">
-        <v>69500.35</v>
+        <v>149052.15</v>
       </c>
       <c r="E130" s="8">
-        <v>3.0973</v>
+        <v>3.3811</v>
       </c>
       <c r="F130" s="8">
-        <v>12.5962</v>
+        <v>12.9355</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B131" s="6">
-        <v>44242</v>
+        <v>44392</v>
       </c>
       <c r="C131" s="9">
-        <v>399404</v>
+        <v>471218</v>
       </c>
       <c r="D131" s="9">
-        <v>88216.1</v>
+        <v>117197.2</v>
       </c>
       <c r="E131" s="10">
-        <v>3.2181</v>
+        <v>3.3185</v>
       </c>
       <c r="F131" s="10">
-        <v>13.5159</v>
+        <v>12.7989</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B132" s="6">
-        <v>44227</v>
+        <v>44377</v>
       </c>
       <c r="C132" s="7">
-        <v>410651.9</v>
+        <v>376117.85</v>
       </c>
       <c r="D132" s="7">
-        <v>89040.6</v>
+        <v>97928</v>
       </c>
       <c r="E132" s="8">
-        <v>3.1755</v>
+        <v>3.4306</v>
       </c>
       <c r="F132" s="8">
-        <v>11.3224</v>
+        <v>13.0317</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B133" s="6">
-        <v>44211</v>
+        <v>44362</v>
       </c>
       <c r="C133" s="9">
-        <v>386216.3</v>
+        <v>404804.9</v>
       </c>
       <c r="D133" s="9">
-        <v>49901.8</v>
+        <v>73440.4</v>
       </c>
       <c r="E133" s="10">
-        <v>2.9409</v>
+        <v>3.3641</v>
       </c>
       <c r="F133" s="10">
-        <v>8.5297</v>
+        <v>11.3226</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B134" s="6">
-        <v>44196</v>
+        <v>44347</v>
       </c>
       <c r="C134" s="7">
-        <v>365185.05</v>
+        <v>388707.25</v>
       </c>
       <c r="D134" s="7">
-        <v>87488.25</v>
+        <v>61593.9</v>
       </c>
       <c r="E134" s="8">
-        <v>3.0585</v>
+        <v>3.3628</v>
       </c>
       <c r="F134" s="8">
-        <v>12.7323</v>
+        <v>12.8666</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B135" s="6">
-        <v>44180</v>
+        <v>44331</v>
       </c>
       <c r="C135" s="9">
-        <v>390613.25</v>
+        <v>404445.55</v>
       </c>
       <c r="D135" s="9">
-        <v>102307.55</v>
+        <v>66560.6</v>
       </c>
       <c r="E135" s="10">
-        <v>2.6489</v>
+        <v>3.1892</v>
       </c>
       <c r="F135" s="10">
-        <v>12.6137</v>
+        <v>11.6903</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B136" s="6">
-        <v>44165</v>
+        <v>44316</v>
       </c>
       <c r="C136" s="7">
-        <v>373146.1</v>
+        <v>374846.75</v>
       </c>
       <c r="D136" s="7">
-        <v>64386.2</v>
+        <v>53838.6</v>
       </c>
       <c r="E136" s="8">
-        <v>2.7862</v>
+        <v>3.2054</v>
       </c>
       <c r="F136" s="8">
-        <v>8.8025</v>
+        <v>13.0225</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B137" s="6">
-        <v>44150</v>
+        <v>44301</v>
       </c>
       <c r="C137" s="9">
-        <v>389427.1</v>
+        <v>382838.15</v>
       </c>
       <c r="D137" s="9">
-        <v>57001.85</v>
+        <v>35737.15</v>
       </c>
       <c r="E137" s="10">
-        <v>3.0869</v>
+        <v>3.1654</v>
       </c>
       <c r="F137" s="10">
-        <v>11.3224</v>
+        <v>13.0885</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B138" s="6">
-        <v>44135</v>
+        <v>44286</v>
       </c>
       <c r="C138" s="7">
-        <v>380112.2</v>
+        <v>364374.3</v>
       </c>
       <c r="D138" s="7">
-        <v>40838.65</v>
+        <v>96417.25</v>
       </c>
       <c r="E138" s="8">
-        <v>3.1924</v>
+        <v>3.3227</v>
       </c>
       <c r="F138" s="8">
-        <v>14.1936</v>
+        <v>13.3656</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B139" s="6">
-        <v>44119</v>
+        <v>44270</v>
       </c>
       <c r="C139" s="9">
-        <v>395015.55</v>
+        <v>403442.7</v>
       </c>
       <c r="D139" s="9">
-        <v>81950.2</v>
+        <v>127121</v>
       </c>
       <c r="E139" s="10">
-        <v>3.248</v>
+        <v>3.1644</v>
       </c>
       <c r="F139" s="10">
-        <v>11.9438</v>
+        <v>12.5153</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B140" s="6">
-        <v>44104</v>
+        <v>44255</v>
       </c>
       <c r="C140" s="7">
-        <v>362310.1</v>
+        <v>390852.95</v>
       </c>
       <c r="D140" s="7">
-        <v>86727.4</v>
+        <v>69500.35</v>
       </c>
       <c r="E140" s="8">
-        <v>3.3215</v>
+        <v>3.0973</v>
       </c>
       <c r="F140" s="8">
-        <v>11.8636</v>
+        <v>12.5962</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B141" s="6">
-        <v>44089</v>
+        <v>44242</v>
       </c>
       <c r="C141" s="9">
-        <v>418270.55</v>
+        <v>399404</v>
       </c>
       <c r="D141" s="9">
-        <v>106924.35</v>
+        <v>88216.1</v>
       </c>
       <c r="E141" s="10">
-        <v>3.1042</v>
+        <v>3.2181</v>
       </c>
       <c r="F141" s="10">
-        <v>8.8698</v>
+        <v>13.5159</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B142" s="6">
-        <v>44074</v>
+        <v>44227</v>
       </c>
       <c r="C142" s="7">
-        <v>372600.8</v>
+        <v>410651.9</v>
       </c>
       <c r="D142" s="7">
-        <v>68405.75</v>
+        <v>89040.6</v>
       </c>
       <c r="E142" s="8">
-        <v>3.1738</v>
+        <v>3.1755</v>
       </c>
       <c r="F142" s="8">
-        <v>13.1447</v>
+        <v>11.3224</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B143" s="6">
-        <v>44058</v>
+        <v>44211</v>
       </c>
       <c r="C143" s="9">
-        <v>380587.65</v>
+        <v>386216.3</v>
       </c>
       <c r="D143" s="9">
-        <v>61152</v>
+        <v>49901.8</v>
       </c>
       <c r="E143" s="10">
-        <v>3.3135</v>
+        <v>2.9409</v>
       </c>
       <c r="F143" s="10">
-        <v>11.7895</v>
+        <v>8.5297</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B144" s="6">
-        <v>44043</v>
+        <v>44196</v>
       </c>
       <c r="C144" s="7">
-        <v>374817.2</v>
+        <v>365185.05</v>
       </c>
       <c r="D144" s="7">
-        <v>53608.1</v>
+        <v>87488.25</v>
       </c>
       <c r="E144" s="8">
-        <v>3.1755</v>
+        <v>3.0585</v>
       </c>
       <c r="F144" s="8">
-        <v>12.3297</v>
+        <v>12.7323</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B145" s="6">
-        <v>44027</v>
+        <v>44180</v>
       </c>
       <c r="C145" s="9">
-        <v>402660.5</v>
+        <v>390613.25</v>
       </c>
       <c r="D145" s="9">
-        <v>37730.15</v>
+        <v>102307.55</v>
       </c>
       <c r="E145" s="10">
-        <v>2.9774</v>
+        <v>2.6489</v>
       </c>
       <c r="F145" s="10">
-        <v>12.0382</v>
+        <v>12.6137</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B146" s="6">
-        <v>44012</v>
+        <v>44165</v>
       </c>
       <c r="C146" s="7">
-        <v>391482.3</v>
+        <v>373146.1</v>
       </c>
       <c r="D146" s="7">
-        <v>56270.85</v>
+        <v>64386.2</v>
       </c>
       <c r="E146" s="8">
-        <v>3.1848</v>
+        <v>2.7862</v>
       </c>
       <c r="F146" s="8">
-        <v>13.3542</v>
+        <v>8.8025</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B147" s="6">
-        <v>43997</v>
+        <v>44150</v>
       </c>
       <c r="C147" s="9">
-        <v>413652.4</v>
+        <v>389427.1</v>
       </c>
       <c r="D147" s="9">
-        <v>68691.7</v>
+        <v>57001.85</v>
       </c>
       <c r="E147" s="10">
-        <v>3.3126</v>
+        <v>3.0869</v>
       </c>
       <c r="F147" s="10">
-        <v>13.1138</v>
+        <v>11.3224</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B148" s="6">
-        <v>43982</v>
+        <v>44135</v>
       </c>
       <c r="C148" s="7">
-        <v>425817</v>
+        <v>380112.2</v>
       </c>
       <c r="D148" s="7">
-        <v>52155.65</v>
+        <v>40838.65</v>
       </c>
       <c r="E148" s="8">
-        <v>3.1259</v>
+        <v>3.1924</v>
       </c>
       <c r="F148" s="8">
-        <v>12.1381</v>
+        <v>14.1936</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B149" s="6">
-        <v>43966</v>
+        <v>44119</v>
       </c>
       <c r="C149" s="9">
-        <v>433624.85</v>
+        <v>395015.55</v>
       </c>
       <c r="D149" s="9">
-        <v>62636.85</v>
+        <v>81950.2</v>
       </c>
       <c r="E149" s="10">
-        <v>3.8329</v>
+        <v>3.248</v>
       </c>
       <c r="F149" s="10">
-        <v>12.6933</v>
+        <v>11.9438</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B150" s="6">
-        <v>43951</v>
+        <v>44104</v>
       </c>
       <c r="C150" s="7">
-        <v>417227.05</v>
+        <v>362310.1</v>
       </c>
       <c r="D150" s="7">
-        <v>77889.2</v>
+        <v>86727.4</v>
       </c>
       <c r="E150" s="8">
-        <v>3.7778</v>
+        <v>3.3215</v>
       </c>
       <c r="F150" s="8">
-        <v>10.4458</v>
+        <v>11.8636</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B151" s="6">
-        <v>43936</v>
+        <v>44089</v>
       </c>
       <c r="C151" s="9">
-        <v>381273.5</v>
+        <v>418270.55</v>
       </c>
       <c r="D151" s="9">
-        <v>54770.55</v>
+        <v>106924.35</v>
       </c>
       <c r="E151" s="10">
-        <v>4.5516</v>
+        <v>3.1042</v>
       </c>
       <c r="F151" s="10">
-        <v>9.8995</v>
+        <v>8.8698</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B152" s="6">
-        <v>43921</v>
+        <v>44074</v>
       </c>
       <c r="C152" s="7">
-        <v>344526.95</v>
+        <v>372600.8</v>
       </c>
       <c r="D152" s="7">
-        <v>63166.1</v>
+        <v>68405.75</v>
       </c>
       <c r="E152" s="8">
-        <v>4.8781</v>
+        <v>3.1738</v>
       </c>
       <c r="F152" s="8">
-        <v>12.3855</v>
+        <v>13.1447</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B153" s="6">
-        <v>43905</v>
+        <v>44058</v>
       </c>
       <c r="C153" s="9">
-        <v>401724.55</v>
+        <v>380587.65</v>
       </c>
       <c r="D153" s="9">
-        <v>148273.3</v>
+        <v>61152</v>
       </c>
       <c r="E153" s="10">
-        <v>5.0083</v>
+        <v>3.3135</v>
       </c>
       <c r="F153" s="10">
-        <v>13.9511</v>
+        <v>11.7895</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B154" s="6">
-        <v>43890</v>
+        <v>44043</v>
       </c>
       <c r="C154" s="7">
-        <v>400200.25</v>
+        <v>374817.2</v>
       </c>
       <c r="D154" s="7">
-        <v>56287.5</v>
+        <v>53608.1</v>
       </c>
       <c r="E154" s="8">
-        <v>5.1087</v>
+        <v>3.1755</v>
       </c>
       <c r="F154" s="8">
-        <v>13.4489</v>
+        <v>12.3297</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B155" s="6">
-        <v>43876</v>
+        <v>44027</v>
       </c>
       <c r="C155" s="9">
-        <v>435803.25</v>
+        <v>402660.5</v>
       </c>
       <c r="D155" s="9">
-        <v>84356.4</v>
+        <v>37730.15</v>
       </c>
       <c r="E155" s="10">
-        <v>5.1064</v>
+        <v>2.9774</v>
       </c>
       <c r="F155" s="10">
-        <v>12.5282</v>
+        <v>12.0382</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B156" s="6">
-        <v>43861</v>
+        <v>44012</v>
       </c>
       <c r="C156" s="7">
-        <v>421988.85</v>
+        <v>391482.3</v>
       </c>
       <c r="D156" s="7">
-        <v>72673.75</v>
+        <v>56270.85</v>
       </c>
       <c r="E156" s="8">
-        <v>5.1171</v>
+        <v>3.1848</v>
       </c>
       <c r="F156" s="8">
-        <v>13.0458</v>
+        <v>13.3542</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B157" s="6">
-        <v>43845</v>
+        <v>43997</v>
       </c>
       <c r="C157" s="9">
-        <v>434895.3</v>
+        <v>413652.4</v>
       </c>
       <c r="D157" s="9">
-        <v>37801.8</v>
+        <v>68691.7</v>
       </c>
       <c r="E157" s="10">
-        <v>4.745</v>
+        <v>3.3126</v>
       </c>
       <c r="F157" s="10">
-        <v>14.2879</v>
+        <v>13.1138</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B158" s="6">
-        <v>43830</v>
+        <v>43982</v>
       </c>
       <c r="C158" s="7">
-        <v>414906.3</v>
+        <v>425817</v>
       </c>
       <c r="D158" s="7">
-        <v>83567.75</v>
+        <v>52155.65</v>
       </c>
       <c r="E158" s="8">
-        <v>4.9939</v>
+        <v>3.1259</v>
       </c>
       <c r="F158" s="8">
-        <v>13.1778</v>
+        <v>12.1381</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B159" s="6">
-        <v>43814</v>
+        <v>43966</v>
       </c>
       <c r="C159" s="9">
-        <v>457213.55</v>
+        <v>433624.85</v>
       </c>
       <c r="D159" s="9">
-        <v>97114</v>
+        <v>62636.85</v>
       </c>
       <c r="E159" s="10">
-        <v>4.8781</v>
+        <v>3.8329</v>
       </c>
       <c r="F159" s="10">
-        <v>12.6487</v>
+        <v>12.6933</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B160" s="6">
-        <v>43799</v>
+        <v>43951</v>
       </c>
       <c r="C160" s="7">
-        <v>458415.6</v>
+        <v>417227.05</v>
       </c>
       <c r="D160" s="7">
-        <v>80022.9</v>
+        <v>77889.2</v>
       </c>
       <c r="E160" s="8">
-        <v>5.0065</v>
+        <v>3.7778</v>
       </c>
       <c r="F160" s="8">
-        <v>13.299</v>
+        <v>10.4458</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B161" s="6">
-        <v>43784</v>
+        <v>43936</v>
       </c>
       <c r="C161" s="9">
-        <v>461813.4</v>
+        <v>381273.5</v>
       </c>
       <c r="D161" s="9">
-        <v>94360.65</v>
+        <v>54770.55</v>
       </c>
       <c r="E161" s="10">
-        <v>4.78</v>
+        <v>4.5516</v>
       </c>
       <c r="F161" s="10">
-        <v>13.23</v>
+        <v>9.8995</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B162" s="6">
-        <v>43769</v>
+        <v>43921</v>
       </c>
       <c r="C162" s="7">
-        <v>462308.75</v>
+        <v>344526.95</v>
       </c>
       <c r="D162" s="7">
-        <v>80459.45</v>
+        <v>63166.1</v>
       </c>
       <c r="E162" s="8">
-        <v>5.027</v>
+        <v>4.8781</v>
       </c>
       <c r="F162" s="8">
-        <v>14.0802</v>
+        <v>12.3855</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B163" s="6">
-        <v>43753</v>
+        <v>43905</v>
       </c>
       <c r="C163" s="9">
-        <v>486121.25</v>
+        <v>401724.55</v>
       </c>
       <c r="D163" s="9">
-        <v>106083.5</v>
+        <v>148273.3</v>
       </c>
       <c r="E163" s="10">
-        <v>5.1879</v>
+        <v>5.0083</v>
       </c>
       <c r="F163" s="10">
-        <v>13.2197</v>
+        <v>13.9511</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B164" s="6">
-        <v>43738</v>
+        <v>43890</v>
       </c>
       <c r="C164" s="7">
-        <v>459742.1</v>
+        <v>400200.25</v>
       </c>
       <c r="D164" s="7">
-        <v>94892.9</v>
+        <v>56287.5</v>
       </c>
       <c r="E164" s="8">
-        <v>5.2989</v>
+        <v>5.1087</v>
       </c>
       <c r="F164" s="8">
-        <v>11.9925</v>
+        <v>13.4489</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B165" s="6">
-        <v>43723</v>
+        <v>43876</v>
       </c>
       <c r="C165" s="9">
-        <v>506326.9</v>
+        <v>435803.25</v>
       </c>
       <c r="D165" s="9">
-        <v>71069.7</v>
+        <v>84356.4</v>
       </c>
       <c r="E165" s="10">
-        <v>5.291</v>
+        <v>5.1064</v>
       </c>
       <c r="F165" s="10">
-        <v>9.9266</v>
+        <v>12.5282</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B166" s="6">
-        <v>43708</v>
+        <v>43861</v>
       </c>
       <c r="C166" s="7">
-        <v>497176.75</v>
+        <v>421988.85</v>
       </c>
       <c r="D166" s="7">
-        <v>77603.3</v>
+        <v>72673.75</v>
       </c>
       <c r="E166" s="8">
-        <v>5.3746</v>
+        <v>5.1171</v>
       </c>
       <c r="F166" s="8">
-        <v>13.3927</v>
+        <v>13.0458</v>
       </c>
     </row>
     <row r="167" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B167" s="6">
-        <v>43692</v>
+        <v>43845</v>
       </c>
       <c r="C167" s="9">
-        <v>516900.55</v>
+        <v>434895.3</v>
       </c>
       <c r="D167" s="9">
-        <v>123734.95</v>
+        <v>37801.8</v>
       </c>
       <c r="E167" s="10">
-        <v>5.3838</v>
+        <v>4.745</v>
       </c>
       <c r="F167" s="10">
-        <v>13.9935</v>
+        <v>14.2879</v>
       </c>
     </row>
     <row r="168" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B168" s="6">
-        <v>43677</v>
+        <v>43830</v>
       </c>
       <c r="C168" s="7">
-        <v>509412.8</v>
+        <v>414906.3</v>
       </c>
       <c r="D168" s="7">
-        <v>119806.65</v>
+        <v>83567.75</v>
       </c>
       <c r="E168" s="8">
-        <v>5.6897</v>
+        <v>4.9939</v>
       </c>
       <c r="F168" s="8">
-        <v>14.465</v>
+        <v>13.1778</v>
       </c>
     </row>
     <row r="169" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B169" s="6">
-        <v>43661</v>
+        <v>43814</v>
       </c>
       <c r="C169" s="9">
-        <v>544981.4</v>
+        <v>457213.55</v>
       </c>
       <c r="D169" s="9">
-        <v>81216.1</v>
+        <v>97114</v>
       </c>
       <c r="E169" s="10">
-        <v>5.8064</v>
+        <v>4.8781</v>
       </c>
       <c r="F169" s="10">
-        <v>13.1919</v>
+        <v>12.6487</v>
       </c>
     </row>
     <row r="170" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B170" s="6">
-        <v>43646</v>
+        <v>43799</v>
       </c>
       <c r="C170" s="7">
-        <v>503943.3</v>
+        <v>458415.6</v>
       </c>
       <c r="D170" s="7">
-        <v>107691.05</v>
+        <v>80022.9</v>
       </c>
       <c r="E170" s="8">
-        <v>5.7926</v>
+        <v>5.0065</v>
       </c>
       <c r="F170" s="8">
-        <v>11.8912</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="171" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B171" s="6">
-        <v>43631</v>
+        <v>43784</v>
       </c>
       <c r="C171" s="9">
-        <v>556177.6</v>
+        <v>461813.4</v>
       </c>
       <c r="D171" s="9">
-        <v>107868.85</v>
+        <v>94360.65</v>
       </c>
       <c r="E171" s="10">
-        <v>5.8661</v>
+        <v>4.78</v>
       </c>
       <c r="F171" s="10">
-        <v>13.9656</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="172" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B172" s="6">
-        <v>43616</v>
+        <v>43769</v>
       </c>
       <c r="C172" s="7">
-        <v>551983.5</v>
+        <v>462308.75</v>
       </c>
       <c r="D172" s="7">
-        <v>102453.5</v>
+        <v>80459.45</v>
       </c>
       <c r="E172" s="8">
-        <v>6.43</v>
+        <v>5.027</v>
       </c>
       <c r="F172" s="8">
-        <v>10.0776</v>
+        <v>14.0802</v>
       </c>
     </row>
     <row r="173" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B173" s="6">
-        <v>43600</v>
+        <v>43753</v>
       </c>
       <c r="C173" s="9">
-        <v>583720.6</v>
+        <v>486121.25</v>
       </c>
       <c r="D173" s="9">
-        <v>105970.75</v>
+        <v>106083.5</v>
       </c>
       <c r="E173" s="10">
-        <v>6.8083</v>
+        <v>5.1879</v>
       </c>
       <c r="F173" s="10">
-        <v>13.0417</v>
+        <v>13.2197</v>
       </c>
     </row>
     <row r="174" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B174" s="6">
-        <v>43585</v>
+        <v>43738</v>
       </c>
       <c r="C174" s="7">
-        <v>542885.8</v>
+        <v>459742.1</v>
       </c>
       <c r="D174" s="7">
-        <v>71210.8</v>
+        <v>94892.9</v>
       </c>
       <c r="E174" s="8">
-        <v>6.6671</v>
+        <v>5.2989</v>
       </c>
       <c r="F174" s="8">
-        <v>13.1405</v>
+        <v>11.9925</v>
       </c>
     </row>
     <row r="175" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B175" s="6">
-        <v>43570</v>
+        <v>43723</v>
       </c>
       <c r="C175" s="9">
-        <v>573599.8</v>
+        <v>506326.9</v>
       </c>
       <c r="D175" s="9">
-        <v>129208.35</v>
+        <v>71069.7</v>
       </c>
       <c r="E175" s="10">
-        <v>6.4078</v>
+        <v>5.291</v>
       </c>
       <c r="F175" s="10">
-        <v>9.9801</v>
+        <v>9.9266</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B176" s="6">
-        <v>43555</v>
+        <v>43708</v>
       </c>
       <c r="C176" s="7">
-        <v>483084.45</v>
+        <v>497176.75</v>
       </c>
       <c r="D176" s="7">
-        <v>101295.55</v>
+        <v>77603.3</v>
       </c>
       <c r="E176" s="8">
-        <v>6.5432</v>
+        <v>5.3746</v>
       </c>
       <c r="F176" s="8">
-        <v>12.5962</v>
+        <v>13.3927</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B177" s="6">
-        <v>43539</v>
+        <v>43692</v>
       </c>
       <c r="C177" s="9">
-        <v>530952</v>
+        <v>516900.55</v>
       </c>
       <c r="D177" s="9">
-        <v>124063</v>
+        <v>123734.95</v>
       </c>
       <c r="E177" s="10">
-        <v>6.4449</v>
+        <v>5.3838</v>
       </c>
       <c r="F177" s="10">
-        <v>9.9801</v>
+        <v>13.9935</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B178" s="6">
-        <v>43524</v>
+        <v>43677</v>
       </c>
       <c r="C178" s="7">
-        <v>520811.05</v>
+        <v>509412.8</v>
       </c>
       <c r="D178" s="7">
-        <v>90081.2</v>
+        <v>119806.65</v>
       </c>
       <c r="E178" s="8">
-        <v>6.3614</v>
+        <v>5.6897</v>
       </c>
       <c r="F178" s="8">
-        <v>11.7416</v>
+        <v>14.465</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B179" s="6">
-        <v>43511</v>
+        <v>43661</v>
       </c>
       <c r="C179" s="9">
-        <v>524231.25</v>
+        <v>544981.4</v>
       </c>
       <c r="D179" s="9">
-        <v>103546.7</v>
+        <v>81216.1</v>
       </c>
       <c r="E179" s="10">
-        <v>6.4137</v>
+        <v>5.8064</v>
       </c>
       <c r="F179" s="10">
-        <v>13.4018</v>
+        <v>13.1919</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B180" s="6">
-        <v>43496</v>
+        <v>43646</v>
       </c>
       <c r="C180" s="7">
-        <v>528741.2</v>
+        <v>503943.3</v>
       </c>
       <c r="D180" s="7">
-        <v>107391.55</v>
+        <v>107691.05</v>
       </c>
       <c r="E180" s="8">
-        <v>6.5444</v>
+        <v>5.7926</v>
       </c>
       <c r="F180" s="8">
-        <v>12.6231</v>
+        <v>11.8912</v>
       </c>
     </row>
     <row r="181" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B181" s="6">
-        <v>43480</v>
+        <v>43631</v>
       </c>
       <c r="C181" s="9">
-        <v>554022.45</v>
+        <v>556177.6</v>
       </c>
       <c r="D181" s="9">
-        <v>100992.3</v>
+        <v>107868.85</v>
       </c>
       <c r="E181" s="10">
-        <v>6.6592</v>
+        <v>5.8661</v>
       </c>
       <c r="F181" s="10">
-        <v>10.9448</v>
+        <v>13.9656</v>
       </c>
     </row>
     <row r="182" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B182" s="6">
-        <v>43465</v>
+        <v>43616</v>
       </c>
       <c r="C182" s="7">
-        <v>498728.65</v>
+        <v>551983.5</v>
       </c>
       <c r="D182" s="7">
-        <v>95777.1</v>
+        <v>102453.5</v>
       </c>
       <c r="E182" s="8">
-        <v>6.7834</v>
+        <v>6.43</v>
       </c>
       <c r="F182" s="8">
-        <v>10.2932</v>
+        <v>10.0776</v>
       </c>
     </row>
     <row r="183" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B183" s="6">
-        <v>43449</v>
+        <v>43600</v>
       </c>
       <c r="C183" s="9">
-        <v>546077.75</v>
+        <v>583720.6</v>
       </c>
       <c r="D183" s="9">
-        <v>103648.9</v>
+        <v>105970.75</v>
       </c>
       <c r="E183" s="10">
-        <v>6.5107</v>
+        <v>6.8083</v>
       </c>
       <c r="F183" s="10">
-        <v>11.1794</v>
+        <v>13.0417</v>
       </c>
     </row>
     <row r="184" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B184" s="6">
-        <v>43434</v>
+        <v>43585</v>
       </c>
       <c r="C184" s="7">
-        <v>560613.81</v>
+        <v>542885.8</v>
       </c>
       <c r="D184" s="7">
-        <v>130058.7</v>
+        <v>71210.8</v>
       </c>
       <c r="E184" s="8">
-        <v>6.6326</v>
+        <v>6.6671</v>
       </c>
       <c r="F184" s="8">
-        <v>11.0906</v>
+        <v>13.1405</v>
       </c>
     </row>
     <row r="185" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B185" s="6">
-        <v>43419</v>
+        <v>43570</v>
       </c>
       <c r="C185" s="9">
-        <v>584716.61</v>
+        <v>573599.8</v>
       </c>
       <c r="D185" s="9">
-        <v>106623.3</v>
+        <v>129208.35</v>
       </c>
       <c r="E185" s="10">
-        <v>6.6899</v>
+        <v>6.4078</v>
       </c>
       <c r="F185" s="10">
-        <v>11.7341</v>
+        <v>9.9801</v>
       </c>
     </row>
     <row r="186" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B186" s="6">
-        <v>43404</v>
+        <v>43555</v>
       </c>
       <c r="C186" s="7">
-        <v>587688.66</v>
+        <v>483084.45</v>
       </c>
       <c r="D186" s="7">
-        <v>94931.15</v>
+        <v>101295.55</v>
       </c>
       <c r="E186" s="8">
-        <v>6.8656</v>
+        <v>6.5432</v>
       </c>
       <c r="F186" s="8">
-        <v>10.3806</v>
+        <v>12.5962</v>
       </c>
     </row>
     <row r="187" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B187" s="6">
-        <v>43388</v>
+        <v>43539</v>
       </c>
       <c r="C187" s="9">
-        <v>594490.16</v>
+        <v>530952</v>
       </c>
       <c r="D187" s="9">
-        <v>79913.95</v>
+        <v>124063</v>
       </c>
       <c r="E187" s="10">
-        <v>6.7238</v>
+        <v>6.4449</v>
       </c>
       <c r="F187" s="10">
-        <v>17.4909</v>
+        <v>9.9801</v>
       </c>
     </row>
     <row r="188" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B188" s="6">
-        <v>43373</v>
+        <v>43524</v>
       </c>
       <c r="C188" s="7">
-        <v>556198.16</v>
+        <v>520811.05</v>
       </c>
       <c r="D188" s="7">
-        <v>112520.4</v>
+        <v>90081.2</v>
       </c>
       <c r="E188" s="8">
-        <v>6.8377</v>
+        <v>6.3614</v>
       </c>
       <c r="F188" s="8">
-        <v>11.1828</v>
+        <v>11.7416</v>
       </c>
     </row>
     <row r="189" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B189" s="6">
-        <v>43358</v>
+        <v>43511</v>
       </c>
       <c r="C189" s="9">
-        <v>640808.71</v>
+        <v>524231.25</v>
       </c>
       <c r="D189" s="9">
-        <v>111261.7</v>
+        <v>103546.7</v>
       </c>
       <c r="E189" s="10">
-        <v>6.5644</v>
+        <v>6.4137</v>
       </c>
       <c r="F189" s="10">
-        <v>15.7923</v>
+        <v>13.4018</v>
       </c>
     </row>
     <row r="190" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B190" s="6">
-        <v>43343</v>
+        <v>43496</v>
       </c>
       <c r="C190" s="7">
-        <v>632296.01</v>
+        <v>528741.2</v>
       </c>
       <c r="D190" s="7">
-        <v>156116</v>
+        <v>107391.55</v>
       </c>
       <c r="E190" s="8">
-        <v>6.4396</v>
+        <v>6.5444</v>
       </c>
       <c r="F190" s="8">
-        <v>10.4006</v>
+        <v>12.6231</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B191" s="6">
-        <v>43327</v>
+        <v>43480</v>
       </c>
       <c r="C191" s="9">
-        <v>597839.31</v>
+        <v>554022.45</v>
       </c>
       <c r="D191" s="9">
-        <v>147848.75</v>
+        <v>100992.3</v>
       </c>
       <c r="E191" s="10">
-        <v>6.5298</v>
+        <v>6.6592</v>
       </c>
       <c r="F191" s="10">
-        <v>15.7923</v>
+        <v>10.9448</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B192" s="6">
-        <v>43312</v>
+        <v>43465</v>
       </c>
       <c r="C192" s="7">
-        <v>639529.66</v>
+        <v>498728.65</v>
       </c>
       <c r="D192" s="7">
-        <v>167712.25</v>
+        <v>95777.1</v>
       </c>
       <c r="E192" s="8">
-        <v>6.1904</v>
+        <v>6.7834</v>
       </c>
       <c r="F192" s="8">
-        <v>12.4726</v>
+        <v>10.2932</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B193" s="6">
-        <v>43296</v>
+        <v>43449</v>
       </c>
       <c r="C193" s="9">
-        <v>563088.86</v>
+        <v>546077.75</v>
       </c>
       <c r="D193" s="9">
-        <v>99548.8</v>
+        <v>103648.9</v>
       </c>
       <c r="E193" s="10">
-        <v>6.0329</v>
+        <v>6.5107</v>
       </c>
       <c r="F193" s="10">
-        <v>10.7065</v>
+        <v>11.1794</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B194" s="6">
-        <v>43281</v>
+        <v>43434</v>
       </c>
       <c r="C194" s="7">
-        <v>491833.06</v>
+        <v>560613.81</v>
       </c>
       <c r="D194" s="7">
-        <v>126726.8</v>
+        <v>130058.7</v>
       </c>
       <c r="E194" s="8">
-        <v>6.1633</v>
+        <v>6.6326</v>
       </c>
       <c r="F194" s="8">
-        <v>11.1862</v>
+        <v>11.0906</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B195" s="6">
-        <v>43266</v>
+        <v>43419</v>
       </c>
       <c r="C195" s="9">
-        <v>507614.46</v>
+        <v>584716.61</v>
       </c>
       <c r="D195" s="9">
-        <v>134164.5</v>
+        <v>106623.3</v>
       </c>
       <c r="E195" s="10">
-        <v>6.2522</v>
+        <v>6.6899</v>
       </c>
       <c r="F195" s="10">
-        <v>15.8608</v>
+        <v>11.7341</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B196" s="6">
-        <v>43251</v>
+        <v>43404</v>
       </c>
       <c r="C196" s="7">
-        <v>466886.96</v>
+        <v>587688.66</v>
       </c>
       <c r="D196" s="7">
-        <v>85015</v>
+        <v>94931.15</v>
       </c>
       <c r="E196" s="8">
-        <v>6.89</v>
+        <v>6.8656</v>
       </c>
       <c r="F196" s="8">
-        <v>9.84</v>
+        <v>10.3806</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B197" s="6">
-        <v>43235</v>
+        <v>43388</v>
       </c>
       <c r="C197" s="9">
-        <v>477697.46</v>
+        <v>594490.16</v>
       </c>
       <c r="D197" s="9">
-        <v>87439.25</v>
+        <v>79913.95</v>
       </c>
       <c r="E197" s="10">
-        <v>6.61</v>
+        <v>6.7238</v>
       </c>
       <c r="F197" s="10">
-        <v>9.55</v>
+        <v>17.4909</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B198" s="6">
-        <v>43220</v>
+        <v>43373</v>
       </c>
       <c r="C198" s="7">
-        <v>447691.41</v>
+        <v>556198.16</v>
       </c>
       <c r="D198" s="7">
-        <v>56773.65</v>
+        <v>112520.4</v>
       </c>
       <c r="E198" s="8">
-        <v>6.35</v>
+        <v>6.8377</v>
       </c>
       <c r="F198" s="8">
-        <v>12.31</v>
+        <v>11.1828</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B199" s="6">
-        <v>43205</v>
+        <v>43358</v>
       </c>
       <c r="C199" s="9">
-        <v>433183.01</v>
+        <v>640808.71</v>
       </c>
       <c r="D199" s="9">
-        <v>72990.2</v>
+        <v>111261.7</v>
       </c>
       <c r="E199" s="10">
-        <v>6.04</v>
+        <v>6.5644</v>
       </c>
       <c r="F199" s="10">
-        <v>11.88</v>
+        <v>15.7923</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B200" s="6">
-        <v>43190</v>
+        <v>43343</v>
       </c>
       <c r="C200" s="7">
-        <v>372577.41</v>
+        <v>632296.01</v>
       </c>
       <c r="D200" s="7">
-        <v>99915.4</v>
+        <v>156116</v>
       </c>
       <c r="E200" s="8">
-        <v>6.49</v>
+        <v>6.4396</v>
       </c>
       <c r="F200" s="8">
-        <v>14</v>
+        <v>10.4006</v>
       </c>
     </row>
     <row r="201" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B201" s="6">
-        <v>43174</v>
+        <v>43327</v>
       </c>
       <c r="C201" s="9">
-        <v>460495.96</v>
+        <v>597839.31</v>
       </c>
       <c r="D201" s="9">
-        <v>115454.25</v>
+        <v>147848.75</v>
       </c>
       <c r="E201" s="10">
-        <v>6.32</v>
+        <v>6.5298</v>
       </c>
       <c r="F201" s="10">
-        <v>11.88</v>
+        <v>15.7923</v>
       </c>
     </row>
     <row r="202" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B202" s="6">
-        <v>43159</v>
+        <v>43312</v>
       </c>
       <c r="C202" s="7">
-        <v>455047.21</v>
+        <v>639529.66</v>
       </c>
       <c r="D202" s="7">
-        <v>72383.8</v>
+        <v>167712.25</v>
       </c>
       <c r="E202" s="8">
-        <v>6.22</v>
+        <v>6.1904</v>
       </c>
       <c r="F202" s="8">
-        <v>10.6</v>
+        <v>12.4726</v>
       </c>
     </row>
     <row r="203" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B203" s="6">
-        <v>43146</v>
+        <v>43296</v>
       </c>
       <c r="C203" s="9">
-        <v>488630.91</v>
+        <v>563088.86</v>
       </c>
       <c r="D203" s="9">
-        <v>103773.6</v>
+        <v>99548.8</v>
       </c>
       <c r="E203" s="10">
-        <v>6.07</v>
+        <v>6.0329</v>
       </c>
       <c r="F203" s="10">
-        <v>11.81</v>
+        <v>10.7065</v>
       </c>
     </row>
     <row r="204" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B204" s="6">
-        <v>43131</v>
+        <v>43281</v>
       </c>
       <c r="C204" s="7">
-        <v>457498.66</v>
+        <v>491833.06</v>
       </c>
       <c r="D204" s="7">
-        <v>132021.65</v>
+        <v>126726.8</v>
       </c>
       <c r="E204" s="8">
-        <v>6.27</v>
+        <v>6.1633</v>
       </c>
       <c r="F204" s="8">
-        <v>11.88</v>
+        <v>11.1862</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B205" s="6">
-        <v>43115</v>
+        <v>43266</v>
       </c>
       <c r="C205" s="9">
-        <v>469648.71</v>
+        <v>507614.46</v>
       </c>
       <c r="D205" s="9">
-        <v>91320.5</v>
+        <v>134164.5</v>
       </c>
       <c r="E205" s="10">
-        <v>5.48</v>
+        <v>6.2522</v>
       </c>
       <c r="F205" s="10">
-        <v>9.65</v>
+        <v>15.8608</v>
       </c>
     </row>
     <row r="206" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B206" s="6">
-        <v>43100</v>
+        <v>43251</v>
       </c>
       <c r="C206" s="7">
-        <v>409053.31</v>
+        <v>466886.96</v>
       </c>
       <c r="D206" s="7">
-        <v>91603.6</v>
+        <v>85015</v>
       </c>
       <c r="E206" s="8">
-        <v>6.22</v>
+        <v>6.89</v>
       </c>
       <c r="F206" s="8">
-        <v>10.76</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="207" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B207" s="6">
-        <v>43084</v>
+        <v>43235</v>
       </c>
       <c r="C207" s="9">
-        <v>481528.71</v>
+        <v>477697.46</v>
       </c>
       <c r="D207" s="9">
-        <v>96187.96</v>
+        <v>87439.25</v>
       </c>
       <c r="E207" s="10">
-        <v>5.98</v>
+        <v>6.61</v>
       </c>
       <c r="F207" s="10">
-        <v>11.19</v>
+        <v>9.55</v>
       </c>
     </row>
     <row r="208" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B208" s="6">
-        <v>43069</v>
+        <v>43220</v>
       </c>
       <c r="C208" s="7">
-        <v>473679.8</v>
+        <v>447691.41</v>
       </c>
       <c r="D208" s="7">
-        <v>96022.9</v>
+        <v>56773.65</v>
       </c>
       <c r="E208" s="8">
-        <v>6.01</v>
+        <v>6.35</v>
       </c>
       <c r="F208" s="8">
-        <v>37.73</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="209" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B209" s="6">
-        <v>43054</v>
+        <v>43205</v>
       </c>
       <c r="C209" s="9">
-        <v>481581.9</v>
+        <v>433183.01</v>
       </c>
       <c r="D209" s="9">
-        <v>103409.5</v>
+        <v>72990.2</v>
       </c>
       <c r="E209" s="10">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="F209" s="10">
-        <v>11.26</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="210" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B210" s="6">
-        <v>43039</v>
+        <v>43190</v>
       </c>
       <c r="C210" s="7">
-        <v>489231.8</v>
+        <v>372577.41</v>
       </c>
       <c r="D210" s="7">
-        <v>135588.45</v>
+        <v>99915.4</v>
       </c>
       <c r="E210" s="8">
-        <v>6.06</v>
+        <v>6.49</v>
       </c>
       <c r="F210" s="8">
-        <v>11.23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B211" s="6">
-        <v>43023</v>
+        <v>43174</v>
       </c>
       <c r="C211" s="9">
-        <v>479675.75</v>
+        <v>460495.96</v>
       </c>
       <c r="D211" s="9">
-        <v>106985.1</v>
+        <v>115454.25</v>
       </c>
       <c r="E211" s="10">
-        <v>5.98</v>
+        <v>6.32</v>
       </c>
       <c r="F211" s="10">
-        <v>11.79</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B212" s="6">
-        <v>43008</v>
+        <v>43159</v>
       </c>
       <c r="C212" s="7">
-        <v>393214.35</v>
+        <v>455047.21</v>
       </c>
       <c r="D212" s="7">
-        <v>116294.1</v>
+        <v>72383.8</v>
       </c>
       <c r="E212" s="8">
-        <v>5.89</v>
+        <v>6.22</v>
       </c>
       <c r="F212" s="8">
-        <v>11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B213" s="6">
-        <v>42993</v>
+        <v>43146</v>
       </c>
       <c r="C213" s="9">
-        <v>442386.25</v>
+        <v>488630.91</v>
       </c>
       <c r="D213" s="9">
-        <v>125068.65</v>
+        <v>103773.6</v>
       </c>
       <c r="E213" s="10">
-        <v>5.59</v>
+        <v>6.07</v>
       </c>
       <c r="F213" s="10">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B214" s="6">
-        <v>42978</v>
+        <v>43131</v>
       </c>
       <c r="C214" s="7">
-        <v>369579.3</v>
+        <v>457498.66</v>
       </c>
       <c r="D214" s="7">
-        <v>99649</v>
+        <v>132021.65</v>
       </c>
       <c r="E214" s="8">
-        <v>6.05</v>
+        <v>6.27</v>
       </c>
       <c r="F214" s="8">
-        <v>11.25</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B215" s="6">
-        <v>42962</v>
+        <v>43115</v>
       </c>
       <c r="C215" s="9">
-        <v>359502.8</v>
+        <v>469648.71</v>
       </c>
       <c r="D215" s="9">
-        <v>119593.2</v>
+        <v>91320.5</v>
       </c>
       <c r="E215" s="10">
-        <v>6.1</v>
+        <v>5.48</v>
       </c>
       <c r="F215" s="10">
-        <v>13.92</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="216" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B216" s="6">
-        <v>42947</v>
+        <v>43100</v>
       </c>
       <c r="C216" s="7">
-        <v>325524.6</v>
+        <v>409053.31</v>
       </c>
       <c r="D216" s="7">
-        <v>32936.85</v>
+        <v>91603.6</v>
       </c>
       <c r="E216" s="8">
-        <v>6.11</v>
+        <v>6.22</v>
       </c>
       <c r="F216" s="8">
-        <v>11.96</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="217" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B217" s="6">
-        <v>42931</v>
+        <v>43084</v>
       </c>
       <c r="C217" s="9">
-        <v>358397.15</v>
+        <v>481528.71</v>
       </c>
       <c r="D217" s="9">
-        <v>84592</v>
+        <v>96187.96</v>
       </c>
       <c r="E217" s="10">
-        <v>6.02</v>
+        <v>5.98</v>
       </c>
       <c r="F217" s="10">
-        <v>11.97</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="218" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B218" s="6">
-        <v>42916</v>
+        <v>43069</v>
       </c>
       <c r="C218" s="7">
-        <v>329415.75</v>
+        <v>473679.8</v>
       </c>
       <c r="D218" s="7">
-        <v>97242</v>
+        <v>96022.9</v>
       </c>
       <c r="E218" s="8">
-        <v>6.23</v>
+        <v>6.01</v>
       </c>
       <c r="F218" s="8">
-        <v>11.95</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B219" s="6">
-        <v>42901</v>
+        <v>43054</v>
       </c>
       <c r="C219" s="9">
-        <v>388518.85</v>
+        <v>481581.9</v>
       </c>
       <c r="D219" s="9">
-        <v>72564</v>
+        <v>103409.5</v>
       </c>
       <c r="E219" s="10">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="F219" s="10">
-        <v>11.97</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="220" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B220" s="6">
-        <v>42886</v>
+        <v>43039</v>
       </c>
       <c r="C220" s="7">
-        <v>391326.85</v>
+        <v>489231.8</v>
       </c>
       <c r="D220" s="7">
-        <v>75756.6</v>
+        <v>135588.45</v>
       </c>
       <c r="E220" s="8">
-        <v>6.2</v>
+        <v>6.06</v>
       </c>
       <c r="F220" s="8">
-        <v>11.94</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="221" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B221" s="6">
-        <v>42870</v>
+        <v>43023</v>
       </c>
       <c r="C221" s="9">
-        <v>467221.55</v>
+        <v>479675.75</v>
       </c>
       <c r="D221" s="9">
-        <v>94181</v>
+        <v>106985.1</v>
       </c>
       <c r="E221" s="10">
-        <v>6.16</v>
+        <v>5.98</v>
       </c>
       <c r="F221" s="10">
-        <v>11.95</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B222" s="6">
-        <v>42855</v>
+        <v>43008</v>
       </c>
       <c r="C222" s="7">
-        <v>439982.55</v>
+        <v>393214.35</v>
       </c>
       <c r="D222" s="7">
-        <v>65523</v>
+        <v>116294.1</v>
       </c>
       <c r="E222" s="8">
-        <v>5.99</v>
+        <v>5.89</v>
       </c>
       <c r="F222" s="8">
-        <v>11.97</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B223" s="6">
-        <v>42840</v>
+        <v>42993</v>
       </c>
       <c r="C223" s="9">
-        <v>436739.7</v>
+        <v>442386.25</v>
       </c>
       <c r="D223" s="9">
-        <v>64479.6</v>
+        <v>125068.65</v>
       </c>
       <c r="E223" s="10">
-        <v>5.9</v>
+        <v>5.59</v>
       </c>
       <c r="F223" s="10">
-        <v>11.97</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B224" s="6">
-        <v>42825</v>
+        <v>42978</v>
       </c>
       <c r="C224" s="7">
-        <v>397965.25</v>
+        <v>369579.3</v>
       </c>
       <c r="D224" s="7">
-        <v>109409.15</v>
+        <v>99649</v>
       </c>
       <c r="E224" s="8">
-        <v>5.99</v>
+        <v>6.05</v>
       </c>
       <c r="F224" s="8">
-        <v>13.33</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B225" s="6">
-        <v>42809</v>
+        <v>42962</v>
       </c>
       <c r="C225" s="9">
-        <v>459050.25</v>
+        <v>359502.8</v>
       </c>
       <c r="D225" s="9">
-        <v>150024.5</v>
+        <v>119593.2</v>
       </c>
       <c r="E225" s="10">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="F225" s="10">
-        <v>14.92</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B226" s="6">
-        <v>42794</v>
+        <v>42947</v>
       </c>
       <c r="C226" s="7">
-        <v>372671.25</v>
+        <v>325524.6</v>
       </c>
       <c r="D226" s="7">
-        <v>77225.3</v>
+        <v>32936.85</v>
       </c>
       <c r="E226" s="8">
-        <v>6.08</v>
+        <v>6.11</v>
       </c>
       <c r="F226" s="8">
-        <v>14.19</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="227" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B227" s="6">
-        <v>42781</v>
+        <v>42931</v>
       </c>
       <c r="C227" s="9">
-        <v>402032.7</v>
+        <v>358397.15</v>
       </c>
       <c r="D227" s="9">
-        <v>104433.5</v>
+        <v>84592</v>
       </c>
       <c r="E227" s="10">
-        <v>6.03</v>
+        <v>6.02</v>
       </c>
       <c r="F227" s="10">
-        <v>14.21</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="228" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B228" s="6">
-        <v>42766</v>
+        <v>42916</v>
       </c>
       <c r="C228" s="7">
-        <v>381371.95</v>
+        <v>329415.75</v>
       </c>
       <c r="D228" s="7">
-        <v>50462.25</v>
+        <v>97242</v>
       </c>
       <c r="E228" s="8">
-        <v>6.19</v>
+        <v>6.23</v>
       </c>
       <c r="F228" s="8">
-        <v>14.21</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B229" s="6">
-        <v>42750</v>
+        <v>42901</v>
       </c>
       <c r="C229" s="9">
-        <v>406587.95</v>
+        <v>388518.85</v>
       </c>
       <c r="D229" s="9">
-        <v>58292.45</v>
+        <v>72564</v>
       </c>
       <c r="E229" s="10">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="F229" s="10">
-        <v>14.19</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="230" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B230" s="6">
-        <v>42735</v>
+        <v>42886</v>
       </c>
       <c r="C230" s="7">
-        <v>361804</v>
+        <v>391326.85</v>
       </c>
       <c r="D230" s="7">
-        <v>90688.9</v>
+        <v>75756.6</v>
       </c>
       <c r="E230" s="8">
-        <v>6.02</v>
+        <v>6.2</v>
       </c>
       <c r="F230" s="8">
-        <v>12.66</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="231" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B231" s="6">
-        <v>42719</v>
+        <v>42870</v>
       </c>
       <c r="C231" s="9">
-        <v>397887.45</v>
+        <v>467221.55</v>
       </c>
       <c r="D231" s="9">
-        <v>77409.95</v>
+        <v>94181</v>
       </c>
       <c r="E231" s="10">
-        <v>5.86</v>
+        <v>6.16</v>
       </c>
       <c r="F231" s="10">
-        <v>13.95</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="232" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B232" s="6">
-        <v>42704</v>
+        <v>42855</v>
       </c>
       <c r="C232" s="7">
-        <v>385876</v>
+        <v>439982.55</v>
       </c>
       <c r="D232" s="7">
-        <v>81407</v>
+        <v>65523</v>
       </c>
       <c r="E232" s="8">
-        <v>5.68</v>
+        <v>5.99</v>
       </c>
       <c r="F232" s="8">
-        <v>13.94</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="233" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B233" s="6">
-        <v>42689</v>
+        <v>42840</v>
       </c>
       <c r="C233" s="9">
-        <v>409848.5</v>
+        <v>436739.7</v>
       </c>
       <c r="D233" s="9">
-        <v>83559.6</v>
+        <v>64479.6</v>
       </c>
       <c r="E233" s="10">
-        <v>6.07</v>
+        <v>5.9</v>
       </c>
       <c r="F233" s="10">
-        <v>12.62</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="234" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B234" s="6">
-        <v>42674</v>
+        <v>42825</v>
       </c>
       <c r="C234" s="7">
-        <v>396117.5</v>
+        <v>397965.25</v>
       </c>
       <c r="D234" s="7">
-        <v>53585.85</v>
+        <v>109409.15</v>
       </c>
       <c r="E234" s="8">
-        <v>6.31</v>
+        <v>5.99</v>
       </c>
       <c r="F234" s="8">
-        <v>11.97</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="235" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B235" s="6">
-        <v>42658</v>
+        <v>42809</v>
       </c>
       <c r="C235" s="9">
-        <v>411595</v>
+        <v>459050.25</v>
       </c>
       <c r="D235" s="9">
-        <v>85365</v>
+        <v>150024.5</v>
       </c>
       <c r="E235" s="10">
-        <v>6.28</v>
+        <v>5.9</v>
       </c>
       <c r="F235" s="10">
-        <v>13.84</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="236" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B236" s="6">
-        <v>42643</v>
+        <v>42794</v>
       </c>
       <c r="C236" s="7">
-        <v>348761</v>
+        <v>372671.25</v>
       </c>
       <c r="D236" s="7">
-        <v>99339</v>
+        <v>77225.3</v>
       </c>
       <c r="E236" s="8">
-        <v>6.32</v>
+        <v>6.08</v>
       </c>
       <c r="F236" s="8">
-        <v>13.94</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="237" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B237" s="6">
-        <v>42628</v>
+        <v>42781</v>
       </c>
       <c r="C237" s="9">
-        <v>397577</v>
+        <v>402032.7</v>
       </c>
       <c r="D237" s="9">
-        <v>85613</v>
+        <v>104433.5</v>
       </c>
       <c r="E237" s="10">
-        <v>6.28</v>
+        <v>6.03</v>
       </c>
       <c r="F237" s="10">
-        <v>12.61</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="238" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B238" s="6">
-        <v>42613</v>
+        <v>42766</v>
       </c>
       <c r="C238" s="7">
-        <v>388311</v>
+        <v>381371.95</v>
       </c>
       <c r="D238" s="7">
-        <v>114988</v>
+        <v>50462.25</v>
       </c>
       <c r="E238" s="8">
-        <v>6.51</v>
+        <v>6.19</v>
       </c>
       <c r="F238" s="8">
-        <v>13.92</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="239" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B239" s="6">
-        <v>42597</v>
+        <v>42750</v>
       </c>
       <c r="C239" s="9">
-        <v>386189.6</v>
+        <v>406587.95</v>
       </c>
       <c r="D239" s="9">
-        <v>81444.9</v>
+        <v>58292.45</v>
       </c>
       <c r="E239" s="10">
-        <v>6.44</v>
+        <v>6.15</v>
       </c>
       <c r="F239" s="10">
-        <v>12.78</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="240" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B240" s="6">
-        <v>42582</v>
+        <v>42735</v>
       </c>
       <c r="C240" s="7">
-        <v>381190</v>
+        <v>361804</v>
       </c>
       <c r="D240" s="7">
-        <v>56626</v>
+        <v>90688.9</v>
       </c>
       <c r="E240" s="8">
-        <v>6.42</v>
+        <v>6.02</v>
       </c>
       <c r="F240" s="8">
-        <v>13.84</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="241" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B241" s="6">
-        <v>42566</v>
+        <v>42719</v>
       </c>
       <c r="C241" s="9">
-        <v>403112.2</v>
+        <v>397887.45</v>
       </c>
       <c r="D241" s="9">
-        <v>93210.1</v>
+        <v>77409.95</v>
       </c>
       <c r="E241" s="10">
-        <v>6.42</v>
+        <v>5.86</v>
       </c>
       <c r="F241" s="10">
-        <v>11.95</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="242" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B242" s="6">
-        <v>42551</v>
+        <v>42704</v>
       </c>
       <c r="C242" s="7">
-        <v>337642</v>
+        <v>385876</v>
       </c>
       <c r="D242" s="7">
-        <v>95943</v>
+        <v>81407</v>
       </c>
       <c r="E242" s="8">
-        <v>6.54</v>
+        <v>5.68</v>
       </c>
       <c r="F242" s="8">
-        <v>13.84</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="243" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B243" s="6">
-        <v>42536</v>
+        <v>42689</v>
       </c>
       <c r="C243" s="9">
-        <v>383171</v>
+        <v>409848.5</v>
       </c>
       <c r="D243" s="9">
-        <v>89944</v>
+        <v>83559.6</v>
       </c>
       <c r="E243" s="10">
-        <v>6.69</v>
+        <v>6.07</v>
       </c>
       <c r="F243" s="10">
-        <v>13.3</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="244" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B244" s="6">
-        <v>42521</v>
+        <v>42674</v>
       </c>
       <c r="C244" s="7">
-        <v>363204.8</v>
+        <v>396117.5</v>
       </c>
       <c r="D244" s="7">
-        <v>91114.1</v>
+        <v>53585.85</v>
       </c>
       <c r="E244" s="8">
-        <v>6.77</v>
+        <v>6.31</v>
       </c>
       <c r="F244" s="8">
-        <v>12.75</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="245" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B245" s="6">
-        <v>42505</v>
+        <v>42658</v>
       </c>
       <c r="C245" s="9">
-        <v>377474.8</v>
+        <v>411595</v>
       </c>
       <c r="D245" s="9">
-        <v>103293.6</v>
+        <v>85365</v>
       </c>
       <c r="E245" s="10">
-        <v>7.08</v>
+        <v>6.28</v>
       </c>
       <c r="F245" s="10">
-        <v>13.29</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="246" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B246" s="6">
-        <v>42490</v>
+        <v>42643</v>
       </c>
       <c r="C246" s="7">
-        <v>335679</v>
+        <v>348761</v>
       </c>
       <c r="D246" s="7">
-        <v>56459</v>
+        <v>99339</v>
       </c>
       <c r="E246" s="8">
-        <v>6.88</v>
+        <v>6.32</v>
       </c>
       <c r="F246" s="8">
-        <v>13.23</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="247" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B247" s="6">
-        <v>42475</v>
+        <v>42628</v>
       </c>
       <c r="C247" s="9">
-        <v>340617</v>
+        <v>397577</v>
       </c>
       <c r="D247" s="9">
-        <v>91806</v>
+        <v>85613</v>
       </c>
       <c r="E247" s="10">
-        <v>6.84</v>
+        <v>6.28</v>
       </c>
       <c r="F247" s="10">
-        <v>11.22</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="248" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B248" s="6">
-        <v>42460</v>
+        <v>42613</v>
       </c>
       <c r="C248" s="7">
-        <v>260244</v>
+        <v>388311</v>
       </c>
       <c r="D248" s="7">
-        <v>67364</v>
+        <v>114988</v>
       </c>
       <c r="E248" s="8">
-        <v>7.35</v>
+        <v>6.51</v>
       </c>
       <c r="F248" s="8">
-        <v>13.14</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="249" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B249" s="6">
-        <v>42444</v>
+        <v>42597</v>
       </c>
       <c r="C249" s="9">
-        <v>345590</v>
+        <v>386189.6</v>
       </c>
       <c r="D249" s="9">
-        <v>82656</v>
+        <v>81444.9</v>
       </c>
       <c r="E249" s="10">
-        <v>7.27</v>
+        <v>6.44</v>
       </c>
       <c r="F249" s="10">
-        <v>13.09</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="250" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B250" s="6">
-        <v>42429</v>
+        <v>42582</v>
       </c>
       <c r="C250" s="7">
-        <v>355783</v>
+        <v>381190</v>
       </c>
       <c r="D250" s="7">
-        <v>67177</v>
+        <v>56626</v>
       </c>
       <c r="E250" s="8">
-        <v>7.33</v>
+        <v>6.42</v>
       </c>
       <c r="F250" s="8">
-        <v>12</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="251" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B251" s="6">
-        <v>42415</v>
+        <v>42566</v>
       </c>
       <c r="C251" s="9">
-        <v>387605</v>
+        <v>403112.2</v>
       </c>
       <c r="D251" s="9">
-        <v>91182</v>
+        <v>93210.1</v>
       </c>
       <c r="E251" s="10">
-        <v>7.14</v>
+        <v>6.42</v>
       </c>
       <c r="F251" s="10">
-        <v>11.31</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B252" s="6">
-        <v>42400</v>
+        <v>42551</v>
       </c>
       <c r="C252" s="7">
-        <v>355380</v>
+        <v>337642</v>
       </c>
       <c r="D252" s="7">
-        <v>51390</v>
+        <v>95943</v>
       </c>
       <c r="E252" s="8">
-        <v>7.3</v>
+        <v>6.54</v>
       </c>
       <c r="F252" s="8">
-        <v>11.18</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B253" s="6">
-        <v>42384</v>
+        <v>42536</v>
       </c>
       <c r="C253" s="9">
-        <v>364372</v>
+        <v>383171</v>
       </c>
       <c r="D253" s="9">
-        <v>71832</v>
+        <v>89944</v>
       </c>
       <c r="E253" s="10">
-        <v>6.89</v>
+        <v>6.69</v>
       </c>
       <c r="F253" s="10">
-        <v>11.42</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="254" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B254" s="6">
-        <v>42369</v>
+        <v>42521</v>
       </c>
       <c r="C254" s="7">
-        <v>308509</v>
+        <v>363204.8</v>
       </c>
       <c r="D254" s="7">
-        <v>66591</v>
+        <v>91114.1</v>
       </c>
       <c r="E254" s="8">
-        <v>7.23</v>
+        <v>6.77</v>
       </c>
       <c r="F254" s="8">
-        <v>11.79</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B255" s="6">
-        <v>42353</v>
+        <v>42505</v>
       </c>
       <c r="C255" s="9">
-        <v>380280</v>
+        <v>377474.8</v>
       </c>
       <c r="D255" s="9">
-        <v>115129</v>
+        <v>103293.6</v>
       </c>
       <c r="E255" s="10">
         <v>7.08</v>
       </c>
       <c r="F255" s="10">
-        <v>12.13</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="256" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B256" s="6">
-        <v>42338</v>
+        <v>42490</v>
       </c>
       <c r="C256" s="7">
-        <v>327379</v>
+        <v>335679</v>
       </c>
       <c r="D256" s="7">
-        <v>62470</v>
+        <v>56459</v>
       </c>
       <c r="E256" s="8">
-        <v>7.07</v>
+        <v>6.88</v>
       </c>
       <c r="F256" s="8">
-        <v>11.66</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="257" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B257" s="6">
-        <v>42323</v>
+        <v>42475</v>
       </c>
       <c r="C257" s="9">
-        <v>344360</v>
+        <v>340617</v>
       </c>
       <c r="D257" s="9">
-        <v>70153</v>
+        <v>91806</v>
       </c>
       <c r="E257" s="10">
-        <v>6.52</v>
+        <v>6.84</v>
       </c>
       <c r="F257" s="10">
-        <v>11.18</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="258" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B258" s="6">
-        <v>42308</v>
+        <v>42460</v>
       </c>
       <c r="C258" s="7">
-        <v>323101</v>
+        <v>260244</v>
       </c>
       <c r="D258" s="7">
-        <v>63483</v>
+        <v>67364</v>
       </c>
       <c r="E258" s="8">
-        <v>7.02</v>
+        <v>7.35</v>
       </c>
       <c r="F258" s="8">
-        <v>11.55</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="259" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B259" s="6">
-        <v>42292</v>
+        <v>42444</v>
       </c>
       <c r="C259" s="9">
-        <v>322635</v>
+        <v>345590</v>
       </c>
       <c r="D259" s="9">
-        <v>76246</v>
+        <v>82656</v>
       </c>
       <c r="E259" s="10">
-        <v>6.99</v>
+        <v>7.27</v>
       </c>
       <c r="F259" s="10">
-        <v>11.54</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="260" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B260" s="6">
-        <v>42277</v>
+        <v>42429</v>
       </c>
       <c r="C260" s="7">
-        <v>268423</v>
+        <v>355783</v>
       </c>
       <c r="D260" s="7">
-        <v>43153</v>
+        <v>67177</v>
       </c>
       <c r="E260" s="8">
-        <v>7.29</v>
+        <v>7.33</v>
       </c>
       <c r="F260" s="8">
-        <v>11.53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B261" s="6">
-        <v>42262</v>
+        <v>42415</v>
       </c>
       <c r="C261" s="9">
-        <v>325595</v>
+        <v>387605</v>
       </c>
       <c r="D261" s="9">
-        <v>63842</v>
+        <v>91182</v>
       </c>
       <c r="E261" s="10">
-        <v>7.19</v>
+        <v>7.14</v>
       </c>
       <c r="F261" s="10">
-        <v>13.06</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="262" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B262" s="6">
-        <v>42247</v>
+        <v>42400</v>
       </c>
       <c r="C262" s="7">
-        <v>309464</v>
+        <v>355380</v>
       </c>
       <c r="D262" s="7">
-        <v>59946</v>
+        <v>51390</v>
       </c>
       <c r="E262" s="8">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="F262" s="8">
-        <v>12.29</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="263" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B263" s="6">
-        <v>42231</v>
+        <v>42384</v>
       </c>
       <c r="C263" s="9">
-        <v>323258</v>
+        <v>364372</v>
       </c>
       <c r="D263" s="9">
-        <v>67881</v>
+        <v>71832</v>
       </c>
       <c r="E263" s="10">
-        <v>7.09</v>
+        <v>6.89</v>
       </c>
       <c r="F263" s="10">
-        <v>12.24</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="264" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B264" s="6">
-        <v>42216</v>
+        <v>42369</v>
       </c>
       <c r="C264" s="7">
-        <v>314939</v>
+        <v>308509</v>
       </c>
       <c r="D264" s="7">
-        <v>57188</v>
+        <v>66591</v>
       </c>
       <c r="E264" s="8">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="F264" s="8">
-        <v>11.76</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="265" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B265" s="6">
-        <v>42200</v>
+        <v>42353</v>
       </c>
       <c r="C265" s="9">
-        <v>318593</v>
+        <v>380280</v>
       </c>
       <c r="D265" s="9">
-        <v>61667</v>
+        <v>115129</v>
       </c>
       <c r="E265" s="10">
-        <v>7.45</v>
+        <v>7.08</v>
       </c>
       <c r="F265" s="10">
-        <v>11.52</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="266" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B266" s="6">
-        <v>42185</v>
+        <v>42338</v>
       </c>
       <c r="C266" s="7">
-        <v>270613</v>
+        <v>327379</v>
       </c>
       <c r="D266" s="7">
-        <v>59339</v>
+        <v>62470</v>
       </c>
       <c r="E266" s="8">
-        <v>7.39</v>
+        <v>7.07</v>
       </c>
       <c r="F266" s="8">
-        <v>11.56</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="267" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B267" s="6">
-        <v>42170</v>
+        <v>42323</v>
       </c>
       <c r="C267" s="9">
-        <v>312692</v>
+        <v>344360</v>
       </c>
       <c r="D267" s="9">
-        <v>71260</v>
+        <v>70153</v>
       </c>
       <c r="E267" s="10">
-        <v>7.07</v>
+        <v>6.52</v>
       </c>
       <c r="F267" s="10">
-        <v>13.06</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="268" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B268" s="6">
-        <v>42155</v>
+        <v>42308</v>
       </c>
       <c r="C268" s="7">
-        <v>298668</v>
+        <v>323101</v>
       </c>
       <c r="D268" s="7">
-        <v>68390.5</v>
+        <v>63483</v>
       </c>
       <c r="E268" s="8">
-        <v>7.79</v>
+        <v>7.02</v>
       </c>
       <c r="F268" s="8">
-        <v>12.11</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="269" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B269" s="6">
-        <v>42139</v>
+        <v>42292</v>
       </c>
       <c r="C269" s="9">
-        <v>290512</v>
+        <v>322635</v>
       </c>
       <c r="D269" s="9">
-        <v>54051</v>
+        <v>76246</v>
       </c>
       <c r="E269" s="10">
-        <v>8</v>
+        <v>6.99</v>
       </c>
       <c r="F269" s="10">
-        <v>11.91</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B270" s="6">
-        <v>42124</v>
+        <v>42277</v>
       </c>
       <c r="C270" s="7">
-        <v>268272</v>
+        <v>268423</v>
       </c>
       <c r="D270" s="7">
-        <v>67893</v>
+        <v>43153</v>
       </c>
       <c r="E270" s="8">
-        <v>7.84</v>
+        <v>7.29</v>
       </c>
       <c r="F270" s="8">
-        <v>12.03</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="271" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B271" s="6">
-        <v>42109</v>
+        <v>42262</v>
       </c>
       <c r="C271" s="9">
-        <v>244318</v>
+        <v>325595</v>
       </c>
       <c r="D271" s="9">
-        <v>68479</v>
+        <v>63842</v>
       </c>
       <c r="E271" s="10">
-        <v>7.78</v>
+        <v>7.19</v>
       </c>
       <c r="F271" s="10">
-        <v>11.36</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="272" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B272" s="6">
-        <v>42094</v>
+        <v>42247</v>
       </c>
       <c r="C272" s="7">
-        <v>193268</v>
+        <v>309464</v>
       </c>
       <c r="D272" s="7">
-        <v>69425</v>
+        <v>59946</v>
       </c>
       <c r="E272" s="8">
-        <v>7.44</v>
+        <v>7.33</v>
       </c>
       <c r="F272" s="8">
-        <v>14.92</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="273" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B273" s="6">
-        <v>42078</v>
+        <v>42231</v>
       </c>
       <c r="C273" s="9">
-        <v>256115</v>
+        <v>323258</v>
       </c>
       <c r="D273" s="9">
-        <v>59652</v>
+        <v>67881</v>
       </c>
       <c r="E273" s="10">
-        <v>7.91</v>
+        <v>7.09</v>
       </c>
       <c r="F273" s="10">
-        <v>13.06</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="274" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B274" s="6">
-        <v>42063</v>
+        <v>42216</v>
       </c>
       <c r="C274" s="7">
-        <v>249351</v>
+        <v>314939</v>
       </c>
       <c r="D274" s="7">
-        <v>51780.15</v>
+        <v>57188</v>
       </c>
       <c r="E274" s="8">
-        <v>8.04</v>
+        <v>7.36</v>
       </c>
       <c r="F274" s="8">
-        <v>12.19</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="275" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B275" s="6">
-        <v>42050</v>
+        <v>42200</v>
       </c>
       <c r="C275" s="9">
-        <v>257485</v>
+        <v>318593</v>
       </c>
       <c r="D275" s="9">
-        <v>54443</v>
+        <v>61667</v>
       </c>
       <c r="E275" s="10">
-        <v>7.86</v>
+        <v>7.45</v>
       </c>
       <c r="F275" s="10">
-        <v>12.21</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="276" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B276" s="6">
-        <v>42035</v>
+        <v>42185</v>
       </c>
       <c r="C276" s="7">
-        <v>237612</v>
+        <v>270613</v>
       </c>
       <c r="D276" s="7">
-        <v>37341.35</v>
+        <v>59339</v>
       </c>
       <c r="E276" s="8">
-        <v>7.95</v>
+        <v>7.39</v>
       </c>
       <c r="F276" s="8">
-        <v>13.21</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="277" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B277" s="6">
-        <v>42019</v>
+        <v>42170</v>
       </c>
       <c r="C277" s="9">
-        <v>252871</v>
+        <v>312692</v>
       </c>
       <c r="D277" s="9">
-        <v>56531</v>
+        <v>71260</v>
       </c>
       <c r="E277" s="10">
-        <v>8.06</v>
+        <v>7.07</v>
       </c>
       <c r="F277" s="10">
-        <v>11.73</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="278" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B278" s="6">
-        <v>42004</v>
+        <v>42155</v>
       </c>
       <c r="C278" s="7">
-        <v>208248</v>
+        <v>298668</v>
       </c>
       <c r="D278" s="7">
-        <v>43642</v>
+        <v>68390.5</v>
       </c>
       <c r="E278" s="8">
-        <v>7.98</v>
+        <v>7.79</v>
       </c>
       <c r="F278" s="8">
-        <v>12.61</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="279" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B279" s="6">
-        <v>41988</v>
+        <v>42139</v>
       </c>
       <c r="C279" s="9">
-        <v>234233</v>
+        <v>290512</v>
       </c>
       <c r="D279" s="9">
-        <v>56210</v>
+        <v>54051</v>
       </c>
       <c r="E279" s="10">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="F279" s="10">
-        <v>11.58</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="280" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B280" s="6">
-        <v>41973</v>
+        <v>42124</v>
       </c>
       <c r="C280" s="7">
-        <v>225380</v>
+        <v>268272</v>
       </c>
       <c r="D280" s="7">
-        <v>47702</v>
+        <v>67893</v>
       </c>
       <c r="E280" s="8">
-        <v>8.05</v>
+        <v>7.84</v>
       </c>
       <c r="F280" s="8">
-        <v>12.48</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="281" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B281" s="6">
-        <v>41958</v>
+        <v>42109</v>
       </c>
       <c r="C281" s="9">
-        <v>228747</v>
+        <v>244318</v>
       </c>
       <c r="D281" s="9">
-        <v>36340</v>
+        <v>68479</v>
       </c>
       <c r="E281" s="10">
-        <v>8.13</v>
+        <v>7.78</v>
       </c>
       <c r="F281" s="10">
-        <v>11.76</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="282" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B282" s="6">
-        <v>41943</v>
+        <v>42094</v>
       </c>
       <c r="C282" s="7">
-        <v>218526</v>
+        <v>193268</v>
       </c>
       <c r="D282" s="7">
-        <v>34645</v>
+        <v>69425</v>
       </c>
       <c r="E282" s="8">
-        <v>7.55</v>
+        <v>7.44</v>
       </c>
       <c r="F282" s="8">
-        <v>11.75</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="283" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B283" s="6">
-        <v>41927</v>
+        <v>42078</v>
       </c>
       <c r="C283" s="9">
-        <v>224177</v>
+        <v>256115</v>
       </c>
       <c r="D283" s="9">
-        <v>50160</v>
+        <v>59652</v>
       </c>
       <c r="E283" s="10">
-        <v>8.34</v>
+        <v>7.91</v>
       </c>
       <c r="F283" s="10">
-        <v>11.62</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="284" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B284" s="6">
-        <v>41912</v>
+        <v>42063</v>
       </c>
       <c r="C284" s="7">
-        <v>184353</v>
+        <v>249351</v>
       </c>
       <c r="D284" s="7">
-        <v>51579</v>
+        <v>51780.15</v>
       </c>
       <c r="E284" s="8">
-        <v>8.44</v>
+        <v>8.04</v>
       </c>
       <c r="F284" s="8">
-        <v>12.6</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="285" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B285" s="6">
-        <v>41897</v>
+        <v>42050</v>
       </c>
       <c r="C285" s="9">
-        <v>232987</v>
+        <v>257485</v>
       </c>
       <c r="D285" s="9">
-        <v>68527</v>
+        <v>54443</v>
       </c>
       <c r="E285" s="10">
-        <v>8.26</v>
+        <v>7.86</v>
       </c>
       <c r="F285" s="10">
-        <v>12</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="286" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B286" s="6">
-        <v>41882</v>
+        <v>42035</v>
       </c>
       <c r="C286" s="7">
-        <v>211195</v>
+        <v>237612</v>
       </c>
       <c r="D286" s="7">
-        <v>35859</v>
+        <v>37341.35</v>
       </c>
       <c r="E286" s="8">
-        <v>8.26</v>
+        <v>7.95</v>
       </c>
       <c r="F286" s="8">
-        <v>12.62</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="287" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B287" s="6">
-        <v>41866</v>
+        <v>42019</v>
       </c>
       <c r="C287" s="9">
-        <v>218463</v>
+        <v>252871</v>
       </c>
       <c r="D287" s="9">
-        <v>47474</v>
+        <v>56531</v>
       </c>
       <c r="E287" s="10">
-        <v>7.36</v>
+        <v>8.06</v>
       </c>
       <c r="F287" s="10">
-        <v>11.96</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="288" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B288" s="6">
-        <v>41851</v>
+        <v>42004</v>
       </c>
       <c r="C288" s="7">
-        <v>201500</v>
+        <v>208248</v>
       </c>
       <c r="D288" s="7">
-        <v>39744</v>
+        <v>43642</v>
       </c>
       <c r="E288" s="8">
-        <v>8.12</v>
+        <v>7.98</v>
       </c>
       <c r="F288" s="8">
-        <v>11.77</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="289" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B289" s="6">
-        <v>41835</v>
+        <v>41988</v>
       </c>
       <c r="C289" s="9">
-        <v>202423</v>
+        <v>234233</v>
       </c>
       <c r="D289" s="9">
-        <v>46457</v>
+        <v>56210</v>
       </c>
       <c r="E289" s="10">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="F289" s="10">
-        <v>12.42</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="290" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B290" s="6">
-        <v>41820</v>
+        <v>41973</v>
       </c>
       <c r="C290" s="7">
-        <v>170570</v>
+        <v>225380</v>
       </c>
       <c r="D290" s="7">
-        <v>50460</v>
+        <v>47702</v>
       </c>
       <c r="E290" s="8">
-        <v>8.29</v>
+        <v>8.05</v>
       </c>
       <c r="F290" s="8">
-        <v>14.02</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="291" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B291" s="6">
-        <v>41805</v>
+        <v>41958</v>
       </c>
       <c r="C291" s="9">
-        <v>196922</v>
+        <v>228747</v>
       </c>
       <c r="D291" s="9">
-        <v>48518</v>
+        <v>36340</v>
       </c>
       <c r="E291" s="10">
-        <v>8.14</v>
+        <v>8.13</v>
       </c>
       <c r="F291" s="10">
-        <v>12.54</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="292" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B292" s="6">
-        <v>41790</v>
+        <v>41943</v>
       </c>
       <c r="C292" s="7">
-        <v>182419</v>
+        <v>218526</v>
       </c>
       <c r="D292" s="7">
-        <v>38696</v>
+        <v>34645</v>
       </c>
       <c r="E292" s="8">
-        <v>8.35</v>
+        <v>7.55</v>
       </c>
       <c r="F292" s="8">
-        <v>12.87</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="293" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B293" s="6">
-        <v>41774</v>
+        <v>41927</v>
       </c>
       <c r="C293" s="9">
-        <v>182592</v>
+        <v>224177</v>
       </c>
       <c r="D293" s="9">
-        <v>46273</v>
+        <v>50160</v>
       </c>
       <c r="E293" s="10">
-        <v>8.48</v>
+        <v>8.34</v>
       </c>
       <c r="F293" s="10">
-        <v>12.65</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="294" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B294" s="6">
-        <v>41759</v>
+        <v>41912</v>
       </c>
       <c r="C294" s="7">
-        <v>153812.3</v>
+        <v>184353</v>
       </c>
       <c r="D294" s="7">
-        <v>34908.3</v>
+        <v>51579</v>
       </c>
       <c r="E294" s="8">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="F294" s="8">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="295" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B295" s="6">
-        <v>41744</v>
+        <v>41897</v>
       </c>
       <c r="C295" s="9">
-        <v>142134</v>
+        <v>232987</v>
       </c>
       <c r="D295" s="9">
-        <v>43694</v>
+        <v>68527</v>
       </c>
       <c r="E295" s="10">
-        <v>8.44</v>
+        <v>8.26</v>
       </c>
       <c r="F295" s="10">
         <v>12</v>
@@ -5224,815 +5225,815 @@
     </row>
     <row r="296" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B296" s="6">
-        <v>41729</v>
+        <v>41882</v>
       </c>
       <c r="C296" s="7">
-        <v>106613.6</v>
+        <v>211195</v>
       </c>
       <c r="D296" s="7">
-        <v>25037</v>
+        <v>35859</v>
       </c>
       <c r="E296" s="8">
-        <v>8.64</v>
+        <v>8.26</v>
       </c>
       <c r="F296" s="8">
-        <v>12.61</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="297" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B297" s="6">
-        <v>41713</v>
+        <v>41866</v>
       </c>
       <c r="C297" s="9">
-        <v>165343</v>
+        <v>218463</v>
       </c>
       <c r="D297" s="9">
-        <v>41424</v>
+        <v>47474</v>
       </c>
       <c r="E297" s="10">
-        <v>7.96</v>
+        <v>7.36</v>
       </c>
       <c r="F297" s="10">
-        <v>14.18</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="298" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B298" s="6">
-        <v>41698</v>
+        <v>41851</v>
       </c>
       <c r="C298" s="7">
-        <v>164603</v>
+        <v>201500</v>
       </c>
       <c r="D298" s="7">
-        <v>29195</v>
+        <v>39744</v>
       </c>
       <c r="E298" s="8">
-        <v>7.84</v>
+        <v>8.12</v>
       </c>
       <c r="F298" s="8">
-        <v>13.06</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="299" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B299" s="6">
-        <v>41685</v>
+        <v>41835</v>
       </c>
       <c r="C299" s="9">
-        <v>176709</v>
+        <v>202423</v>
       </c>
       <c r="D299" s="9">
-        <v>35133</v>
+        <v>46457</v>
       </c>
       <c r="E299" s="10">
-        <v>8.33</v>
+        <v>8.16</v>
       </c>
       <c r="F299" s="10">
-        <v>12.7</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="300" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B300" s="6">
-        <v>41670</v>
+        <v>41820</v>
       </c>
       <c r="C300" s="7">
-        <v>164173</v>
+        <v>170570</v>
       </c>
       <c r="D300" s="7">
-        <v>29072</v>
+        <v>50460</v>
       </c>
       <c r="E300" s="8">
-        <v>7.99</v>
+        <v>8.29</v>
       </c>
       <c r="F300" s="8">
-        <v>12.5</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="301" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B301" s="6">
-        <v>41654</v>
+        <v>41805</v>
       </c>
       <c r="C301" s="9">
-        <v>172103.48</v>
+        <v>196922</v>
       </c>
       <c r="D301" s="9">
-        <v>39208.6</v>
+        <v>48518</v>
       </c>
       <c r="E301" s="10">
-        <v>8.33</v>
+        <v>8.14</v>
       </c>
       <c r="F301" s="10">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="302" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B302" s="6">
-        <v>41639</v>
+        <v>41790</v>
       </c>
       <c r="C302" s="7">
-        <v>140358</v>
+        <v>182419</v>
       </c>
       <c r="D302" s="7">
-        <v>29986</v>
+        <v>38696</v>
       </c>
       <c r="E302" s="8">
-        <v>8.38</v>
+        <v>8.35</v>
       </c>
       <c r="F302" s="8">
-        <v>12.63</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="303" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B303" s="6">
-        <v>41623</v>
+        <v>41774</v>
       </c>
       <c r="C303" s="9">
-        <v>187536</v>
+        <v>182592</v>
       </c>
       <c r="D303" s="9">
-        <v>43304</v>
+        <v>46273</v>
       </c>
       <c r="E303" s="10">
-        <v>8.05</v>
+        <v>8.48</v>
       </c>
       <c r="F303" s="10">
-        <v>12.7</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="304" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B304" s="6">
-        <v>41608</v>
+        <v>41759</v>
       </c>
       <c r="C304" s="7">
-        <v>175637</v>
+        <v>153812.3</v>
       </c>
       <c r="D304" s="7">
-        <v>32295</v>
+        <v>34908.3</v>
       </c>
       <c r="E304" s="8">
-        <v>8.74</v>
+        <v>8.58</v>
       </c>
       <c r="F304" s="8">
-        <v>12.46</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B305" s="6">
-        <v>41593</v>
+        <v>41744</v>
       </c>
       <c r="C305" s="9">
-        <v>172515</v>
+        <v>142134</v>
       </c>
       <c r="D305" s="9">
-        <v>30309</v>
+        <v>43694</v>
       </c>
       <c r="E305" s="10">
         <v>8.44</v>
       </c>
       <c r="F305" s="10">
-        <v>12.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B306" s="6">
-        <v>41578</v>
+        <v>41729</v>
       </c>
       <c r="C306" s="7">
-        <v>157449</v>
+        <v>106613.6</v>
       </c>
       <c r="D306" s="7">
-        <v>33724</v>
+        <v>25037</v>
       </c>
       <c r="E306" s="8">
-        <v>8.63</v>
+        <v>8.64</v>
       </c>
       <c r="F306" s="8">
-        <v>12.39</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B307" s="6">
-        <v>41562</v>
+        <v>41713</v>
       </c>
       <c r="C307" s="9">
-        <v>136312</v>
+        <v>165343</v>
       </c>
       <c r="D307" s="9">
-        <v>45270</v>
+        <v>41424</v>
       </c>
       <c r="E307" s="10">
-        <v>8.03</v>
+        <v>7.96</v>
       </c>
       <c r="F307" s="10">
-        <v>12.53</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="308" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B308" s="6">
-        <v>41547</v>
+        <v>41698</v>
       </c>
       <c r="C308" s="7">
-        <v>98638</v>
+        <v>164603</v>
       </c>
       <c r="D308" s="7">
-        <v>26778</v>
+        <v>29195</v>
       </c>
       <c r="E308" s="8">
-        <v>9.5</v>
+        <v>7.84</v>
       </c>
       <c r="F308" s="8">
-        <v>13.57</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="309" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B309" s="6">
-        <v>41532</v>
+        <v>41685</v>
       </c>
       <c r="C309" s="9">
-        <v>108187</v>
+        <v>176709</v>
       </c>
       <c r="D309" s="9">
-        <v>17027</v>
+        <v>35133</v>
       </c>
       <c r="E309" s="10">
-        <v>8.17</v>
+        <v>8.33</v>
       </c>
       <c r="F309" s="10">
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="310" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B310" s="6">
-        <v>41517</v>
+        <v>41670</v>
       </c>
       <c r="C310" s="7">
-        <v>118290</v>
+        <v>164173</v>
       </c>
       <c r="D310" s="7">
-        <v>9760</v>
+        <v>29072</v>
       </c>
       <c r="E310" s="8">
-        <v>9.5</v>
+        <v>7.99</v>
       </c>
       <c r="F310" s="8">
-        <v>14.31</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="311" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B311" s="6">
-        <v>41501</v>
+        <v>41654</v>
       </c>
       <c r="C311" s="9">
-        <v>136340</v>
+        <v>172103.48</v>
       </c>
       <c r="D311" s="9">
-        <v>8390</v>
+        <v>39208.6</v>
       </c>
       <c r="E311" s="10">
-        <v>7.82</v>
+        <v>8.33</v>
       </c>
       <c r="F311" s="10">
-        <v>12.84</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="312" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B312" s="6">
-        <v>41486</v>
+        <v>41639</v>
       </c>
       <c r="C312" s="7">
-        <v>149581</v>
+        <v>140358</v>
       </c>
       <c r="D312" s="7">
-        <v>6600</v>
+        <v>29986</v>
       </c>
       <c r="E312" s="8">
-        <v>7.43</v>
+        <v>8.38</v>
       </c>
       <c r="F312" s="8">
-        <v>12.36</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B313" s="6">
-        <v>41470</v>
+        <v>41623</v>
       </c>
       <c r="C313" s="9">
-        <v>169426</v>
+        <v>187536</v>
       </c>
       <c r="D313" s="9">
-        <v>42812</v>
+        <v>43304</v>
       </c>
       <c r="E313" s="10">
-        <v>7.36</v>
+        <v>8.05</v>
       </c>
       <c r="F313" s="10">
-        <v>12.62</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="314" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B314" s="6">
-        <v>41455</v>
+        <v>41608</v>
       </c>
       <c r="C314" s="7">
-        <v>135588</v>
+        <v>175637</v>
       </c>
       <c r="D314" s="7">
-        <v>26364</v>
+        <v>32295</v>
       </c>
       <c r="E314" s="8">
-        <v>7.58</v>
+        <v>8.74</v>
       </c>
       <c r="F314" s="8">
-        <v>12.71</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="315" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B315" s="6">
-        <v>41440</v>
+        <v>41593</v>
       </c>
       <c r="C315" s="9">
-        <v>170246</v>
+        <v>172515</v>
       </c>
       <c r="D315" s="9">
-        <v>40806</v>
+        <v>30309</v>
       </c>
       <c r="E315" s="10">
-        <v>7.57</v>
+        <v>8.44</v>
       </c>
       <c r="F315" s="10">
-        <v>12.79</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="316" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B316" s="6">
-        <v>41425</v>
+        <v>41578</v>
       </c>
       <c r="C316" s="7">
-        <v>173248</v>
+        <v>157449</v>
       </c>
       <c r="D316" s="7">
-        <v>27475</v>
+        <v>33724</v>
       </c>
       <c r="E316" s="8">
-        <v>7.7</v>
+        <v>8.63</v>
       </c>
       <c r="F316" s="8">
-        <v>13.3</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="317" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B317" s="6">
-        <v>41409</v>
+        <v>41562</v>
       </c>
       <c r="C317" s="9">
-        <v>175575</v>
+        <v>136312</v>
       </c>
       <c r="D317" s="9">
-        <v>29479</v>
+        <v>45270</v>
       </c>
       <c r="E317" s="10">
-        <v>7.7</v>
+        <v>8.03</v>
       </c>
       <c r="F317" s="10">
-        <v>12.77</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="318" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B318" s="6">
-        <v>41394</v>
+        <v>41547</v>
       </c>
       <c r="C318" s="7">
-        <v>157491</v>
+        <v>98638</v>
       </c>
       <c r="D318" s="7">
-        <v>27717</v>
+        <v>26778</v>
       </c>
       <c r="E318" s="8">
-        <v>7.85</v>
+        <v>9.5</v>
       </c>
       <c r="F318" s="8">
-        <v>13.3</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="319" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B319" s="6">
-        <v>41379</v>
+        <v>41532</v>
       </c>
       <c r="C319" s="9">
-        <v>150355</v>
+        <v>108187</v>
       </c>
       <c r="D319" s="9">
-        <v>50980</v>
+        <v>17027</v>
       </c>
       <c r="E319" s="10">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="F319" s="10">
-        <v>13.25</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="320" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B320" s="6">
-        <v>41364</v>
+        <v>41517</v>
       </c>
       <c r="C320" s="7">
-        <v>109255</v>
+        <v>118290</v>
       </c>
       <c r="D320" s="7">
-        <v>19273</v>
+        <v>9760</v>
       </c>
       <c r="E320" s="8">
-        <v>8.05</v>
+        <v>9.5</v>
       </c>
       <c r="F320" s="8">
-        <v>13.42</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B321" s="6">
-        <v>41348</v>
+        <v>41501</v>
       </c>
       <c r="C321" s="9">
-        <v>181072</v>
+        <v>136340</v>
       </c>
       <c r="D321" s="9">
-        <v>30874</v>
+        <v>8390</v>
       </c>
       <c r="E321" s="10">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="F321" s="10">
-        <v>13.61</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B322" s="6">
-        <v>41333</v>
+        <v>41486</v>
       </c>
       <c r="C322" s="7">
-        <v>192340</v>
+        <v>149581</v>
       </c>
       <c r="D322" s="7">
-        <v>26305</v>
+        <v>6600</v>
       </c>
       <c r="E322" s="8">
-        <v>8.02</v>
+        <v>7.43</v>
       </c>
       <c r="F322" s="8">
-        <v>13.96</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B323" s="6">
-        <v>41320</v>
+        <v>41470</v>
       </c>
       <c r="C323" s="9">
-        <v>209558</v>
+        <v>169426</v>
       </c>
       <c r="D323" s="9">
-        <v>43003</v>
+        <v>42812</v>
       </c>
       <c r="E323" s="10">
-        <v>7.88</v>
+        <v>7.36</v>
       </c>
       <c r="F323" s="10">
-        <v>14.96</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B324" s="6">
-        <v>41305</v>
+        <v>41455</v>
       </c>
       <c r="C324" s="7">
-        <v>199841.55</v>
+        <v>135588</v>
       </c>
       <c r="D324" s="7">
-        <v>27556.5</v>
+        <v>26364</v>
       </c>
       <c r="E324" s="8">
-        <v>7.97</v>
+        <v>7.58</v>
       </c>
       <c r="F324" s="8">
-        <v>13.37</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B325" s="6">
-        <v>41289</v>
+        <v>41440</v>
       </c>
       <c r="C325" s="9">
-        <v>211750</v>
+        <v>170246</v>
       </c>
       <c r="D325" s="9">
-        <v>47228</v>
+        <v>40806</v>
       </c>
       <c r="E325" s="10">
-        <v>8.05</v>
+        <v>7.57</v>
       </c>
       <c r="F325" s="10">
-        <v>13.45</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B326" s="6">
-        <v>41274</v>
+        <v>41425</v>
       </c>
       <c r="C326" s="7">
-        <v>181766</v>
+        <v>173248</v>
       </c>
       <c r="D326" s="7">
-        <v>27893</v>
+        <v>27475</v>
       </c>
       <c r="E326" s="8">
-        <v>8.36</v>
+        <v>7.7</v>
       </c>
       <c r="F326" s="8">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="327" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B327" s="6">
-        <v>41258</v>
+        <v>41409</v>
       </c>
       <c r="C327" s="9">
-        <v>215239</v>
+        <v>175575</v>
       </c>
       <c r="D327" s="9">
-        <v>54826</v>
+        <v>29479</v>
       </c>
       <c r="E327" s="10">
-        <v>8.05</v>
+        <v>7.7</v>
       </c>
       <c r="F327" s="10">
-        <v>14.46</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="328" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B328" s="6">
-        <v>41243</v>
+        <v>41394</v>
       </c>
       <c r="C328" s="7">
-        <v>199433</v>
+        <v>157491</v>
       </c>
       <c r="D328" s="7">
-        <v>42364</v>
+        <v>27717</v>
       </c>
       <c r="E328" s="8">
-        <v>7.92</v>
+        <v>7.85</v>
       </c>
       <c r="F328" s="8">
-        <v>14</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B329" s="6">
-        <v>41228</v>
+        <v>41379</v>
       </c>
       <c r="C329" s="9">
-        <v>204009.1</v>
+        <v>150355</v>
       </c>
       <c r="D329" s="9">
-        <v>26849.5</v>
+        <v>50980</v>
       </c>
       <c r="E329" s="10">
-        <v>7.64</v>
+        <v>7.8</v>
       </c>
       <c r="F329" s="10">
-        <v>12.67</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="330" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B330" s="6">
-        <v>41213</v>
+        <v>41364</v>
       </c>
       <c r="C330" s="7">
-        <v>194106</v>
+        <v>109255</v>
       </c>
       <c r="D330" s="7">
-        <v>24424</v>
+        <v>19273</v>
       </c>
       <c r="E330" s="8">
         <v>8.05</v>
       </c>
       <c r="F330" s="8">
-        <v>12.59</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="331" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B331" s="6">
-        <v>41197</v>
+        <v>41348</v>
       </c>
       <c r="C331" s="9">
-        <v>196129.2</v>
+        <v>181072</v>
       </c>
       <c r="D331" s="9">
-        <v>33991</v>
+        <v>30874</v>
       </c>
       <c r="E331" s="10">
-        <v>7.99</v>
+        <v>7.9</v>
       </c>
       <c r="F331" s="10">
-        <v>14.47</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B332" s="6">
-        <v>41182</v>
+        <v>41333</v>
       </c>
       <c r="C332" s="7">
-        <v>170577.65</v>
+        <v>192340</v>
       </c>
       <c r="D332" s="7">
-        <v>27920.5</v>
+        <v>26305</v>
       </c>
       <c r="E332" s="8">
-        <v>8.33</v>
+        <v>8.02</v>
       </c>
       <c r="F332" s="8">
-        <v>14.5</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B333" s="6">
-        <v>41167</v>
+        <v>41320</v>
       </c>
       <c r="C333" s="9">
-        <v>194793.15</v>
+        <v>209558</v>
       </c>
       <c r="D333" s="9">
-        <v>41460</v>
+        <v>43003</v>
       </c>
       <c r="E333" s="10">
-        <v>7.37</v>
+        <v>7.88</v>
       </c>
       <c r="F333" s="10">
-        <v>14.5</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="334" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B334" s="6">
-        <v>41152</v>
+        <v>41305</v>
       </c>
       <c r="C334" s="7">
-        <v>187890</v>
+        <v>199841.55</v>
       </c>
       <c r="D334" s="7">
-        <v>30770</v>
+        <v>27556.5</v>
       </c>
       <c r="E334" s="8">
-        <v>8.21</v>
+        <v>7.97</v>
       </c>
       <c r="F334" s="8">
-        <v>13.96</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="335" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B335" s="6">
-        <v>41136</v>
+        <v>41289</v>
       </c>
       <c r="C335" s="9">
-        <v>183021.7</v>
+        <v>211750</v>
       </c>
       <c r="D335" s="9">
-        <v>24976.05</v>
+        <v>47228</v>
       </c>
       <c r="E335" s="10">
-        <v>8.35</v>
+        <v>8.05</v>
       </c>
       <c r="F335" s="10">
-        <v>14.23</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B336" s="6">
-        <v>41121</v>
+        <v>41274</v>
       </c>
       <c r="C336" s="7">
-        <v>173225</v>
+        <v>181766</v>
       </c>
       <c r="D336" s="7">
-        <v>29003</v>
+        <v>27893</v>
       </c>
       <c r="E336" s="8">
-        <v>7.43</v>
+        <v>8.36</v>
       </c>
       <c r="F336" s="8">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="337" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B337" s="6">
-        <v>41105</v>
+        <v>41258</v>
       </c>
       <c r="C337" s="9">
-        <v>164728</v>
+        <v>215239</v>
       </c>
       <c r="D337" s="9">
-        <v>43941</v>
+        <v>54826</v>
       </c>
       <c r="E337" s="10">
-        <v>8.43</v>
+        <v>8.05</v>
       </c>
       <c r="F337" s="10">
-        <v>14.38</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="338" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B338" s="6">
-        <v>41090</v>
+        <v>41243</v>
       </c>
       <c r="C338" s="7">
-        <v>125811</v>
+        <v>199433</v>
       </c>
       <c r="D338" s="7">
-        <v>27600</v>
+        <v>42364</v>
       </c>
       <c r="E338" s="8">
-        <v>8.24</v>
+        <v>7.92</v>
       </c>
       <c r="F338" s="8">
-        <v>15.25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B339" s="6">
-        <v>41075</v>
+        <v>41228</v>
       </c>
       <c r="C339" s="9">
-        <v>163481</v>
+        <v>204009.1</v>
       </c>
       <c r="D339" s="9">
-        <v>32887</v>
+        <v>26849.5</v>
       </c>
       <c r="E339" s="10">
-        <v>8.85</v>
+        <v>7.64</v>
       </c>
       <c r="F339" s="10">
-        <v>14.75</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B340" s="6">
-        <v>41060</v>
+        <v>41213</v>
       </c>
       <c r="C340" s="7">
-        <v>149801</v>
+        <v>194106</v>
       </c>
       <c r="D340" s="7">
-        <v>21489</v>
+        <v>24424</v>
       </c>
       <c r="E340" s="8">
-        <v>7.9</v>
+        <v>8.05</v>
       </c>
       <c r="F340" s="8">
-        <v>15</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B341" s="6">
-        <v>41044</v>
+        <v>41197</v>
       </c>
       <c r="C341" s="9">
-        <v>144345</v>
+        <v>196129.2</v>
       </c>
       <c r="D341" s="9">
-        <v>21844</v>
+        <v>33991</v>
       </c>
       <c r="E341" s="10">
-        <v>8.68</v>
+        <v>7.99</v>
       </c>
       <c r="F341" s="10">
-        <v>15</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="342" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B342" s="6">
-        <v>41029</v>
+        <v>41182</v>
       </c>
       <c r="C342" s="7">
-        <v>131003</v>
+        <v>170577.65</v>
       </c>
       <c r="D342" s="7">
-        <v>35328</v>
+        <v>27920.5</v>
       </c>
       <c r="E342" s="8">
-        <v>8.02</v>
+        <v>8.33</v>
       </c>
       <c r="F342" s="8">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B343" s="6">
-        <v>41014</v>
+        <v>41167</v>
       </c>
       <c r="C343" s="9">
-        <v>110350</v>
+        <v>194793.15</v>
       </c>
       <c r="D343" s="9">
-        <v>23547</v>
+        <v>41460</v>
       </c>
       <c r="E343" s="10">
-        <v>8.51</v>
+        <v>7.37</v>
       </c>
       <c r="F343" s="10">
         <v>14.5</v>
@@ -6040,371 +6041,542 @@
     </row>
     <row r="344" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B344" s="6">
-        <v>40999</v>
+        <v>41152</v>
       </c>
       <c r="C344" s="7">
-        <v>91188</v>
+        <v>187890</v>
       </c>
       <c r="D344" s="7">
-        <v>17630</v>
+        <v>30770</v>
       </c>
       <c r="E344" s="8">
-        <v>9.75</v>
+        <v>8.21</v>
       </c>
       <c r="F344" s="8">
-        <v>15.25</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B345" s="6">
-        <v>40983</v>
+        <v>41136</v>
       </c>
       <c r="C345" s="9">
-        <v>133527</v>
+        <v>183021.7</v>
       </c>
       <c r="D345" s="9">
-        <v>21110</v>
+        <v>24976.05</v>
       </c>
       <c r="E345" s="10">
-        <v>9.63</v>
+        <v>8.35</v>
       </c>
       <c r="F345" s="10">
-        <v>14.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="346" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B346" s="6">
-        <v>40968</v>
+        <v>41121</v>
       </c>
       <c r="C346" s="7">
-        <v>161759</v>
+        <v>173225</v>
       </c>
       <c r="D346" s="7">
-        <v>25494</v>
+        <v>29003</v>
       </c>
       <c r="E346" s="8">
-        <v>8.47</v>
+        <v>7.43</v>
       </c>
       <c r="F346" s="8">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="347" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B347" s="6">
-        <v>40954</v>
+        <v>41105</v>
       </c>
       <c r="C347" s="9">
-        <v>161394</v>
+        <v>164728</v>
       </c>
       <c r="D347" s="9">
-        <v>31420</v>
+        <v>43941</v>
       </c>
       <c r="E347" s="10">
-        <v>7.75</v>
+        <v>8.43</v>
       </c>
       <c r="F347" s="10">
-        <v>14.65</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="348" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B348" s="6">
-        <v>40939</v>
+        <v>41090</v>
       </c>
       <c r="C348" s="7">
-        <v>149883</v>
+        <v>125811</v>
       </c>
       <c r="D348" s="7">
-        <v>15968</v>
+        <v>27600</v>
       </c>
       <c r="E348" s="8">
-        <v>8.66</v>
+        <v>8.24</v>
       </c>
       <c r="F348" s="8">
-        <v>13.25</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="349" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B349" s="6">
-        <v>40923</v>
+        <v>41075</v>
       </c>
       <c r="C349" s="9">
-        <v>152829</v>
+        <v>163481</v>
       </c>
       <c r="D349" s="9">
-        <v>27467</v>
+        <v>32887</v>
       </c>
       <c r="E349" s="10">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="F349" s="10">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="350" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B350" s="6">
-        <v>40908</v>
+        <v>41060</v>
       </c>
       <c r="C350" s="7">
-        <v>134148.5</v>
+        <v>149801</v>
       </c>
       <c r="D350" s="7">
-        <v>22437</v>
+        <v>21489</v>
       </c>
       <c r="E350" s="8">
-        <v>8.38</v>
+        <v>7.9</v>
       </c>
       <c r="F350" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B351" s="6">
-        <v>40892</v>
+        <v>41044</v>
       </c>
       <c r="C351" s="9">
-        <v>177521</v>
+        <v>144345</v>
       </c>
       <c r="D351" s="9">
-        <v>34006</v>
+        <v>21844</v>
       </c>
       <c r="E351" s="10">
-        <v>9.1</v>
+        <v>8.68</v>
       </c>
       <c r="F351" s="10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B352" s="6">
-        <v>40877</v>
+        <v>41029</v>
       </c>
       <c r="C352" s="7">
-        <v>173476</v>
+        <v>131003</v>
       </c>
       <c r="D352" s="7">
-        <v>18811</v>
+        <v>35328</v>
       </c>
       <c r="E352" s="8">
-        <v>8</v>
+        <v>8.02</v>
       </c>
       <c r="F352" s="8">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="353" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B353" s="6">
-        <v>40862</v>
+        <v>41014</v>
       </c>
       <c r="C353" s="9">
-        <v>176069</v>
+        <v>110350</v>
       </c>
       <c r="D353" s="9">
-        <v>24944</v>
+        <v>23547</v>
       </c>
       <c r="E353" s="10">
-        <v>8.78</v>
+        <v>8.51</v>
       </c>
       <c r="F353" s="10">
-        <v>13.55</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="354" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B354" s="6">
-        <v>40847</v>
+        <v>40999</v>
       </c>
       <c r="C354" s="7">
-        <v>168769</v>
+        <v>91188</v>
       </c>
       <c r="D354" s="7">
-        <v>16179</v>
+        <v>17630</v>
       </c>
       <c r="E354" s="8">
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
       <c r="F354" s="8">
-        <v>14.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="355" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B355" s="6">
-        <v>40831</v>
+        <v>40983</v>
       </c>
       <c r="C355" s="9">
-        <v>166462</v>
+        <v>133527</v>
       </c>
       <c r="D355" s="9">
-        <v>29243</v>
+        <v>21110</v>
       </c>
       <c r="E355" s="10">
-        <v>8.75</v>
+        <v>9.63</v>
       </c>
       <c r="F355" s="10">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="356" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B356" s="6">
-        <v>40816</v>
+        <v>40968</v>
       </c>
       <c r="C356" s="7">
-        <v>144621</v>
+        <v>161759</v>
       </c>
       <c r="D356" s="7">
-        <v>37926</v>
+        <v>25494</v>
       </c>
       <c r="E356" s="8">
-        <v>7.83</v>
+        <v>8.47</v>
       </c>
       <c r="F356" s="8">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="357" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B357" s="6">
-        <v>40801</v>
+        <v>40954</v>
       </c>
       <c r="C357" s="9">
-        <v>159701</v>
+        <v>161394</v>
       </c>
       <c r="D357" s="9">
-        <v>31045</v>
+        <v>31420</v>
       </c>
       <c r="E357" s="10">
-        <v>8.47</v>
+        <v>7.75</v>
       </c>
       <c r="F357" s="10">
-        <v>14</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="358" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B358" s="6">
-        <v>40786</v>
+        <v>40939</v>
       </c>
       <c r="C358" s="7">
-        <v>148812</v>
+        <v>149883</v>
       </c>
       <c r="D358" s="7">
-        <v>21797</v>
+        <v>15968</v>
       </c>
       <c r="E358" s="8">
-        <v>7.67</v>
+        <v>8.66</v>
       </c>
       <c r="F358" s="8">
-        <v>14.5</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="359" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B359" s="6">
-        <v>40770</v>
+        <v>40923</v>
       </c>
       <c r="C359" s="9">
-        <v>142452</v>
+        <v>152829</v>
       </c>
       <c r="D359" s="9">
-        <v>19445</v>
+        <v>27467</v>
       </c>
       <c r="E359" s="10">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F359" s="10">
-        <v>13.85</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="360" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B360" s="6">
-        <v>40755</v>
+        <v>40908</v>
       </c>
       <c r="C360" s="7">
-        <v>133691</v>
+        <v>134148.5</v>
       </c>
       <c r="D360" s="7">
-        <v>16868</v>
+        <v>22437</v>
       </c>
       <c r="E360" s="8">
-        <v>7.06</v>
+        <v>8.38</v>
       </c>
       <c r="F360" s="8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="361" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B361" s="6">
-        <v>40739</v>
+        <v>40892</v>
       </c>
       <c r="C361" s="9">
-        <v>128347</v>
+        <v>177521</v>
       </c>
       <c r="D361" s="9">
-        <v>29818</v>
+        <v>34006</v>
       </c>
       <c r="E361" s="10">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="F361" s="10">
-        <v>13.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="362" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B362" s="6">
+        <v>40877</v>
+      </c>
+      <c r="C362" s="7">
+        <v>173476</v>
+      </c>
+      <c r="D362" s="7">
+        <v>18811</v>
+      </c>
+      <c r="E362" s="8">
+        <v>8</v>
+      </c>
+      <c r="F362" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="363" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B363" s="6">
+        <v>40862</v>
+      </c>
+      <c r="C363" s="9">
+        <v>176069</v>
+      </c>
+      <c r="D363" s="9">
+        <v>24944</v>
+      </c>
+      <c r="E363" s="10">
+        <v>8.78</v>
+      </c>
+      <c r="F363" s="10">
+        <v>13.55</v>
+      </c>
+    </row>
+    <row r="364" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B364" s="6">
+        <v>40847</v>
+      </c>
+      <c r="C364" s="7">
+        <v>168769</v>
+      </c>
+      <c r="D364" s="7">
+        <v>16179</v>
+      </c>
+      <c r="E364" s="8">
+        <v>7.75</v>
+      </c>
+      <c r="F364" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="365" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B365" s="6">
+        <v>40831</v>
+      </c>
+      <c r="C365" s="9">
+        <v>166462</v>
+      </c>
+      <c r="D365" s="9">
+        <v>29243</v>
+      </c>
+      <c r="E365" s="10">
+        <v>8.75</v>
+      </c>
+      <c r="F365" s="10">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="366" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B366" s="6">
+        <v>40816</v>
+      </c>
+      <c r="C366" s="7">
+        <v>144621</v>
+      </c>
+      <c r="D366" s="7">
+        <v>37926</v>
+      </c>
+      <c r="E366" s="8">
+        <v>7.83</v>
+      </c>
+      <c r="F366" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="367" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B367" s="6">
+        <v>40801</v>
+      </c>
+      <c r="C367" s="9">
+        <v>159701</v>
+      </c>
+      <c r="D367" s="9">
+        <v>31045</v>
+      </c>
+      <c r="E367" s="10">
+        <v>8.47</v>
+      </c>
+      <c r="F367" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="368" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B368" s="6">
+        <v>40786</v>
+      </c>
+      <c r="C368" s="7">
+        <v>148812</v>
+      </c>
+      <c r="D368" s="7">
+        <v>21797</v>
+      </c>
+      <c r="E368" s="8">
+        <v>7.67</v>
+      </c>
+      <c r="F368" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="369" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B369" s="6">
+        <v>40770</v>
+      </c>
+      <c r="C369" s="9">
+        <v>142452</v>
+      </c>
+      <c r="D369" s="9">
+        <v>19445</v>
+      </c>
+      <c r="E369" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="F369" s="10">
+        <v>13.85</v>
+      </c>
+    </row>
+    <row r="370" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B370" s="6">
+        <v>40755</v>
+      </c>
+      <c r="C370" s="7">
+        <v>133691</v>
+      </c>
+      <c r="D370" s="7">
+        <v>16868</v>
+      </c>
+      <c r="E370" s="8">
+        <v>7.06</v>
+      </c>
+      <c r="F370" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="371" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B371" s="6">
+        <v>40739</v>
+      </c>
+      <c r="C371" s="9">
+        <v>128347</v>
+      </c>
+      <c r="D371" s="9">
+        <v>29818</v>
+      </c>
+      <c r="E371" s="10">
+        <v>8.1</v>
+      </c>
+      <c r="F371" s="10">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="372" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B372" s="6">
         <v>40724</v>
       </c>
-      <c r="C362" s="7">
+      <c r="C372" s="7">
         <v>104689</v>
       </c>
-      <c r="D362" s="7">
+      <c r="D372" s="7">
         <v>30290</v>
       </c>
-      <c r="E362" s="8">
+      <c r="E372" s="8">
         <v>8.35</v>
       </c>
-      <c r="F362" s="8">
+      <c r="F372" s="8">
         <v>13.5</v>
       </c>
     </row>
-    <row r="363" s="1" customFormat="1" ht="19.1988" customHeight="1">
-      <c r="B363" s="11">
+    <row r="373" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B373" s="11">
         <v>40709</v>
       </c>
-      <c r="C363" s="12">
+      <c r="C373" s="12">
         <v>123400</v>
       </c>
-      <c r="D363" s="12">
+      <c r="D373" s="12">
         <v>20522</v>
       </c>
-      <c r="E363" s="13">
+      <c r="E373" s="13">
         <v>8.25</v>
       </c>
-      <c r="F363" s="13">
+      <c r="F373" s="13">
         <v>13</v>
       </c>
     </row>
-    <row r="364" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
-    <row r="365" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="B365" s="14" t="s">
+    <row r="374" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
+    <row r="375" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B375" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C365" s="15" t="s">
+      <c r="C375" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D365" s="15"/>
-      <c r="E365" s="15"/>
-      <c r="F365" s="15"/>
-    </row>
-    <row r="366" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="B366" s="18" t="s">
+      <c r="D375" s="15"/>
+      <c r="E375" s="15"/>
+      <c r="F375" s="15"/>
+    </row>
+    <row r="376" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B376" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C366" s="18"/>
-      <c r="D366" s="18"/>
-      <c r="E366" s="18"/>
-      <c r="F366" s="18"/>
-    </row>
+      <c r="C376" s="18"/>
+      <c r="D376" s="18"/>
+      <c r="E376" s="18"/>
+      <c r="F376" s="18"/>
+    </row>
+    <row r="377" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B366:F366"/>
+    <mergeCell ref="B376:F376"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C365:F365"/>
+    <mergeCell ref="C375:F375"/>
   </mergeCells>
   <pageSetup paperSize="120" scale="100" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/publications/monthly-rbi-bulletin/financial-markets/table-29-commercial-paper.xlsx
+++ b/data/publications/monthly-rbi-bulletin/financial-markets/table-29-commercial-paper.xlsx
@@ -236,10 +236,10 @@
     <xf numFmtId="173" fontId="3" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="2" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="4" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="5" fillId="2" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="5" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -266,7 +266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F377"/>
+  <dimension ref="A1:F378"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="5" width="20.8466173333333" customWidth="1"/>
@@ -329,1376 +329,1376 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B8" s="6">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="C8" s="7">
-        <v>639856.7</v>
+        <v>652945.45</v>
       </c>
       <c r="D8" s="7">
-        <v>91579.05</v>
+        <v>184787.25</v>
       </c>
       <c r="E8" s="8">
-        <v>6.2896</v>
+        <v>5.2456</v>
       </c>
       <c r="F8" s="8">
-        <v>14.0955</v>
+        <v>12.1381</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B9" s="6">
-        <v>46249</v>
+        <v>46265</v>
       </c>
       <c r="C9" s="9">
-        <v>618019.65</v>
+        <v>639856.7</v>
       </c>
       <c r="D9" s="9">
-        <v>88890.5</v>
+        <v>91579.05</v>
       </c>
       <c r="E9" s="10">
-        <v>4.9901</v>
+        <v>6.2896</v>
       </c>
       <c r="F9" s="10">
-        <v>12.6681</v>
+        <v>14.0955</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B10" s="6">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="C10" s="7">
-        <v>586897.4</v>
+        <v>618019.65</v>
       </c>
       <c r="D10" s="7">
-        <v>59083.65</v>
+        <v>88890.5</v>
       </c>
       <c r="E10" s="8">
-        <v>6.2287</v>
+        <v>4.9901</v>
       </c>
       <c r="F10" s="8">
-        <v>13.9102</v>
+        <v>12.6681</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B11" s="6">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="C11" s="9">
-        <v>565904.95</v>
+        <v>586897.4</v>
       </c>
       <c r="D11" s="9">
-        <v>62526.35</v>
+        <v>59083.65</v>
       </c>
       <c r="E11" s="10">
-        <v>6.0184</v>
+        <v>6.2287</v>
       </c>
       <c r="F11" s="10">
-        <v>10.607</v>
+        <v>13.9102</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B12" s="6">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="C12" s="7">
-        <v>541805.35</v>
+        <v>565904.95</v>
       </c>
       <c r="D12" s="7">
-        <v>96188.65</v>
+        <v>62526.35</v>
       </c>
       <c r="E12" s="8">
-        <v>6.267</v>
+        <v>6.0184</v>
       </c>
       <c r="F12" s="8">
-        <v>14.1829</v>
+        <v>10.607</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B13" s="6">
-        <v>46188</v>
+        <v>46203</v>
       </c>
       <c r="C13" s="9">
-        <v>557704.55</v>
+        <v>541805.35</v>
       </c>
       <c r="D13" s="9">
-        <v>158714.4</v>
+        <v>96188.65</v>
       </c>
       <c r="E13" s="10">
-        <v>6.1344</v>
+        <v>6.267</v>
       </c>
       <c r="F13" s="10">
-        <v>14.1572</v>
+        <v>14.1829</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B14" s="6">
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="C14" s="7">
-        <v>536186.35</v>
+        <v>557704.55</v>
       </c>
       <c r="D14" s="7">
-        <v>74982.4</v>
+        <v>158714.4</v>
       </c>
       <c r="E14" s="8">
-        <v>5.8824</v>
+        <v>6.1344</v>
       </c>
       <c r="F14" s="8">
-        <v>13.3022</v>
+        <v>14.1572</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B15" s="6">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="C15" s="9">
-        <v>539318.4</v>
+        <v>536186.35</v>
       </c>
       <c r="D15" s="9">
-        <v>62963.15</v>
+        <v>74982.4</v>
       </c>
       <c r="E15" s="10">
-        <v>6.2289</v>
+        <v>5.8824</v>
       </c>
       <c r="F15" s="10">
-        <v>12.0791</v>
+        <v>13.3022</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B16" s="6">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="C16" s="7">
-        <v>560941.15</v>
+        <v>539318.4</v>
       </c>
       <c r="D16" s="7">
-        <v>65227.35</v>
+        <v>62963.15</v>
       </c>
       <c r="E16" s="8">
-        <v>5.5363</v>
+        <v>6.2289</v>
       </c>
       <c r="F16" s="8">
-        <v>13.3022</v>
+        <v>12.0791</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B17" s="6">
-        <v>46127</v>
+        <v>46142</v>
       </c>
       <c r="C17" s="9">
-        <v>526603.7</v>
+        <v>560941.15</v>
       </c>
       <c r="D17" s="9">
-        <v>79682.25</v>
+        <v>65227.35</v>
       </c>
       <c r="E17" s="10">
-        <v>5.565</v>
+        <v>5.5363</v>
       </c>
       <c r="F17" s="10">
-        <v>9.7169</v>
+        <v>13.3022</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B18" s="6">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="C18" s="7">
-        <v>460151.55</v>
+        <v>526603.7</v>
       </c>
       <c r="D18" s="7">
-        <v>77688.35</v>
+        <v>79682.25</v>
       </c>
       <c r="E18" s="8">
-        <v>5.9155</v>
+        <v>5.565</v>
       </c>
       <c r="F18" s="8">
-        <v>14.4011</v>
+        <v>9.7169</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B19" s="6">
-        <v>46096</v>
+        <v>46112</v>
       </c>
       <c r="C19" s="9">
-        <v>476150.85</v>
+        <v>460151.55</v>
       </c>
       <c r="D19" s="9">
-        <v>100794.6</v>
+        <v>77688.35</v>
       </c>
       <c r="E19" s="10">
-        <v>6.2702</v>
+        <v>5.9155</v>
       </c>
       <c r="F19" s="10">
-        <v>12.0003</v>
+        <v>14.4011</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B20" s="6">
-        <v>46081</v>
+        <v>46096</v>
       </c>
       <c r="C20" s="7">
-        <v>478434.45</v>
+        <v>476150.85</v>
       </c>
       <c r="D20" s="7">
-        <v>79734.2</v>
+        <v>100794.6</v>
       </c>
       <c r="E20" s="8">
-        <v>5.9624</v>
+        <v>6.2702</v>
       </c>
       <c r="F20" s="8">
-        <v>11.1794</v>
+        <v>12.0003</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B21" s="6">
-        <v>46068</v>
+        <v>46081</v>
       </c>
       <c r="C21" s="9">
-        <v>481234.6</v>
+        <v>478434.45</v>
       </c>
       <c r="D21" s="9">
-        <v>110283.75</v>
+        <v>79734.2</v>
       </c>
       <c r="E21" s="10">
-        <v>6.0631</v>
+        <v>5.9624</v>
       </c>
       <c r="F21" s="10">
-        <v>13.5649</v>
+        <v>11.1794</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B22" s="6">
-        <v>46053</v>
+        <v>46068</v>
       </c>
       <c r="C22" s="7">
-        <v>438787.05</v>
+        <v>481234.6</v>
       </c>
       <c r="D22" s="7">
-        <v>41076.2</v>
+        <v>110283.75</v>
       </c>
       <c r="E22" s="8">
-        <v>6.1822</v>
+        <v>6.0631</v>
       </c>
       <c r="F22" s="8">
-        <v>14.465</v>
+        <v>13.5649</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B23" s="6">
-        <v>46037</v>
+        <v>46053</v>
       </c>
       <c r="C23" s="9">
-        <v>453838.55</v>
+        <v>438787.05</v>
       </c>
       <c r="D23" s="9">
-        <v>26659.2</v>
+        <v>41076.2</v>
       </c>
       <c r="E23" s="10">
-        <v>5.9221</v>
+        <v>6.1822</v>
       </c>
       <c r="F23" s="10">
-        <v>13.4239</v>
+        <v>14.465</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B24" s="6">
-        <v>46022</v>
+        <v>46037</v>
       </c>
       <c r="C24" s="7">
-        <v>451053.35</v>
+        <v>453838.55</v>
       </c>
       <c r="D24" s="7">
-        <v>59006.25</v>
+        <v>26659.2</v>
       </c>
       <c r="E24" s="8">
-        <v>5.9922</v>
+        <v>5.9221</v>
       </c>
       <c r="F24" s="8">
-        <v>13.5279</v>
+        <v>13.4239</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B25" s="6">
-        <v>46006</v>
+        <v>46022</v>
       </c>
       <c r="C25" s="9">
-        <v>473476.3</v>
+        <v>451053.35</v>
       </c>
       <c r="D25" s="9">
-        <v>79654</v>
+        <v>59006.25</v>
       </c>
       <c r="E25" s="10">
-        <v>5.8143</v>
+        <v>5.9922</v>
       </c>
       <c r="F25" s="10">
-        <v>12.1224</v>
+        <v>13.5279</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B26" s="6">
-        <v>45991</v>
+        <v>46006</v>
       </c>
       <c r="C26" s="7">
-        <v>501649.2</v>
+        <v>473476.3</v>
       </c>
       <c r="D26" s="7">
-        <v>69177.7</v>
+        <v>79654</v>
       </c>
       <c r="E26" s="8">
-        <v>5.79</v>
+        <v>5.8143</v>
       </c>
       <c r="F26" s="8">
-        <v>11.49</v>
+        <v>12.1224</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B27" s="6">
-        <v>45976</v>
+        <v>45991</v>
       </c>
       <c r="C27" s="9">
-        <v>501658</v>
+        <v>501649.2</v>
       </c>
       <c r="D27" s="9">
-        <v>66525.85</v>
+        <v>69177.7</v>
       </c>
       <c r="E27" s="10">
-        <v>5.86</v>
+        <v>5.79</v>
       </c>
       <c r="F27" s="10">
-        <v>9.7117</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B28" s="6">
-        <v>45961</v>
+        <v>45976</v>
       </c>
       <c r="C28" s="7">
-        <v>479629.5</v>
+        <v>501658</v>
       </c>
       <c r="D28" s="7">
-        <v>52397.55</v>
+        <v>66525.85</v>
       </c>
       <c r="E28" s="8">
-        <v>5.79</v>
+        <v>5.86</v>
       </c>
       <c r="F28" s="8">
-        <v>14.93</v>
+        <v>9.7117</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B29" s="6">
-        <v>45945</v>
+        <v>45961</v>
       </c>
       <c r="C29" s="9">
-        <v>495678.6</v>
+        <v>479629.5</v>
       </c>
       <c r="D29" s="9">
-        <v>30794.65</v>
+        <v>52397.55</v>
       </c>
       <c r="E29" s="10">
-        <v>5.71</v>
+        <v>5.79</v>
       </c>
       <c r="F29" s="10">
-        <v>12.49</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B30" s="6">
-        <v>45930</v>
+        <v>45945</v>
       </c>
       <c r="C30" s="7">
-        <v>488262.8</v>
+        <v>495678.6</v>
       </c>
       <c r="D30" s="7">
-        <v>70288</v>
+        <v>30794.65</v>
       </c>
       <c r="E30" s="8">
-        <v>5.7269</v>
+        <v>5.71</v>
       </c>
       <c r="F30" s="8">
-        <v>12.3382</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B31" s="6">
-        <v>45915</v>
+        <v>45930</v>
       </c>
       <c r="C31" s="9">
-        <v>526704.3</v>
+        <v>488262.8</v>
       </c>
       <c r="D31" s="9">
-        <v>99422.2</v>
+        <v>70288</v>
       </c>
       <c r="E31" s="10">
-        <v>5.7173</v>
+        <v>5.7269</v>
       </c>
       <c r="F31" s="10">
-        <v>11.9658</v>
+        <v>12.3382</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B32" s="6">
-        <v>45900</v>
+        <v>45915</v>
       </c>
       <c r="C32" s="7">
-        <v>543870.1</v>
+        <v>526704.3</v>
       </c>
       <c r="D32" s="7">
-        <v>60807.6</v>
+        <v>99422.2</v>
       </c>
       <c r="E32" s="8">
         <v>5.7173</v>
       </c>
       <c r="F32" s="8">
-        <v>13.8301</v>
+        <v>11.9658</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B33" s="6">
-        <v>45884</v>
+        <v>45900</v>
       </c>
       <c r="C33" s="9">
-        <v>554479.7</v>
+        <v>543870.1</v>
       </c>
       <c r="D33" s="9">
-        <v>56758.35</v>
+        <v>60807.6</v>
       </c>
       <c r="E33" s="10">
-        <v>5.683</v>
+        <v>5.7173</v>
       </c>
       <c r="F33" s="10">
-        <v>12.6681</v>
+        <v>13.8301</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B34" s="6">
-        <v>45869</v>
+        <v>45884</v>
       </c>
       <c r="C34" s="7">
-        <v>547229.3</v>
+        <v>554479.7</v>
       </c>
       <c r="D34" s="7">
-        <v>73858.5</v>
+        <v>56758.35</v>
       </c>
       <c r="E34" s="8">
-        <v>5.57</v>
+        <v>5.683</v>
       </c>
       <c r="F34" s="8">
-        <v>13.84</v>
+        <v>12.6681</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B35" s="6">
-        <v>45853</v>
+        <v>45869</v>
       </c>
       <c r="C35" s="9">
-        <v>534009.15</v>
+        <v>547229.3</v>
       </c>
       <c r="D35" s="9">
-        <v>79530.05</v>
+        <v>73858.5</v>
       </c>
       <c r="E35" s="10">
-        <v>5.51</v>
+        <v>5.57</v>
       </c>
       <c r="F35" s="10">
-        <v>12.67</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B36" s="6">
-        <v>45838</v>
+        <v>45853</v>
       </c>
       <c r="C36" s="7">
-        <v>500000.6</v>
+        <v>534009.15</v>
       </c>
       <c r="D36" s="7">
-        <v>58021.75</v>
+        <v>79530.05</v>
       </c>
       <c r="E36" s="8">
-        <v>5.7085</v>
+        <v>5.51</v>
       </c>
       <c r="F36" s="8">
-        <v>13.8408</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B37" s="6">
-        <v>45823</v>
+        <v>45838</v>
       </c>
       <c r="C37" s="9">
-        <v>549258.3</v>
+        <v>500000.6</v>
       </c>
       <c r="D37" s="9">
-        <v>102447</v>
+        <v>58021.75</v>
       </c>
       <c r="E37" s="10">
-        <v>5.6687</v>
+        <v>5.7085</v>
       </c>
       <c r="F37" s="10">
-        <v>11.6256</v>
+        <v>13.8408</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B38" s="6">
-        <v>45808</v>
+        <v>45823</v>
       </c>
       <c r="C38" s="7">
-        <v>553874.25</v>
+        <v>549258.3</v>
       </c>
       <c r="D38" s="7">
-        <v>81053.8</v>
+        <v>102447</v>
       </c>
       <c r="E38" s="8">
-        <v>5.97</v>
+        <v>5.6687</v>
       </c>
       <c r="F38" s="8">
-        <v>12.23</v>
+        <v>11.6256</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B39" s="6">
-        <v>45792</v>
+        <v>45808</v>
       </c>
       <c r="C39" s="9">
-        <v>541591.1</v>
+        <v>553874.25</v>
       </c>
       <c r="D39" s="9">
-        <v>48973.55</v>
+        <v>81053.8</v>
       </c>
       <c r="E39" s="10">
-        <v>6.44</v>
+        <v>5.97</v>
       </c>
       <c r="F39" s="10">
-        <v>10.14</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B40" s="6">
-        <v>45777</v>
+        <v>45792</v>
       </c>
       <c r="C40" s="7">
-        <v>545586.95</v>
+        <v>541591.1</v>
       </c>
       <c r="D40" s="7">
-        <v>72418.9</v>
+        <v>48973.55</v>
       </c>
       <c r="E40" s="8">
-        <v>6.2581</v>
+        <v>6.44</v>
       </c>
       <c r="F40" s="8">
-        <v>13.0015</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B41" s="6">
-        <v>45762</v>
+        <v>45777</v>
       </c>
       <c r="C41" s="9">
-        <v>521558.1</v>
+        <v>545586.95</v>
       </c>
       <c r="D41" s="9">
-        <v>91006.4</v>
+        <v>72418.9</v>
       </c>
       <c r="E41" s="10">
-        <v>6.3071</v>
+        <v>6.2581</v>
       </c>
       <c r="F41" s="10">
-        <v>11.6515</v>
+        <v>13.0015</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B42" s="6">
-        <v>45747</v>
+        <v>45762</v>
       </c>
       <c r="C42" s="7">
-        <v>442892.7</v>
+        <v>521558.1</v>
       </c>
       <c r="D42" s="7">
-        <v>77133.85</v>
+        <v>91006.4</v>
       </c>
       <c r="E42" s="8">
-        <v>7</v>
+        <v>6.3071</v>
       </c>
       <c r="F42" s="8">
-        <v>14.46</v>
+        <v>11.6515</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B43" s="6">
-        <v>45731</v>
+        <v>45747</v>
       </c>
       <c r="C43" s="9">
-        <v>457051.3</v>
+        <v>442892.7</v>
       </c>
       <c r="D43" s="9">
-        <v>107624.2</v>
+        <v>77133.85</v>
       </c>
       <c r="E43" s="10">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="F43" s="10">
-        <v>11.78</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B44" s="6">
-        <v>45716</v>
+        <v>45731</v>
       </c>
       <c r="C44" s="7">
-        <v>465926.95</v>
+        <v>457051.3</v>
       </c>
       <c r="D44" s="7">
-        <v>64880.85</v>
+        <v>107624.2</v>
       </c>
       <c r="E44" s="8">
-        <v>6.7752</v>
+        <v>6.67</v>
       </c>
       <c r="F44" s="8">
-        <v>12.2399</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B45" s="6">
-        <v>45703</v>
+        <v>45716</v>
       </c>
       <c r="C45" s="9">
-        <v>479257.25</v>
+        <v>465926.95</v>
       </c>
       <c r="D45" s="9">
-        <v>80693.35</v>
+        <v>64880.85</v>
       </c>
       <c r="E45" s="10">
-        <v>6.9732</v>
+        <v>6.7752</v>
       </c>
       <c r="F45" s="10">
-        <v>12.404</v>
+        <v>12.2399</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B46" s="6">
-        <v>45688</v>
+        <v>45703</v>
       </c>
       <c r="C46" s="7">
-        <v>456483.15</v>
+        <v>479257.25</v>
       </c>
       <c r="D46" s="7">
-        <v>69001.15</v>
+        <v>80693.35</v>
       </c>
       <c r="E46" s="8">
-        <v>7.12</v>
+        <v>6.9732</v>
       </c>
       <c r="F46" s="8">
-        <v>13.77</v>
+        <v>12.404</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B47" s="6">
-        <v>45672</v>
+        <v>45688</v>
       </c>
       <c r="C47" s="9">
-        <v>450242.05</v>
+        <v>456483.15</v>
       </c>
       <c r="D47" s="9">
-        <v>39647.3</v>
+        <v>69001.15</v>
       </c>
       <c r="E47" s="10">
-        <v>7.06</v>
+        <v>7.12</v>
       </c>
       <c r="F47" s="10">
-        <v>12.12</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B48" s="6">
-        <v>45657</v>
+        <v>45672</v>
       </c>
       <c r="C48" s="7">
-        <v>435779.45</v>
+        <v>450242.05</v>
       </c>
       <c r="D48" s="7">
-        <v>51524.05</v>
+        <v>39647.3</v>
       </c>
       <c r="E48" s="8">
-        <v>6.98</v>
+        <v>7.06</v>
       </c>
       <c r="F48" s="8">
-        <v>12</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B49" s="6">
-        <v>45641</v>
+        <v>45657</v>
       </c>
       <c r="C49" s="9">
-        <v>463801.3</v>
+        <v>435779.45</v>
       </c>
       <c r="D49" s="9">
-        <v>98956.25</v>
+        <v>51524.05</v>
       </c>
       <c r="E49" s="10">
-        <v>7</v>
+        <v>6.98</v>
       </c>
       <c r="F49" s="10">
-        <v>11.89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B50" s="6">
-        <v>45626</v>
+        <v>45641</v>
       </c>
       <c r="C50" s="7">
-        <v>445122.05</v>
+        <v>463801.3</v>
       </c>
       <c r="D50" s="7">
-        <v>64504.65</v>
+        <v>98956.25</v>
       </c>
       <c r="E50" s="8">
         <v>7</v>
       </c>
       <c r="F50" s="8">
-        <v>12.61</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B51" s="6">
-        <v>45611</v>
+        <v>45626</v>
       </c>
       <c r="C51" s="9">
-        <v>448862.8</v>
+        <v>445122.05</v>
       </c>
       <c r="D51" s="9">
-        <v>50771.85</v>
+        <v>64504.65</v>
       </c>
       <c r="E51" s="10">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="F51" s="10">
-        <v>13.77</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B52" s="6">
-        <v>45596</v>
+        <v>45611</v>
       </c>
       <c r="C52" s="7">
-        <v>445104.9</v>
+        <v>448862.8</v>
       </c>
       <c r="D52" s="7">
-        <v>66159.85</v>
+        <v>50771.85</v>
       </c>
       <c r="E52" s="8">
-        <v>6.988</v>
+        <v>6.99</v>
       </c>
       <c r="F52" s="8">
-        <v>12.5313</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B53" s="6">
-        <v>45580</v>
+        <v>45596</v>
       </c>
       <c r="C53" s="9">
-        <v>438134.2</v>
+        <v>445104.9</v>
       </c>
       <c r="D53" s="9">
-        <v>48517.65</v>
+        <v>66159.85</v>
       </c>
       <c r="E53" s="10">
-        <v>6.95</v>
+        <v>6.988</v>
       </c>
       <c r="F53" s="10">
-        <v>12.6</v>
+        <v>12.5313</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B54" s="6">
-        <v>45565</v>
+        <v>45580</v>
       </c>
       <c r="C54" s="7">
-        <v>397590.45</v>
+        <v>438134.2</v>
       </c>
       <c r="D54" s="7">
-        <v>48447.9</v>
+        <v>48517.65</v>
       </c>
       <c r="E54" s="8">
-        <v>7.07</v>
+        <v>6.95</v>
       </c>
       <c r="F54" s="8">
-        <v>14.72</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B55" s="6">
-        <v>45550</v>
+        <v>45565</v>
       </c>
       <c r="C55" s="9">
-        <v>440945.45</v>
+        <v>397590.45</v>
       </c>
       <c r="D55" s="9">
-        <v>78418.6</v>
+        <v>48447.9</v>
       </c>
       <c r="E55" s="10">
-        <v>7.09</v>
+        <v>7.07</v>
       </c>
       <c r="F55" s="10">
-        <v>12.88</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B56" s="6">
-        <v>45535</v>
+        <v>45550</v>
       </c>
       <c r="C56" s="7">
-        <v>471121.5</v>
+        <v>440945.45</v>
       </c>
       <c r="D56" s="7">
-        <v>78270.05</v>
+        <v>78418.6</v>
       </c>
       <c r="E56" s="8">
-        <v>6.9</v>
+        <v>7.09</v>
       </c>
       <c r="F56" s="8">
-        <v>13.77</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B57" s="6">
-        <v>45519</v>
+        <v>45535</v>
       </c>
       <c r="C57" s="9">
-        <v>473153.85</v>
+        <v>471121.5</v>
       </c>
       <c r="D57" s="9">
-        <v>63925.5</v>
+        <v>78270.05</v>
       </c>
       <c r="E57" s="10">
-        <v>6.97</v>
+        <v>6.9</v>
       </c>
       <c r="F57" s="10">
-        <v>11.69</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B58" s="6">
-        <v>45504</v>
+        <v>45519</v>
       </c>
       <c r="C58" s="7">
-        <v>458911.05</v>
+        <v>473153.85</v>
       </c>
       <c r="D58" s="7">
-        <v>67966.95</v>
+        <v>63925.5</v>
       </c>
       <c r="E58" s="8">
-        <v>6.89</v>
+        <v>6.97</v>
       </c>
       <c r="F58" s="8">
-        <v>12.07</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B59" s="6">
-        <v>45488</v>
+        <v>45504</v>
       </c>
       <c r="C59" s="9">
-        <v>440818.85</v>
+        <v>458911.05</v>
       </c>
       <c r="D59" s="9">
-        <v>37452.1</v>
+        <v>67966.95</v>
       </c>
       <c r="E59" s="10">
-        <v>6.93</v>
+        <v>6.89</v>
       </c>
       <c r="F59" s="10">
-        <v>11.69</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B60" s="6">
-        <v>45473</v>
+        <v>45488</v>
       </c>
       <c r="C60" s="7">
-        <v>422447.45</v>
+        <v>440818.85</v>
       </c>
       <c r="D60" s="7">
-        <v>56023.85</v>
+        <v>37452.1</v>
       </c>
       <c r="E60" s="8">
-        <v>6.99</v>
+        <v>6.93</v>
       </c>
       <c r="F60" s="8">
-        <v>15.06</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B61" s="6">
-        <v>45458</v>
+        <v>45473</v>
       </c>
       <c r="C61" s="9">
-        <v>431100.55</v>
+        <v>422447.45</v>
       </c>
       <c r="D61" s="9">
-        <v>106920.7</v>
+        <v>56023.85</v>
       </c>
       <c r="E61" s="10">
-        <v>6.95</v>
+        <v>6.99</v>
       </c>
       <c r="F61" s="10">
-        <v>12.08</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B62" s="6">
-        <v>45443</v>
+        <v>45458</v>
       </c>
       <c r="C62" s="7">
-        <v>403970</v>
+        <v>431100.55</v>
       </c>
       <c r="D62" s="7">
-        <v>80921.75</v>
+        <v>106920.7</v>
       </c>
       <c r="E62" s="8">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
       <c r="F62" s="8">
-        <v>13.92</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B63" s="6">
-        <v>45427</v>
+        <v>45443</v>
       </c>
       <c r="C63" s="9">
-        <v>421150.9</v>
+        <v>403970</v>
       </c>
       <c r="D63" s="9">
-        <v>52596.55</v>
+        <v>80921.75</v>
       </c>
       <c r="E63" s="10">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="F63" s="10">
-        <v>11.96</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B64" s="6">
-        <v>45412</v>
+        <v>45427</v>
       </c>
       <c r="C64" s="7">
-        <v>411533.6</v>
+        <v>421150.9</v>
       </c>
       <c r="D64" s="7">
-        <v>60407.45</v>
+        <v>52596.55</v>
       </c>
       <c r="E64" s="8">
-        <v>6.89</v>
+        <v>7.06</v>
       </c>
       <c r="F64" s="8">
-        <v>12.59</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B65" s="6">
-        <v>45397</v>
+        <v>45412</v>
       </c>
       <c r="C65" s="9">
-        <v>397251</v>
+        <v>411533.6</v>
       </c>
       <c r="D65" s="9">
-        <v>23663</v>
+        <v>60407.45</v>
       </c>
       <c r="E65" s="10">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="F65" s="10">
-        <v>13.85</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B66" s="6">
-        <v>45382</v>
+        <v>45397</v>
       </c>
       <c r="C66" s="7">
-        <v>388559.2</v>
+        <v>397251</v>
       </c>
       <c r="D66" s="7">
-        <v>57334.1</v>
+        <v>23663</v>
       </c>
       <c r="E66" s="8">
-        <v>7.07</v>
+        <v>6.9</v>
       </c>
       <c r="F66" s="8">
-        <v>14.2</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B67" s="6">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c r="C67" s="9">
-        <v>406182.5</v>
+        <v>388559.2</v>
       </c>
       <c r="D67" s="9">
-        <v>93685.95</v>
+        <v>57334.1</v>
       </c>
       <c r="E67" s="10">
-        <v>7.09</v>
+        <v>7.07</v>
       </c>
       <c r="F67" s="10">
-        <v>13.92</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B68" s="6">
-        <v>45351</v>
+        <v>45366</v>
       </c>
       <c r="C68" s="7">
-        <v>408048.25</v>
+        <v>406182.5</v>
       </c>
       <c r="D68" s="7">
-        <v>82067.8</v>
+        <v>93685.95</v>
       </c>
       <c r="E68" s="8">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="F68" s="8">
-        <v>11.91</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B69" s="6">
-        <v>45337</v>
+        <v>45351</v>
       </c>
       <c r="C69" s="9">
-        <v>395262.1</v>
+        <v>408048.25</v>
       </c>
       <c r="D69" s="9">
-        <v>57899.85</v>
+        <v>82067.8</v>
       </c>
       <c r="E69" s="10">
-        <v>7.38</v>
+        <v>7.05</v>
       </c>
       <c r="F69" s="10">
-        <v>12.74</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B70" s="6">
-        <v>45322</v>
+        <v>45337</v>
       </c>
       <c r="C70" s="7">
-        <v>377707.2</v>
+        <v>395262.1</v>
       </c>
       <c r="D70" s="7">
-        <v>53532.05</v>
+        <v>57899.85</v>
       </c>
       <c r="E70" s="8">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="F70" s="8">
-        <v>14.74</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B71" s="6">
-        <v>45306</v>
+        <v>45322</v>
       </c>
       <c r="C71" s="9">
-        <v>378628.1</v>
+        <v>377707.2</v>
       </c>
       <c r="D71" s="9">
-        <v>34492.95</v>
+        <v>53532.05</v>
       </c>
       <c r="E71" s="10">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="F71" s="10">
-        <v>12.34</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B72" s="6">
-        <v>45291</v>
+        <v>45306</v>
       </c>
       <c r="C72" s="7">
-        <v>364181.25</v>
+        <v>378628.1</v>
       </c>
       <c r="D72" s="7">
-        <v>42874.35</v>
+        <v>34492.95</v>
       </c>
       <c r="E72" s="8">
-        <v>7.02</v>
+        <v>7.12</v>
       </c>
       <c r="F72" s="8">
-        <v>12.13</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B73" s="6">
-        <v>45275</v>
+        <v>45291</v>
       </c>
       <c r="C73" s="9">
-        <v>387266.65</v>
+        <v>364181.25</v>
       </c>
       <c r="D73" s="9">
-        <v>68393.55</v>
+        <v>42874.35</v>
       </c>
       <c r="E73" s="10">
-        <v>7.17</v>
+        <v>7.02</v>
       </c>
       <c r="F73" s="10">
-        <v>11.77</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B74" s="6">
-        <v>45260</v>
+        <v>45275</v>
       </c>
       <c r="C74" s="7">
-        <v>394967.95</v>
+        <v>387266.65</v>
       </c>
       <c r="D74" s="7">
-        <v>59808.25</v>
+        <v>68393.55</v>
       </c>
       <c r="E74" s="8">
-        <v>6.99</v>
+        <v>7.17</v>
       </c>
       <c r="F74" s="8">
-        <v>14.34</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B75" s="6">
-        <v>45245</v>
+        <v>45260</v>
       </c>
       <c r="C75" s="9">
-        <v>417630.65</v>
+        <v>394967.95</v>
       </c>
       <c r="D75" s="9">
-        <v>41107.05</v>
+        <v>59808.25</v>
       </c>
       <c r="E75" s="10">
-        <v>7.1</v>
+        <v>6.99</v>
       </c>
       <c r="F75" s="10">
-        <v>12</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B76" s="6">
-        <v>45230</v>
+        <v>45245</v>
       </c>
       <c r="C76" s="7">
-        <v>413685.3</v>
+        <v>417630.65</v>
       </c>
       <c r="D76" s="7">
-        <v>50039.65</v>
+        <v>41107.05</v>
       </c>
       <c r="E76" s="8">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F76" s="8">
-        <v>11.89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B77" s="6">
-        <v>45214</v>
+        <v>45230</v>
       </c>
       <c r="C77" s="9">
-        <v>418804.1</v>
+        <v>413685.3</v>
       </c>
       <c r="D77" s="9">
-        <v>25039.05</v>
+        <v>50039.65</v>
       </c>
       <c r="E77" s="10">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="F77" s="10">
-        <v>16.41</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B78" s="6">
-        <v>45199</v>
+        <v>45214</v>
       </c>
       <c r="C78" s="7">
-        <v>412234.35</v>
+        <v>418804.1</v>
       </c>
       <c r="D78" s="7">
-        <v>49675.85</v>
+        <v>25039.05</v>
       </c>
       <c r="E78" s="8">
-        <v>6.89</v>
+        <v>6.91</v>
       </c>
       <c r="F78" s="8">
-        <v>11.36</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B79" s="6">
-        <v>45184</v>
+        <v>45199</v>
       </c>
       <c r="C79" s="9">
-        <v>432568.65</v>
+        <v>412234.35</v>
       </c>
       <c r="D79" s="9">
-        <v>71469.15</v>
+        <v>49675.85</v>
       </c>
       <c r="E79" s="10">
-        <v>6.8429</v>
+        <v>6.89</v>
       </c>
       <c r="F79" s="10">
-        <v>12.5012</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B80" s="6">
-        <v>45169</v>
+        <v>45184</v>
       </c>
       <c r="C80" s="7">
-        <v>450064.05</v>
+        <v>432568.65</v>
       </c>
       <c r="D80" s="7">
-        <v>73816.05</v>
+        <v>71469.15</v>
       </c>
       <c r="E80" s="8">
-        <v>6.93</v>
+        <v>6.8429</v>
       </c>
       <c r="F80" s="8">
-        <v>16.55</v>
+        <v>12.5012</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B81" s="6">
-        <v>45153</v>
+        <v>45169</v>
       </c>
       <c r="C81" s="9">
-        <v>447570.85</v>
+        <v>450064.05</v>
       </c>
       <c r="D81" s="9">
-        <v>41800.2</v>
+        <v>73816.05</v>
       </c>
       <c r="E81" s="10">
-        <v>6.81</v>
+        <v>6.93</v>
       </c>
       <c r="F81" s="10">
-        <v>12.55</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B82" s="6">
-        <v>45138</v>
+        <v>45153</v>
       </c>
       <c r="C82" s="7">
-        <v>444567.6</v>
+        <v>447570.85</v>
       </c>
       <c r="D82" s="7">
-        <v>65987.7</v>
+        <v>41800.2</v>
       </c>
       <c r="E82" s="8">
-        <v>6.75</v>
+        <v>6.81</v>
       </c>
       <c r="F82" s="8">
-        <v>12.23</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B83" s="6">
-        <v>45122</v>
+        <v>45138</v>
       </c>
       <c r="C83" s="9">
-        <v>434827.8</v>
+        <v>444567.6</v>
       </c>
       <c r="D83" s="9">
-        <v>26230.4</v>
+        <v>65987.7</v>
       </c>
       <c r="E83" s="10">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="F83" s="10">
-        <v>13.1</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B84" s="6">
-        <v>45107</v>
+        <v>45122</v>
       </c>
       <c r="C84" s="7">
-        <v>433212.15</v>
+        <v>434827.8</v>
       </c>
       <c r="D84" s="7">
-        <v>67287.35</v>
+        <v>26230.4</v>
       </c>
       <c r="E84" s="8">
-        <v>6.77</v>
+        <v>6.72</v>
       </c>
       <c r="F84" s="8">
-        <v>12.37</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B85" s="6">
-        <v>45092</v>
+        <v>45107</v>
       </c>
       <c r="C85" s="9">
-        <v>446509.9</v>
+        <v>433212.15</v>
       </c>
       <c r="D85" s="9">
-        <v>83468.3</v>
+        <v>67287.35</v>
       </c>
       <c r="E85" s="10">
-        <v>6.7147</v>
+        <v>6.77</v>
       </c>
       <c r="F85" s="10">
-        <v>11.7971</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B86" s="6">
-        <v>45077</v>
+        <v>45092</v>
       </c>
       <c r="C86" s="7">
-        <v>433543.35</v>
+        <v>446509.9</v>
       </c>
       <c r="D86" s="7">
-        <v>81179.55</v>
+        <v>83468.3</v>
       </c>
       <c r="E86" s="8">
-        <v>6.7278</v>
+        <v>6.7147</v>
       </c>
       <c r="F86" s="8">
-        <v>16.3087</v>
+        <v>11.7971</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B87" s="6">
-        <v>45061</v>
+        <v>45077</v>
       </c>
       <c r="C87" s="9">
-        <v>421454.4</v>
+        <v>433543.35</v>
       </c>
       <c r="D87" s="9">
-        <v>37178.35</v>
+        <v>81179.55</v>
       </c>
       <c r="E87" s="10">
-        <v>7.008</v>
+        <v>6.7278</v>
       </c>
       <c r="F87" s="10">
-        <v>13.8402</v>
+        <v>16.3087</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B88" s="6">
-        <v>45046</v>
+        <v>45061</v>
       </c>
       <c r="C88" s="7">
-        <v>421736.55</v>
+        <v>421454.4</v>
       </c>
       <c r="D88" s="7">
-        <v>58226.95</v>
+        <v>37178.35</v>
       </c>
       <c r="E88" s="8">
-        <v>6.7506</v>
+        <v>7.008</v>
       </c>
       <c r="F88" s="8">
         <v>13.8402</v>
@@ -1706,16 +1706,16 @@
     </row>
     <row r="89" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B89" s="6">
-        <v>45031</v>
+        <v>45046</v>
       </c>
       <c r="C89" s="9">
-        <v>391420.9</v>
+        <v>421736.55</v>
       </c>
       <c r="D89" s="9">
-        <v>52791.25</v>
+        <v>58226.95</v>
       </c>
       <c r="E89" s="10">
-        <v>6.7336</v>
+        <v>6.7506</v>
       </c>
       <c r="F89" s="10">
         <v>13.8402</v>
@@ -1723,2447 +1723,2447 @@
     </row>
     <row r="90" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B90" s="6">
-        <v>45016</v>
+        <v>45031</v>
       </c>
       <c r="C90" s="7">
-        <v>353688.25</v>
+        <v>391420.9</v>
       </c>
       <c r="D90" s="7">
-        <v>61469.1</v>
+        <v>52791.25</v>
       </c>
       <c r="E90" s="8">
-        <v>6.88</v>
+        <v>6.7336</v>
       </c>
       <c r="F90" s="8">
-        <v>12.6725</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B91" s="6">
-        <v>45000</v>
+        <v>45016</v>
       </c>
       <c r="C91" s="9">
-        <v>371326.7</v>
+        <v>353688.25</v>
       </c>
       <c r="D91" s="9">
-        <v>65488.9</v>
+        <v>61469.1</v>
       </c>
       <c r="E91" s="10">
-        <v>6.924</v>
+        <v>6.88</v>
       </c>
       <c r="F91" s="10">
-        <v>10.7756</v>
+        <v>12.6725</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B92" s="6">
-        <v>44985</v>
+        <v>45000</v>
       </c>
       <c r="C92" s="7">
-        <v>364530.1</v>
+        <v>371326.7</v>
       </c>
       <c r="D92" s="7">
-        <v>58975.35</v>
+        <v>65488.9</v>
       </c>
       <c r="E92" s="8">
-        <v>6.7696</v>
+        <v>6.924</v>
       </c>
       <c r="F92" s="8">
-        <v>12.5107</v>
+        <v>10.7756</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B93" s="6">
-        <v>44972</v>
+        <v>44985</v>
       </c>
       <c r="C93" s="9">
-        <v>368908.25</v>
+        <v>364530.1</v>
       </c>
       <c r="D93" s="9">
-        <v>43347.15</v>
+        <v>58975.35</v>
       </c>
       <c r="E93" s="10">
-        <v>6.6951</v>
+        <v>6.7696</v>
       </c>
       <c r="F93" s="10">
-        <v>16.3087</v>
+        <v>12.5107</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B94" s="6">
-        <v>44957</v>
+        <v>44972</v>
       </c>
       <c r="C94" s="7">
-        <v>363889.15</v>
+        <v>368908.25</v>
       </c>
       <c r="D94" s="7">
-        <v>51481.6</v>
+        <v>43347.15</v>
       </c>
       <c r="E94" s="8">
-        <v>6.5562</v>
+        <v>6.6951</v>
       </c>
       <c r="F94" s="8">
-        <v>13.0958</v>
+        <v>16.3087</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B95" s="6">
-        <v>44941</v>
+        <v>44957</v>
       </c>
       <c r="C95" s="9">
-        <v>381154.85</v>
+        <v>363889.15</v>
       </c>
       <c r="D95" s="9">
-        <v>45026.9</v>
+        <v>51481.6</v>
       </c>
       <c r="E95" s="10">
-        <v>6.3659</v>
+        <v>6.5562</v>
       </c>
       <c r="F95" s="10">
-        <v>12.7452</v>
+        <v>13.0958</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B96" s="6">
-        <v>44926</v>
+        <v>44941</v>
       </c>
       <c r="C96" s="7">
-        <v>359673.3</v>
+        <v>381154.85</v>
       </c>
       <c r="D96" s="7">
-        <v>54575.6</v>
+        <v>45026.9</v>
       </c>
       <c r="E96" s="8">
-        <v>6.5777</v>
+        <v>6.3659</v>
       </c>
       <c r="F96" s="8">
-        <v>13.7499</v>
+        <v>12.7452</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B97" s="6">
-        <v>44910</v>
+        <v>44926</v>
       </c>
       <c r="C97" s="9">
-        <v>363736.15</v>
+        <v>359673.3</v>
       </c>
       <c r="D97" s="9">
-        <v>65701.7</v>
+        <v>54575.6</v>
       </c>
       <c r="E97" s="10">
-        <v>6.3406</v>
+        <v>6.5777</v>
       </c>
       <c r="F97" s="10">
-        <v>13.7489</v>
+        <v>13.7499</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B98" s="6">
-        <v>44895</v>
+        <v>44910</v>
       </c>
       <c r="C98" s="7">
-        <v>362307.65</v>
+        <v>363736.15</v>
       </c>
       <c r="D98" s="7">
-        <v>66918.15</v>
+        <v>65701.7</v>
       </c>
       <c r="E98" s="8">
-        <v>6.5013</v>
+        <v>6.3406</v>
       </c>
       <c r="F98" s="8">
-        <v>12.0126</v>
+        <v>13.7489</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B99" s="6">
-        <v>44880</v>
+        <v>44895</v>
       </c>
       <c r="C99" s="9">
-        <v>381455.7</v>
+        <v>362307.65</v>
       </c>
       <c r="D99" s="9">
-        <v>55158.95</v>
+        <v>66918.15</v>
       </c>
       <c r="E99" s="10">
-        <v>6.2147</v>
+        <v>6.5013</v>
       </c>
       <c r="F99" s="10">
-        <v>13.7767</v>
+        <v>12.0126</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B100" s="6">
-        <v>44865</v>
+        <v>44880</v>
       </c>
       <c r="C100" s="7">
-        <v>373332.25</v>
+        <v>381455.7</v>
       </c>
       <c r="D100" s="7">
-        <v>39745.2</v>
+        <v>55158.95</v>
       </c>
       <c r="E100" s="8">
-        <v>6.3976</v>
+        <v>6.2147</v>
       </c>
       <c r="F100" s="8">
-        <v>13.7196</v>
+        <v>13.7767</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B101" s="6">
-        <v>44849</v>
+        <v>44865</v>
       </c>
       <c r="C101" s="9">
-        <v>415849.4</v>
+        <v>373332.25</v>
       </c>
       <c r="D101" s="9">
-        <v>33906.35</v>
+        <v>39745.2</v>
       </c>
       <c r="E101" s="10">
-        <v>5.9234</v>
+        <v>6.3976</v>
       </c>
       <c r="F101" s="10">
-        <v>11.977</v>
+        <v>13.7196</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B102" s="6">
-        <v>44834</v>
+        <v>44849</v>
       </c>
       <c r="C102" s="7">
-        <v>400866.35</v>
+        <v>415849.4</v>
       </c>
       <c r="D102" s="7">
-        <v>62062.8</v>
+        <v>33906.35</v>
       </c>
       <c r="E102" s="8">
-        <v>5.9095</v>
+        <v>5.9234</v>
       </c>
       <c r="F102" s="8">
-        <v>12.2577</v>
+        <v>11.977</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B103" s="6">
-        <v>44819</v>
+        <v>44834</v>
       </c>
       <c r="C103" s="9">
-        <v>438644.65</v>
+        <v>400866.35</v>
       </c>
       <c r="D103" s="9">
-        <v>76371.55</v>
+        <v>62062.8</v>
       </c>
       <c r="E103" s="10">
-        <v>5.6552</v>
+        <v>5.9095</v>
       </c>
       <c r="F103" s="10">
-        <v>13.018</v>
+        <v>12.2577</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B104" s="6">
-        <v>44804</v>
+        <v>44819</v>
       </c>
       <c r="C104" s="7">
-        <v>410076.8</v>
+        <v>438644.65</v>
       </c>
       <c r="D104" s="7">
-        <v>87514.55</v>
+        <v>76371.55</v>
       </c>
       <c r="E104" s="8">
-        <v>5.6419</v>
+        <v>5.6552</v>
       </c>
       <c r="F104" s="8">
-        <v>13.658</v>
+        <v>13.018</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B105" s="6">
-        <v>44788</v>
+        <v>44804</v>
       </c>
       <c r="C105" s="9">
-        <v>411152.1</v>
+        <v>410076.8</v>
       </c>
       <c r="D105" s="9">
-        <v>63123.35</v>
+        <v>87514.55</v>
       </c>
       <c r="E105" s="10">
-        <v>5.5132</v>
+        <v>5.6419</v>
       </c>
       <c r="F105" s="10">
-        <v>13.6888</v>
+        <v>13.658</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B106" s="6">
-        <v>44773</v>
+        <v>44788</v>
       </c>
       <c r="C106" s="7">
-        <v>374226.45</v>
+        <v>411152.1</v>
       </c>
       <c r="D106" s="7">
-        <v>48380.15</v>
+        <v>63123.35</v>
       </c>
       <c r="E106" s="8">
-        <v>5.0497</v>
+        <v>5.5132</v>
       </c>
       <c r="F106" s="8">
-        <v>12.4036</v>
+        <v>13.6888</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B107" s="6">
-        <v>44757</v>
+        <v>44773</v>
       </c>
       <c r="C107" s="9">
-        <v>381468.7</v>
+        <v>374226.45</v>
       </c>
       <c r="D107" s="9">
-        <v>46218.5</v>
+        <v>48380.15</v>
       </c>
       <c r="E107" s="10">
-        <v>4.9454</v>
+        <v>5.0497</v>
       </c>
       <c r="F107" s="10">
-        <v>12.1283</v>
+        <v>12.4036</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B108" s="6">
-        <v>44742</v>
+        <v>44757</v>
       </c>
       <c r="C108" s="7">
-        <v>372542.35</v>
+        <v>381468.7</v>
       </c>
       <c r="D108" s="7">
-        <v>67595.3</v>
+        <v>46218.5</v>
       </c>
       <c r="E108" s="8">
-        <v>4.8837</v>
+        <v>4.9454</v>
       </c>
       <c r="F108" s="8">
-        <v>12.3782</v>
+        <v>12.1283</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B109" s="6">
-        <v>44727</v>
+        <v>44742</v>
       </c>
       <c r="C109" s="9">
-        <v>389282</v>
+        <v>372542.35</v>
       </c>
       <c r="D109" s="9">
-        <v>55172.75</v>
+        <v>67595.3</v>
       </c>
       <c r="E109" s="10">
-        <v>4.6892</v>
+        <v>4.8837</v>
       </c>
       <c r="F109" s="10">
-        <v>13.5229</v>
+        <v>12.3782</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B110" s="6">
-        <v>44712</v>
+        <v>44727</v>
       </c>
       <c r="C110" s="7">
-        <v>384544</v>
+        <v>389282</v>
       </c>
       <c r="D110" s="7">
-        <v>72437.6</v>
+        <v>55172.75</v>
       </c>
       <c r="E110" s="8">
-        <v>4.4817</v>
+        <v>4.6892</v>
       </c>
       <c r="F110" s="8">
-        <v>12.305</v>
+        <v>13.5229</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B111" s="6">
-        <v>44696</v>
+        <v>44712</v>
       </c>
       <c r="C111" s="9">
-        <v>384417.4</v>
+        <v>384544</v>
       </c>
       <c r="D111" s="9">
-        <v>44342.95</v>
+        <v>72437.6</v>
       </c>
       <c r="E111" s="10">
-        <v>3.9101</v>
+        <v>4.4817</v>
       </c>
       <c r="F111" s="10">
-        <v>10.5891</v>
+        <v>12.305</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B112" s="6">
-        <v>44681</v>
+        <v>44696</v>
       </c>
       <c r="C112" s="7">
-        <v>364999.65</v>
+        <v>384417.4</v>
       </c>
       <c r="D112" s="7">
-        <v>64930.35</v>
+        <v>44342.95</v>
       </c>
       <c r="E112" s="8">
-        <v>3.7706</v>
+        <v>3.9101</v>
       </c>
       <c r="F112" s="8">
-        <v>13.4069</v>
+        <v>10.5891</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B113" s="6">
-        <v>44666</v>
+        <v>44681</v>
       </c>
       <c r="C113" s="9">
-        <v>351642.1</v>
+        <v>364999.65</v>
       </c>
       <c r="D113" s="9">
-        <v>43499.3</v>
+        <v>64930.35</v>
       </c>
       <c r="E113" s="10">
-        <v>3.7011</v>
+        <v>3.7706</v>
       </c>
       <c r="F113" s="10">
-        <v>12.1102</v>
+        <v>13.4069</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B114" s="6">
-        <v>44651</v>
+        <v>44666</v>
       </c>
       <c r="C114" s="7">
-        <v>352292.55</v>
+        <v>351642.1</v>
       </c>
       <c r="D114" s="7">
-        <v>71015.75</v>
+        <v>43499.3</v>
       </c>
       <c r="E114" s="8">
-        <v>3.7934</v>
+        <v>3.7011</v>
       </c>
       <c r="F114" s="8">
-        <v>12.1707</v>
+        <v>12.1102</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B115" s="6">
-        <v>44635</v>
+        <v>44651</v>
       </c>
       <c r="C115" s="9">
-        <v>368090.45</v>
+        <v>352292.55</v>
       </c>
       <c r="D115" s="9">
-        <v>44531.6</v>
+        <v>71015.75</v>
       </c>
       <c r="E115" s="10">
-        <v>3.8395</v>
+        <v>3.7934</v>
       </c>
       <c r="F115" s="10">
-        <v>12.1463</v>
+        <v>12.1707</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B116" s="6">
-        <v>44620</v>
+        <v>44635</v>
       </c>
       <c r="C116" s="7">
-        <v>364645.3</v>
+        <v>368090.45</v>
       </c>
       <c r="D116" s="7">
-        <v>44435.25</v>
+        <v>44531.6</v>
       </c>
       <c r="E116" s="8">
-        <v>3.6362</v>
+        <v>3.8395</v>
       </c>
       <c r="F116" s="8">
-        <v>11.5076</v>
+        <v>12.1463</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B117" s="6">
-        <v>44607</v>
+        <v>44620</v>
       </c>
       <c r="C117" s="9">
-        <v>389950.7</v>
+        <v>364645.3</v>
       </c>
       <c r="D117" s="9">
-        <v>64232.7</v>
+        <v>44435.25</v>
       </c>
       <c r="E117" s="10">
-        <v>3.6696</v>
+        <v>3.6362</v>
       </c>
       <c r="F117" s="10">
-        <v>12.287</v>
+        <v>11.5076</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B118" s="6">
-        <v>44592</v>
+        <v>44607</v>
       </c>
       <c r="C118" s="7">
-        <v>395881</v>
+        <v>389950.7</v>
       </c>
       <c r="D118" s="7">
-        <v>71201.95</v>
+        <v>64232.7</v>
       </c>
       <c r="E118" s="8">
-        <v>3.4721</v>
+        <v>3.6696</v>
       </c>
       <c r="F118" s="8">
-        <v>12.3176</v>
+        <v>12.287</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B119" s="6">
-        <v>44576</v>
+        <v>44592</v>
       </c>
       <c r="C119" s="9">
-        <v>386159.9</v>
+        <v>395881</v>
       </c>
       <c r="D119" s="9">
-        <v>64665.3</v>
+        <v>71201.95</v>
       </c>
       <c r="E119" s="10">
-        <v>3.3928</v>
+        <v>3.4721</v>
       </c>
       <c r="F119" s="10">
-        <v>13.4516</v>
+        <v>12.3176</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B120" s="6">
-        <v>44561</v>
+        <v>44576</v>
       </c>
       <c r="C120" s="7">
-        <v>350068.65</v>
+        <v>386159.9</v>
       </c>
       <c r="D120" s="7">
-        <v>87182.55</v>
+        <v>64665.3</v>
       </c>
       <c r="E120" s="8">
-        <v>3.4962</v>
+        <v>3.3928</v>
       </c>
       <c r="F120" s="8">
-        <v>12.305</v>
+        <v>13.4516</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B121" s="6">
-        <v>44545</v>
+        <v>44561</v>
       </c>
       <c r="C121" s="9">
-        <v>446975.4</v>
+        <v>350068.65</v>
       </c>
       <c r="D121" s="9">
-        <v>161701.6</v>
+        <v>87182.55</v>
       </c>
       <c r="E121" s="10">
-        <v>3.3841</v>
+        <v>3.4962</v>
       </c>
       <c r="F121" s="10">
-        <v>12.3439</v>
+        <v>12.305</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B122" s="6">
-        <v>44530</v>
+        <v>44545</v>
       </c>
       <c r="C122" s="7">
-        <v>388363.05</v>
+        <v>446975.4</v>
       </c>
       <c r="D122" s="7">
-        <v>115234.25</v>
+        <v>161701.6</v>
       </c>
       <c r="E122" s="8">
-        <v>3.3804</v>
+        <v>3.3841</v>
       </c>
       <c r="F122" s="8">
-        <v>12.763</v>
+        <v>12.3439</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B123" s="6">
-        <v>44515</v>
+        <v>44530</v>
       </c>
       <c r="C123" s="9">
-        <v>450890.7</v>
+        <v>388363.05</v>
       </c>
       <c r="D123" s="9">
-        <v>172504</v>
+        <v>115234.25</v>
       </c>
       <c r="E123" s="10">
         <v>3.3804</v>
       </c>
       <c r="F123" s="10">
-        <v>10.4429</v>
+        <v>12.763</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B124" s="6">
-        <v>44500</v>
+        <v>44515</v>
       </c>
       <c r="C124" s="7">
-        <v>379278.3</v>
+        <v>450890.7</v>
       </c>
       <c r="D124" s="7">
-        <v>56178.95</v>
+        <v>172504</v>
       </c>
       <c r="E124" s="8">
-        <v>3.3194</v>
+        <v>3.3804</v>
       </c>
       <c r="F124" s="8">
-        <v>12.7106</v>
+        <v>10.4429</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B125" s="6">
-        <v>44484</v>
+        <v>44500</v>
       </c>
       <c r="C125" s="9">
-        <v>399720.05</v>
+        <v>379278.3</v>
       </c>
       <c r="D125" s="9">
-        <v>55664.1</v>
+        <v>56178.95</v>
       </c>
       <c r="E125" s="10">
-        <v>3.3841</v>
+        <v>3.3194</v>
       </c>
       <c r="F125" s="10">
-        <v>8.4664</v>
+        <v>12.7106</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B126" s="6">
-        <v>44469</v>
+        <v>44484</v>
       </c>
       <c r="C126" s="7">
-        <v>370982.1</v>
+        <v>399720.05</v>
       </c>
       <c r="D126" s="7">
-        <v>59167.05</v>
+        <v>55664.1</v>
       </c>
       <c r="E126" s="8">
-        <v>3.2589</v>
+        <v>3.3841</v>
       </c>
       <c r="F126" s="8">
-        <v>12.8346</v>
+        <v>8.4664</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B127" s="6">
-        <v>44454</v>
+        <v>44469</v>
       </c>
       <c r="C127" s="9">
-        <v>401221.25</v>
+        <v>370982.1</v>
       </c>
       <c r="D127" s="9">
-        <v>74402.55</v>
+        <v>59167.05</v>
       </c>
       <c r="E127" s="10">
-        <v>3.144</v>
+        <v>3.2589</v>
       </c>
       <c r="F127" s="10">
-        <v>13.4184</v>
+        <v>12.8346</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B128" s="6">
-        <v>44439</v>
+        <v>44454</v>
       </c>
       <c r="C128" s="7">
-        <v>391504.85</v>
+        <v>401221.25</v>
       </c>
       <c r="D128" s="7">
-        <v>73288.65</v>
+        <v>74402.55</v>
       </c>
       <c r="E128" s="8">
-        <v>3.1474</v>
+        <v>3.144</v>
       </c>
       <c r="F128" s="8">
-        <v>12.8346</v>
+        <v>13.4184</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B129" s="6">
-        <v>44423</v>
+        <v>44439</v>
       </c>
       <c r="C129" s="9">
-        <v>419726</v>
+        <v>391504.85</v>
       </c>
       <c r="D129" s="9">
-        <v>148470.35</v>
+        <v>73288.65</v>
       </c>
       <c r="E129" s="10">
-        <v>3.2558</v>
+        <v>3.1474</v>
       </c>
       <c r="F129" s="10">
-        <v>12.0106</v>
+        <v>12.8346</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B130" s="6">
-        <v>44408</v>
+        <v>44423</v>
       </c>
       <c r="C130" s="7">
-        <v>414981.65</v>
+        <v>419726</v>
       </c>
       <c r="D130" s="7">
-        <v>149052.15</v>
+        <v>148470.35</v>
       </c>
       <c r="E130" s="8">
-        <v>3.3811</v>
+        <v>3.2558</v>
       </c>
       <c r="F130" s="8">
-        <v>12.9355</v>
+        <v>12.0106</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B131" s="6">
-        <v>44392</v>
+        <v>44408</v>
       </c>
       <c r="C131" s="9">
-        <v>471218</v>
+        <v>414981.65</v>
       </c>
       <c r="D131" s="9">
-        <v>117197.2</v>
+        <v>149052.15</v>
       </c>
       <c r="E131" s="10">
-        <v>3.3185</v>
+        <v>3.3811</v>
       </c>
       <c r="F131" s="10">
-        <v>12.7989</v>
+        <v>12.9355</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B132" s="6">
-        <v>44377</v>
+        <v>44392</v>
       </c>
       <c r="C132" s="7">
-        <v>376117.85</v>
+        <v>471218</v>
       </c>
       <c r="D132" s="7">
-        <v>97928</v>
+        <v>117197.2</v>
       </c>
       <c r="E132" s="8">
-        <v>3.4306</v>
+        <v>3.3185</v>
       </c>
       <c r="F132" s="8">
-        <v>13.0317</v>
+        <v>12.7989</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B133" s="6">
-        <v>44362</v>
+        <v>44377</v>
       </c>
       <c r="C133" s="9">
-        <v>404804.9</v>
+        <v>376117.85</v>
       </c>
       <c r="D133" s="9">
-        <v>73440.4</v>
+        <v>97928</v>
       </c>
       <c r="E133" s="10">
-        <v>3.3641</v>
+        <v>3.4306</v>
       </c>
       <c r="F133" s="10">
-        <v>11.3226</v>
+        <v>13.0317</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B134" s="6">
-        <v>44347</v>
+        <v>44362</v>
       </c>
       <c r="C134" s="7">
-        <v>388707.25</v>
+        <v>404804.9</v>
       </c>
       <c r="D134" s="7">
-        <v>61593.9</v>
+        <v>73440.4</v>
       </c>
       <c r="E134" s="8">
-        <v>3.3628</v>
+        <v>3.3641</v>
       </c>
       <c r="F134" s="8">
-        <v>12.8666</v>
+        <v>11.3226</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B135" s="6">
-        <v>44331</v>
+        <v>44347</v>
       </c>
       <c r="C135" s="9">
-        <v>404445.55</v>
+        <v>388707.25</v>
       </c>
       <c r="D135" s="9">
-        <v>66560.6</v>
+        <v>61593.9</v>
       </c>
       <c r="E135" s="10">
-        <v>3.1892</v>
+        <v>3.3628</v>
       </c>
       <c r="F135" s="10">
-        <v>11.6903</v>
+        <v>12.8666</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B136" s="6">
-        <v>44316</v>
+        <v>44331</v>
       </c>
       <c r="C136" s="7">
-        <v>374846.75</v>
+        <v>404445.55</v>
       </c>
       <c r="D136" s="7">
-        <v>53838.6</v>
+        <v>66560.6</v>
       </c>
       <c r="E136" s="8">
-        <v>3.2054</v>
+        <v>3.1892</v>
       </c>
       <c r="F136" s="8">
-        <v>13.0225</v>
+        <v>11.6903</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B137" s="6">
-        <v>44301</v>
+        <v>44316</v>
       </c>
       <c r="C137" s="9">
-        <v>382838.15</v>
+        <v>374846.75</v>
       </c>
       <c r="D137" s="9">
-        <v>35737.15</v>
+        <v>53838.6</v>
       </c>
       <c r="E137" s="10">
-        <v>3.1654</v>
+        <v>3.2054</v>
       </c>
       <c r="F137" s="10">
-        <v>13.0885</v>
+        <v>13.0225</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B138" s="6">
-        <v>44286</v>
+        <v>44301</v>
       </c>
       <c r="C138" s="7">
-        <v>364374.3</v>
+        <v>382838.15</v>
       </c>
       <c r="D138" s="7">
-        <v>96417.25</v>
+        <v>35737.15</v>
       </c>
       <c r="E138" s="8">
-        <v>3.3227</v>
+        <v>3.1654</v>
       </c>
       <c r="F138" s="8">
-        <v>13.3656</v>
+        <v>13.0885</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B139" s="6">
-        <v>44270</v>
+        <v>44286</v>
       </c>
       <c r="C139" s="9">
-        <v>403442.7</v>
+        <v>364374.3</v>
       </c>
       <c r="D139" s="9">
-        <v>127121</v>
+        <v>96417.25</v>
       </c>
       <c r="E139" s="10">
-        <v>3.1644</v>
+        <v>3.3227</v>
       </c>
       <c r="F139" s="10">
-        <v>12.5153</v>
+        <v>13.3656</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B140" s="6">
-        <v>44255</v>
+        <v>44270</v>
       </c>
       <c r="C140" s="7">
-        <v>390852.95</v>
+        <v>403442.7</v>
       </c>
       <c r="D140" s="7">
-        <v>69500.35</v>
+        <v>127121</v>
       </c>
       <c r="E140" s="8">
-        <v>3.0973</v>
+        <v>3.1644</v>
       </c>
       <c r="F140" s="8">
-        <v>12.5962</v>
+        <v>12.5153</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B141" s="6">
-        <v>44242</v>
+        <v>44255</v>
       </c>
       <c r="C141" s="9">
-        <v>399404</v>
+        <v>390852.95</v>
       </c>
       <c r="D141" s="9">
-        <v>88216.1</v>
+        <v>69500.35</v>
       </c>
       <c r="E141" s="10">
-        <v>3.2181</v>
+        <v>3.0973</v>
       </c>
       <c r="F141" s="10">
-        <v>13.5159</v>
+        <v>12.5962</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B142" s="6">
-        <v>44227</v>
+        <v>44242</v>
       </c>
       <c r="C142" s="7">
-        <v>410651.9</v>
+        <v>399404</v>
       </c>
       <c r="D142" s="7">
-        <v>89040.6</v>
+        <v>88216.1</v>
       </c>
       <c r="E142" s="8">
-        <v>3.1755</v>
+        <v>3.2181</v>
       </c>
       <c r="F142" s="8">
-        <v>11.3224</v>
+        <v>13.5159</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B143" s="6">
-        <v>44211</v>
+        <v>44227</v>
       </c>
       <c r="C143" s="9">
-        <v>386216.3</v>
+        <v>410651.9</v>
       </c>
       <c r="D143" s="9">
-        <v>49901.8</v>
+        <v>89040.6</v>
       </c>
       <c r="E143" s="10">
-        <v>2.9409</v>
+        <v>3.1755</v>
       </c>
       <c r="F143" s="10">
-        <v>8.5297</v>
+        <v>11.3224</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B144" s="6">
-        <v>44196</v>
+        <v>44211</v>
       </c>
       <c r="C144" s="7">
-        <v>365185.05</v>
+        <v>386216.3</v>
       </c>
       <c r="D144" s="7">
-        <v>87488.25</v>
+        <v>49901.8</v>
       </c>
       <c r="E144" s="8">
-        <v>3.0585</v>
+        <v>2.9409</v>
       </c>
       <c r="F144" s="8">
-        <v>12.7323</v>
+        <v>8.5297</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B145" s="6">
-        <v>44180</v>
+        <v>44196</v>
       </c>
       <c r="C145" s="9">
-        <v>390613.25</v>
+        <v>365185.05</v>
       </c>
       <c r="D145" s="9">
-        <v>102307.55</v>
+        <v>87488.25</v>
       </c>
       <c r="E145" s="10">
-        <v>2.6489</v>
+        <v>3.0585</v>
       </c>
       <c r="F145" s="10">
-        <v>12.6137</v>
+        <v>12.7323</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B146" s="6">
-        <v>44165</v>
+        <v>44180</v>
       </c>
       <c r="C146" s="7">
-        <v>373146.1</v>
+        <v>390613.25</v>
       </c>
       <c r="D146" s="7">
-        <v>64386.2</v>
+        <v>102307.55</v>
       </c>
       <c r="E146" s="8">
-        <v>2.7862</v>
+        <v>2.6489</v>
       </c>
       <c r="F146" s="8">
-        <v>8.8025</v>
+        <v>12.6137</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B147" s="6">
-        <v>44150</v>
+        <v>44165</v>
       </c>
       <c r="C147" s="9">
-        <v>389427.1</v>
+        <v>373146.1</v>
       </c>
       <c r="D147" s="9">
-        <v>57001.85</v>
+        <v>64386.2</v>
       </c>
       <c r="E147" s="10">
-        <v>3.0869</v>
+        <v>2.7862</v>
       </c>
       <c r="F147" s="10">
-        <v>11.3224</v>
+        <v>8.8025</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B148" s="6">
-        <v>44135</v>
+        <v>44150</v>
       </c>
       <c r="C148" s="7">
-        <v>380112.2</v>
+        <v>389427.1</v>
       </c>
       <c r="D148" s="7">
-        <v>40838.65</v>
+        <v>57001.85</v>
       </c>
       <c r="E148" s="8">
-        <v>3.1924</v>
+        <v>3.0869</v>
       </c>
       <c r="F148" s="8">
-        <v>14.1936</v>
+        <v>11.3224</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B149" s="6">
-        <v>44119</v>
+        <v>44135</v>
       </c>
       <c r="C149" s="9">
-        <v>395015.55</v>
+        <v>380112.2</v>
       </c>
       <c r="D149" s="9">
-        <v>81950.2</v>
+        <v>40838.65</v>
       </c>
       <c r="E149" s="10">
-        <v>3.248</v>
+        <v>3.1924</v>
       </c>
       <c r="F149" s="10">
-        <v>11.9438</v>
+        <v>14.1936</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B150" s="6">
-        <v>44104</v>
+        <v>44119</v>
       </c>
       <c r="C150" s="7">
-        <v>362310.1</v>
+        <v>395015.55</v>
       </c>
       <c r="D150" s="7">
-        <v>86727.4</v>
+        <v>81950.2</v>
       </c>
       <c r="E150" s="8">
-        <v>3.3215</v>
+        <v>3.248</v>
       </c>
       <c r="F150" s="8">
-        <v>11.8636</v>
+        <v>11.9438</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B151" s="6">
-        <v>44089</v>
+        <v>44104</v>
       </c>
       <c r="C151" s="9">
-        <v>418270.55</v>
+        <v>362310.1</v>
       </c>
       <c r="D151" s="9">
-        <v>106924.35</v>
+        <v>86727.4</v>
       </c>
       <c r="E151" s="10">
-        <v>3.1042</v>
+        <v>3.3215</v>
       </c>
       <c r="F151" s="10">
-        <v>8.8698</v>
+        <v>11.8636</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B152" s="6">
-        <v>44074</v>
+        <v>44089</v>
       </c>
       <c r="C152" s="7">
-        <v>372600.8</v>
+        <v>418270.55</v>
       </c>
       <c r="D152" s="7">
-        <v>68405.75</v>
+        <v>106924.35</v>
       </c>
       <c r="E152" s="8">
-        <v>3.1738</v>
+        <v>3.1042</v>
       </c>
       <c r="F152" s="8">
-        <v>13.1447</v>
+        <v>8.8698</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B153" s="6">
-        <v>44058</v>
+        <v>44074</v>
       </c>
       <c r="C153" s="9">
-        <v>380587.65</v>
+        <v>372600.8</v>
       </c>
       <c r="D153" s="9">
-        <v>61152</v>
+        <v>68405.75</v>
       </c>
       <c r="E153" s="10">
-        <v>3.3135</v>
+        <v>3.1738</v>
       </c>
       <c r="F153" s="10">
-        <v>11.7895</v>
+        <v>13.1447</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B154" s="6">
-        <v>44043</v>
+        <v>44058</v>
       </c>
       <c r="C154" s="7">
-        <v>374817.2</v>
+        <v>380587.65</v>
       </c>
       <c r="D154" s="7">
-        <v>53608.1</v>
+        <v>61152</v>
       </c>
       <c r="E154" s="8">
-        <v>3.1755</v>
+        <v>3.3135</v>
       </c>
       <c r="F154" s="8">
-        <v>12.3297</v>
+        <v>11.7895</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B155" s="6">
-        <v>44027</v>
+        <v>44043</v>
       </c>
       <c r="C155" s="9">
-        <v>402660.5</v>
+        <v>374817.2</v>
       </c>
       <c r="D155" s="9">
-        <v>37730.15</v>
+        <v>53608.1</v>
       </c>
       <c r="E155" s="10">
-        <v>2.9774</v>
+        <v>3.1755</v>
       </c>
       <c r="F155" s="10">
-        <v>12.0382</v>
+        <v>12.3297</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B156" s="6">
-        <v>44012</v>
+        <v>44027</v>
       </c>
       <c r="C156" s="7">
-        <v>391482.3</v>
+        <v>402660.5</v>
       </c>
       <c r="D156" s="7">
-        <v>56270.85</v>
+        <v>37730.15</v>
       </c>
       <c r="E156" s="8">
-        <v>3.1848</v>
+        <v>2.9774</v>
       </c>
       <c r="F156" s="8">
-        <v>13.3542</v>
+        <v>12.0382</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B157" s="6">
-        <v>43997</v>
+        <v>44012</v>
       </c>
       <c r="C157" s="9">
-        <v>413652.4</v>
+        <v>391482.3</v>
       </c>
       <c r="D157" s="9">
-        <v>68691.7</v>
+        <v>56270.85</v>
       </c>
       <c r="E157" s="10">
-        <v>3.3126</v>
+        <v>3.1848</v>
       </c>
       <c r="F157" s="10">
-        <v>13.1138</v>
+        <v>13.3542</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B158" s="6">
-        <v>43982</v>
+        <v>43997</v>
       </c>
       <c r="C158" s="7">
-        <v>425817</v>
+        <v>413652.4</v>
       </c>
       <c r="D158" s="7">
-        <v>52155.65</v>
+        <v>68691.7</v>
       </c>
       <c r="E158" s="8">
-        <v>3.1259</v>
+        <v>3.3126</v>
       </c>
       <c r="F158" s="8">
-        <v>12.1381</v>
+        <v>13.1138</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B159" s="6">
-        <v>43966</v>
+        <v>43982</v>
       </c>
       <c r="C159" s="9">
-        <v>433624.85</v>
+        <v>425817</v>
       </c>
       <c r="D159" s="9">
-        <v>62636.85</v>
+        <v>52155.65</v>
       </c>
       <c r="E159" s="10">
-        <v>3.8329</v>
+        <v>3.1259</v>
       </c>
       <c r="F159" s="10">
-        <v>12.6933</v>
+        <v>12.1381</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B160" s="6">
-        <v>43951</v>
+        <v>43966</v>
       </c>
       <c r="C160" s="7">
-        <v>417227.05</v>
+        <v>433624.85</v>
       </c>
       <c r="D160" s="7">
-        <v>77889.2</v>
+        <v>62636.85</v>
       </c>
       <c r="E160" s="8">
-        <v>3.7778</v>
+        <v>3.8329</v>
       </c>
       <c r="F160" s="8">
-        <v>10.4458</v>
+        <v>12.6933</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B161" s="6">
-        <v>43936</v>
+        <v>43951</v>
       </c>
       <c r="C161" s="9">
-        <v>381273.5</v>
+        <v>417227.05</v>
       </c>
       <c r="D161" s="9">
-        <v>54770.55</v>
+        <v>77889.2</v>
       </c>
       <c r="E161" s="10">
-        <v>4.5516</v>
+        <v>3.7778</v>
       </c>
       <c r="F161" s="10">
-        <v>9.8995</v>
+        <v>10.4458</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B162" s="6">
-        <v>43921</v>
+        <v>43936</v>
       </c>
       <c r="C162" s="7">
-        <v>344526.95</v>
+        <v>381273.5</v>
       </c>
       <c r="D162" s="7">
-        <v>63166.1</v>
+        <v>54770.55</v>
       </c>
       <c r="E162" s="8">
-        <v>4.8781</v>
+        <v>4.5516</v>
       </c>
       <c r="F162" s="8">
-        <v>12.3855</v>
+        <v>9.8995</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B163" s="6">
-        <v>43905</v>
+        <v>43921</v>
       </c>
       <c r="C163" s="9">
-        <v>401724.55</v>
+        <v>344526.95</v>
       </c>
       <c r="D163" s="9">
-        <v>148273.3</v>
+        <v>63166.1</v>
       </c>
       <c r="E163" s="10">
-        <v>5.0083</v>
+        <v>4.8781</v>
       </c>
       <c r="F163" s="10">
-        <v>13.9511</v>
+        <v>12.3855</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B164" s="6">
-        <v>43890</v>
+        <v>43905</v>
       </c>
       <c r="C164" s="7">
-        <v>400200.25</v>
+        <v>401724.55</v>
       </c>
       <c r="D164" s="7">
-        <v>56287.5</v>
+        <v>148273.3</v>
       </c>
       <c r="E164" s="8">
-        <v>5.1087</v>
+        <v>5.0083</v>
       </c>
       <c r="F164" s="8">
-        <v>13.4489</v>
+        <v>13.9511</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B165" s="6">
-        <v>43876</v>
+        <v>43890</v>
       </c>
       <c r="C165" s="9">
-        <v>435803.25</v>
+        <v>400200.25</v>
       </c>
       <c r="D165" s="9">
-        <v>84356.4</v>
+        <v>56287.5</v>
       </c>
       <c r="E165" s="10">
-        <v>5.1064</v>
+        <v>5.1087</v>
       </c>
       <c r="F165" s="10">
-        <v>12.5282</v>
+        <v>13.4489</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B166" s="6">
-        <v>43861</v>
+        <v>43876</v>
       </c>
       <c r="C166" s="7">
-        <v>421988.85</v>
+        <v>435803.25</v>
       </c>
       <c r="D166" s="7">
-        <v>72673.75</v>
+        <v>84356.4</v>
       </c>
       <c r="E166" s="8">
-        <v>5.1171</v>
+        <v>5.1064</v>
       </c>
       <c r="F166" s="8">
-        <v>13.0458</v>
+        <v>12.5282</v>
       </c>
     </row>
     <row r="167" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B167" s="6">
-        <v>43845</v>
+        <v>43861</v>
       </c>
       <c r="C167" s="9">
-        <v>434895.3</v>
+        <v>421988.85</v>
       </c>
       <c r="D167" s="9">
-        <v>37801.8</v>
+        <v>72673.75</v>
       </c>
       <c r="E167" s="10">
-        <v>4.745</v>
+        <v>5.1171</v>
       </c>
       <c r="F167" s="10">
-        <v>14.2879</v>
+        <v>13.0458</v>
       </c>
     </row>
     <row r="168" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B168" s="6">
-        <v>43830</v>
+        <v>43845</v>
       </c>
       <c r="C168" s="7">
-        <v>414906.3</v>
+        <v>434895.3</v>
       </c>
       <c r="D168" s="7">
-        <v>83567.75</v>
+        <v>37801.8</v>
       </c>
       <c r="E168" s="8">
-        <v>4.9939</v>
+        <v>4.745</v>
       </c>
       <c r="F168" s="8">
-        <v>13.1778</v>
+        <v>14.2879</v>
       </c>
     </row>
     <row r="169" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B169" s="6">
-        <v>43814</v>
+        <v>43830</v>
       </c>
       <c r="C169" s="9">
-        <v>457213.55</v>
+        <v>414906.3</v>
       </c>
       <c r="D169" s="9">
-        <v>97114</v>
+        <v>83567.75</v>
       </c>
       <c r="E169" s="10">
-        <v>4.8781</v>
+        <v>4.9939</v>
       </c>
       <c r="F169" s="10">
-        <v>12.6487</v>
+        <v>13.1778</v>
       </c>
     </row>
     <row r="170" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B170" s="6">
-        <v>43799</v>
+        <v>43814</v>
       </c>
       <c r="C170" s="7">
-        <v>458415.6</v>
+        <v>457213.55</v>
       </c>
       <c r="D170" s="7">
-        <v>80022.9</v>
+        <v>97114</v>
       </c>
       <c r="E170" s="8">
-        <v>5.0065</v>
+        <v>4.8781</v>
       </c>
       <c r="F170" s="8">
-        <v>13.299</v>
+        <v>12.6487</v>
       </c>
     </row>
     <row r="171" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B171" s="6">
-        <v>43784</v>
+        <v>43799</v>
       </c>
       <c r="C171" s="9">
-        <v>461813.4</v>
+        <v>458415.6</v>
       </c>
       <c r="D171" s="9">
-        <v>94360.65</v>
+        <v>80022.9</v>
       </c>
       <c r="E171" s="10">
-        <v>4.78</v>
+        <v>5.0065</v>
       </c>
       <c r="F171" s="10">
-        <v>13.23</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="172" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B172" s="6">
-        <v>43769</v>
+        <v>43784</v>
       </c>
       <c r="C172" s="7">
-        <v>462308.75</v>
+        <v>461813.4</v>
       </c>
       <c r="D172" s="7">
-        <v>80459.45</v>
+        <v>94360.65</v>
       </c>
       <c r="E172" s="8">
-        <v>5.027</v>
+        <v>4.78</v>
       </c>
       <c r="F172" s="8">
-        <v>14.0802</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="173" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B173" s="6">
-        <v>43753</v>
+        <v>43769</v>
       </c>
       <c r="C173" s="9">
-        <v>486121.25</v>
+        <v>462308.75</v>
       </c>
       <c r="D173" s="9">
-        <v>106083.5</v>
+        <v>80459.45</v>
       </c>
       <c r="E173" s="10">
-        <v>5.1879</v>
+        <v>5.027</v>
       </c>
       <c r="F173" s="10">
-        <v>13.2197</v>
+        <v>14.0802</v>
       </c>
     </row>
     <row r="174" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B174" s="6">
-        <v>43738</v>
+        <v>43753</v>
       </c>
       <c r="C174" s="7">
-        <v>459742.1</v>
+        <v>486121.25</v>
       </c>
       <c r="D174" s="7">
-        <v>94892.9</v>
+        <v>106083.5</v>
       </c>
       <c r="E174" s="8">
-        <v>5.2989</v>
+        <v>5.1879</v>
       </c>
       <c r="F174" s="8">
-        <v>11.9925</v>
+        <v>13.2197</v>
       </c>
     </row>
     <row r="175" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B175" s="6">
-        <v>43723</v>
+        <v>43738</v>
       </c>
       <c r="C175" s="9">
-        <v>506326.9</v>
+        <v>459742.1</v>
       </c>
       <c r="D175" s="9">
-        <v>71069.7</v>
+        <v>94892.9</v>
       </c>
       <c r="E175" s="10">
-        <v>5.291</v>
+        <v>5.2989</v>
       </c>
       <c r="F175" s="10">
-        <v>9.9266</v>
+        <v>11.9925</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B176" s="6">
-        <v>43708</v>
+        <v>43723</v>
       </c>
       <c r="C176" s="7">
-        <v>497176.75</v>
+        <v>506326.9</v>
       </c>
       <c r="D176" s="7">
-        <v>77603.3</v>
+        <v>71069.7</v>
       </c>
       <c r="E176" s="8">
-        <v>5.3746</v>
+        <v>5.291</v>
       </c>
       <c r="F176" s="8">
-        <v>13.3927</v>
+        <v>9.9266</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B177" s="6">
-        <v>43692</v>
+        <v>43708</v>
       </c>
       <c r="C177" s="9">
-        <v>516900.55</v>
+        <v>497176.75</v>
       </c>
       <c r="D177" s="9">
-        <v>123734.95</v>
+        <v>77603.3</v>
       </c>
       <c r="E177" s="10">
-        <v>5.3838</v>
+        <v>5.3746</v>
       </c>
       <c r="F177" s="10">
-        <v>13.9935</v>
+        <v>13.3927</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B178" s="6">
-        <v>43677</v>
+        <v>43692</v>
       </c>
       <c r="C178" s="7">
-        <v>509412.8</v>
+        <v>516900.55</v>
       </c>
       <c r="D178" s="7">
-        <v>119806.65</v>
+        <v>123734.95</v>
       </c>
       <c r="E178" s="8">
-        <v>5.6897</v>
+        <v>5.3838</v>
       </c>
       <c r="F178" s="8">
-        <v>14.465</v>
+        <v>13.9935</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B179" s="6">
-        <v>43661</v>
+        <v>43677</v>
       </c>
       <c r="C179" s="9">
-        <v>544981.4</v>
+        <v>509412.8</v>
       </c>
       <c r="D179" s="9">
-        <v>81216.1</v>
+        <v>119806.65</v>
       </c>
       <c r="E179" s="10">
-        <v>5.8064</v>
+        <v>5.6897</v>
       </c>
       <c r="F179" s="10">
-        <v>13.1919</v>
+        <v>14.465</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B180" s="6">
-        <v>43646</v>
+        <v>43661</v>
       </c>
       <c r="C180" s="7">
-        <v>503943.3</v>
+        <v>544981.4</v>
       </c>
       <c r="D180" s="7">
-        <v>107691.05</v>
+        <v>81216.1</v>
       </c>
       <c r="E180" s="8">
-        <v>5.7926</v>
+        <v>5.8064</v>
       </c>
       <c r="F180" s="8">
-        <v>11.8912</v>
+        <v>13.1919</v>
       </c>
     </row>
     <row r="181" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B181" s="6">
-        <v>43631</v>
+        <v>43646</v>
       </c>
       <c r="C181" s="9">
-        <v>556177.6</v>
+        <v>503943.3</v>
       </c>
       <c r="D181" s="9">
-        <v>107868.85</v>
+        <v>107691.05</v>
       </c>
       <c r="E181" s="10">
-        <v>5.8661</v>
+        <v>5.7926</v>
       </c>
       <c r="F181" s="10">
-        <v>13.9656</v>
+        <v>11.8912</v>
       </c>
     </row>
     <row r="182" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B182" s="6">
-        <v>43616</v>
+        <v>43631</v>
       </c>
       <c r="C182" s="7">
-        <v>551983.5</v>
+        <v>556177.6</v>
       </c>
       <c r="D182" s="7">
-        <v>102453.5</v>
+        <v>107868.85</v>
       </c>
       <c r="E182" s="8">
-        <v>6.43</v>
+        <v>5.8661</v>
       </c>
       <c r="F182" s="8">
-        <v>10.0776</v>
+        <v>13.9656</v>
       </c>
     </row>
     <row r="183" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B183" s="6">
-        <v>43600</v>
+        <v>43616</v>
       </c>
       <c r="C183" s="9">
-        <v>583720.6</v>
+        <v>551983.5</v>
       </c>
       <c r="D183" s="9">
-        <v>105970.75</v>
+        <v>102453.5</v>
       </c>
       <c r="E183" s="10">
-        <v>6.8083</v>
+        <v>6.43</v>
       </c>
       <c r="F183" s="10">
-        <v>13.0417</v>
+        <v>10.0776</v>
       </c>
     </row>
     <row r="184" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B184" s="6">
-        <v>43585</v>
+        <v>43600</v>
       </c>
       <c r="C184" s="7">
-        <v>542885.8</v>
+        <v>583720.6</v>
       </c>
       <c r="D184" s="7">
-        <v>71210.8</v>
+        <v>105970.75</v>
       </c>
       <c r="E184" s="8">
-        <v>6.6671</v>
+        <v>6.8083</v>
       </c>
       <c r="F184" s="8">
-        <v>13.1405</v>
+        <v>13.0417</v>
       </c>
     </row>
     <row r="185" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B185" s="6">
-        <v>43570</v>
+        <v>43585</v>
       </c>
       <c r="C185" s="9">
-        <v>573599.8</v>
+        <v>542885.8</v>
       </c>
       <c r="D185" s="9">
-        <v>129208.35</v>
+        <v>71210.8</v>
       </c>
       <c r="E185" s="10">
-        <v>6.4078</v>
+        <v>6.6671</v>
       </c>
       <c r="F185" s="10">
-        <v>9.9801</v>
+        <v>13.1405</v>
       </c>
     </row>
     <row r="186" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B186" s="6">
-        <v>43555</v>
+        <v>43570</v>
       </c>
       <c r="C186" s="7">
-        <v>483084.45</v>
+        <v>573599.8</v>
       </c>
       <c r="D186" s="7">
-        <v>101295.55</v>
+        <v>129208.35</v>
       </c>
       <c r="E186" s="8">
-        <v>6.5432</v>
+        <v>6.4078</v>
       </c>
       <c r="F186" s="8">
-        <v>12.5962</v>
+        <v>9.9801</v>
       </c>
     </row>
     <row r="187" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B187" s="6">
-        <v>43539</v>
+        <v>43555</v>
       </c>
       <c r="C187" s="9">
-        <v>530952</v>
+        <v>483084.45</v>
       </c>
       <c r="D187" s="9">
-        <v>124063</v>
+        <v>101295.55</v>
       </c>
       <c r="E187" s="10">
-        <v>6.4449</v>
+        <v>6.5432</v>
       </c>
       <c r="F187" s="10">
-        <v>9.9801</v>
+        <v>12.5962</v>
       </c>
     </row>
     <row r="188" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B188" s="6">
-        <v>43524</v>
+        <v>43539</v>
       </c>
       <c r="C188" s="7">
-        <v>520811.05</v>
+        <v>530952</v>
       </c>
       <c r="D188" s="7">
-        <v>90081.2</v>
+        <v>124063</v>
       </c>
       <c r="E188" s="8">
-        <v>6.3614</v>
+        <v>6.4449</v>
       </c>
       <c r="F188" s="8">
-        <v>11.7416</v>
+        <v>9.9801</v>
       </c>
     </row>
     <row r="189" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B189" s="6">
-        <v>43511</v>
+        <v>43524</v>
       </c>
       <c r="C189" s="9">
-        <v>524231.25</v>
+        <v>520811.05</v>
       </c>
       <c r="D189" s="9">
-        <v>103546.7</v>
+        <v>90081.2</v>
       </c>
       <c r="E189" s="10">
-        <v>6.4137</v>
+        <v>6.3614</v>
       </c>
       <c r="F189" s="10">
-        <v>13.4018</v>
+        <v>11.7416</v>
       </c>
     </row>
     <row r="190" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B190" s="6">
-        <v>43496</v>
+        <v>43511</v>
       </c>
       <c r="C190" s="7">
-        <v>528741.2</v>
+        <v>524231.25</v>
       </c>
       <c r="D190" s="7">
-        <v>107391.55</v>
+        <v>103546.7</v>
       </c>
       <c r="E190" s="8">
-        <v>6.5444</v>
+        <v>6.4137</v>
       </c>
       <c r="F190" s="8">
-        <v>12.6231</v>
+        <v>13.4018</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B191" s="6">
-        <v>43480</v>
+        <v>43496</v>
       </c>
       <c r="C191" s="9">
-        <v>554022.45</v>
+        <v>528741.2</v>
       </c>
       <c r="D191" s="9">
-        <v>100992.3</v>
+        <v>107391.55</v>
       </c>
       <c r="E191" s="10">
-        <v>6.6592</v>
+        <v>6.5444</v>
       </c>
       <c r="F191" s="10">
-        <v>10.9448</v>
+        <v>12.6231</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B192" s="6">
-        <v>43465</v>
+        <v>43480</v>
       </c>
       <c r="C192" s="7">
-        <v>498728.65</v>
+        <v>554022.45</v>
       </c>
       <c r="D192" s="7">
-        <v>95777.1</v>
+        <v>100992.3</v>
       </c>
       <c r="E192" s="8">
-        <v>6.7834</v>
+        <v>6.6592</v>
       </c>
       <c r="F192" s="8">
-        <v>10.2932</v>
+        <v>10.9448</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B193" s="6">
-        <v>43449</v>
+        <v>43465</v>
       </c>
       <c r="C193" s="9">
-        <v>546077.75</v>
+        <v>498728.65</v>
       </c>
       <c r="D193" s="9">
-        <v>103648.9</v>
+        <v>95777.1</v>
       </c>
       <c r="E193" s="10">
-        <v>6.5107</v>
+        <v>6.7834</v>
       </c>
       <c r="F193" s="10">
-        <v>11.1794</v>
+        <v>10.2932</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B194" s="6">
-        <v>43434</v>
+        <v>43449</v>
       </c>
       <c r="C194" s="7">
-        <v>560613.81</v>
+        <v>546077.75</v>
       </c>
       <c r="D194" s="7">
-        <v>130058.7</v>
+        <v>103648.9</v>
       </c>
       <c r="E194" s="8">
-        <v>6.6326</v>
+        <v>6.5107</v>
       </c>
       <c r="F194" s="8">
-        <v>11.0906</v>
+        <v>11.1794</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B195" s="6">
-        <v>43419</v>
+        <v>43434</v>
       </c>
       <c r="C195" s="9">
-        <v>584716.61</v>
+        <v>560613.81</v>
       </c>
       <c r="D195" s="9">
-        <v>106623.3</v>
+        <v>130058.7</v>
       </c>
       <c r="E195" s="10">
-        <v>6.6899</v>
+        <v>6.6326</v>
       </c>
       <c r="F195" s="10">
-        <v>11.7341</v>
+        <v>11.0906</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B196" s="6">
-        <v>43404</v>
+        <v>43419</v>
       </c>
       <c r="C196" s="7">
-        <v>587688.66</v>
+        <v>584716.61</v>
       </c>
       <c r="D196" s="7">
-        <v>94931.15</v>
+        <v>106623.3</v>
       </c>
       <c r="E196" s="8">
-        <v>6.8656</v>
+        <v>6.6899</v>
       </c>
       <c r="F196" s="8">
-        <v>10.3806</v>
+        <v>11.7341</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B197" s="6">
-        <v>43388</v>
+        <v>43404</v>
       </c>
       <c r="C197" s="9">
-        <v>594490.16</v>
+        <v>587688.66</v>
       </c>
       <c r="D197" s="9">
-        <v>79913.95</v>
+        <v>94931.15</v>
       </c>
       <c r="E197" s="10">
-        <v>6.7238</v>
+        <v>6.8656</v>
       </c>
       <c r="F197" s="10">
-        <v>17.4909</v>
+        <v>10.3806</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B198" s="6">
-        <v>43373</v>
+        <v>43388</v>
       </c>
       <c r="C198" s="7">
-        <v>556198.16</v>
+        <v>594490.16</v>
       </c>
       <c r="D198" s="7">
-        <v>112520.4</v>
+        <v>79913.95</v>
       </c>
       <c r="E198" s="8">
-        <v>6.8377</v>
+        <v>6.7238</v>
       </c>
       <c r="F198" s="8">
-        <v>11.1828</v>
+        <v>17.4909</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B199" s="6">
-        <v>43358</v>
+        <v>43373</v>
       </c>
       <c r="C199" s="9">
-        <v>640808.71</v>
+        <v>556198.16</v>
       </c>
       <c r="D199" s="9">
-        <v>111261.7</v>
+        <v>112520.4</v>
       </c>
       <c r="E199" s="10">
-        <v>6.5644</v>
+        <v>6.8377</v>
       </c>
       <c r="F199" s="10">
-        <v>15.7923</v>
+        <v>11.1828</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B200" s="6">
-        <v>43343</v>
+        <v>43358</v>
       </c>
       <c r="C200" s="7">
-        <v>632296.01</v>
+        <v>640808.71</v>
       </c>
       <c r="D200" s="7">
-        <v>156116</v>
+        <v>111261.7</v>
       </c>
       <c r="E200" s="8">
-        <v>6.4396</v>
+        <v>6.5644</v>
       </c>
       <c r="F200" s="8">
-        <v>10.4006</v>
+        <v>15.7923</v>
       </c>
     </row>
     <row r="201" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B201" s="6">
-        <v>43327</v>
+        <v>43343</v>
       </c>
       <c r="C201" s="9">
-        <v>597839.31</v>
+        <v>632296.01</v>
       </c>
       <c r="D201" s="9">
-        <v>147848.75</v>
+        <v>156116</v>
       </c>
       <c r="E201" s="10">
-        <v>6.5298</v>
+        <v>6.4396</v>
       </c>
       <c r="F201" s="10">
-        <v>15.7923</v>
+        <v>10.4006</v>
       </c>
     </row>
     <row r="202" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B202" s="6">
-        <v>43312</v>
+        <v>43327</v>
       </c>
       <c r="C202" s="7">
-        <v>639529.66</v>
+        <v>597839.31</v>
       </c>
       <c r="D202" s="7">
-        <v>167712.25</v>
+        <v>147848.75</v>
       </c>
       <c r="E202" s="8">
-        <v>6.1904</v>
+        <v>6.5298</v>
       </c>
       <c r="F202" s="8">
-        <v>12.4726</v>
+        <v>15.7923</v>
       </c>
     </row>
     <row r="203" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B203" s="6">
-        <v>43296</v>
+        <v>43312</v>
       </c>
       <c r="C203" s="9">
-        <v>563088.86</v>
+        <v>639529.66</v>
       </c>
       <c r="D203" s="9">
-        <v>99548.8</v>
+        <v>167712.25</v>
       </c>
       <c r="E203" s="10">
-        <v>6.0329</v>
+        <v>6.1904</v>
       </c>
       <c r="F203" s="10">
-        <v>10.7065</v>
+        <v>12.4726</v>
       </c>
     </row>
     <row r="204" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B204" s="6">
-        <v>43281</v>
+        <v>43296</v>
       </c>
       <c r="C204" s="7">
-        <v>491833.06</v>
+        <v>563088.86</v>
       </c>
       <c r="D204" s="7">
-        <v>126726.8</v>
+        <v>99548.8</v>
       </c>
       <c r="E204" s="8">
-        <v>6.1633</v>
+        <v>6.0329</v>
       </c>
       <c r="F204" s="8">
-        <v>11.1862</v>
+        <v>10.7065</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B205" s="6">
-        <v>43266</v>
+        <v>43281</v>
       </c>
       <c r="C205" s="9">
-        <v>507614.46</v>
+        <v>491833.06</v>
       </c>
       <c r="D205" s="9">
-        <v>134164.5</v>
+        <v>126726.8</v>
       </c>
       <c r="E205" s="10">
-        <v>6.2522</v>
+        <v>6.1633</v>
       </c>
       <c r="F205" s="10">
-        <v>15.8608</v>
+        <v>11.1862</v>
       </c>
     </row>
     <row r="206" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B206" s="6">
-        <v>43251</v>
+        <v>43266</v>
       </c>
       <c r="C206" s="7">
-        <v>466886.96</v>
+        <v>507614.46</v>
       </c>
       <c r="D206" s="7">
-        <v>85015</v>
+        <v>134164.5</v>
       </c>
       <c r="E206" s="8">
-        <v>6.89</v>
+        <v>6.2522</v>
       </c>
       <c r="F206" s="8">
-        <v>9.84</v>
+        <v>15.8608</v>
       </c>
     </row>
     <row r="207" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B207" s="6">
-        <v>43235</v>
+        <v>43251</v>
       </c>
       <c r="C207" s="9">
-        <v>477697.46</v>
+        <v>466886.96</v>
       </c>
       <c r="D207" s="9">
-        <v>87439.25</v>
+        <v>85015</v>
       </c>
       <c r="E207" s="10">
-        <v>6.61</v>
+        <v>6.89</v>
       </c>
       <c r="F207" s="10">
-        <v>9.55</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="208" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B208" s="6">
-        <v>43220</v>
+        <v>43235</v>
       </c>
       <c r="C208" s="7">
-        <v>447691.41</v>
+        <v>477697.46</v>
       </c>
       <c r="D208" s="7">
-        <v>56773.65</v>
+        <v>87439.25</v>
       </c>
       <c r="E208" s="8">
-        <v>6.35</v>
+        <v>6.61</v>
       </c>
       <c r="F208" s="8">
-        <v>12.31</v>
+        <v>9.55</v>
       </c>
     </row>
     <row r="209" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B209" s="6">
-        <v>43205</v>
+        <v>43220</v>
       </c>
       <c r="C209" s="9">
-        <v>433183.01</v>
+        <v>447691.41</v>
       </c>
       <c r="D209" s="9">
-        <v>72990.2</v>
+        <v>56773.65</v>
       </c>
       <c r="E209" s="10">
-        <v>6.04</v>
+        <v>6.35</v>
       </c>
       <c r="F209" s="10">
-        <v>11.88</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="210" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B210" s="6">
-        <v>43190</v>
+        <v>43205</v>
       </c>
       <c r="C210" s="7">
-        <v>372577.41</v>
+        <v>433183.01</v>
       </c>
       <c r="D210" s="7">
-        <v>99915.4</v>
+        <v>72990.2</v>
       </c>
       <c r="E210" s="8">
-        <v>6.49</v>
+        <v>6.04</v>
       </c>
       <c r="F210" s="8">
-        <v>14</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B211" s="6">
-        <v>43174</v>
+        <v>43190</v>
       </c>
       <c r="C211" s="9">
-        <v>460495.96</v>
+        <v>372577.41</v>
       </c>
       <c r="D211" s="9">
-        <v>115454.25</v>
+        <v>99915.4</v>
       </c>
       <c r="E211" s="10">
-        <v>6.32</v>
+        <v>6.49</v>
       </c>
       <c r="F211" s="10">
-        <v>11.88</v>
+        <v>14</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B212" s="6">
-        <v>43159</v>
+        <v>43174</v>
       </c>
       <c r="C212" s="7">
-        <v>455047.21</v>
+        <v>460495.96</v>
       </c>
       <c r="D212" s="7">
-        <v>72383.8</v>
+        <v>115454.25</v>
       </c>
       <c r="E212" s="8">
-        <v>6.22</v>
+        <v>6.32</v>
       </c>
       <c r="F212" s="8">
-        <v>10.6</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B213" s="6">
-        <v>43146</v>
+        <v>43159</v>
       </c>
       <c r="C213" s="9">
-        <v>488630.91</v>
+        <v>455047.21</v>
       </c>
       <c r="D213" s="9">
-        <v>103773.6</v>
+        <v>72383.8</v>
       </c>
       <c r="E213" s="10">
-        <v>6.07</v>
+        <v>6.22</v>
       </c>
       <c r="F213" s="10">
-        <v>11.81</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B214" s="6">
-        <v>43131</v>
+        <v>43146</v>
       </c>
       <c r="C214" s="7">
-        <v>457498.66</v>
+        <v>488630.91</v>
       </c>
       <c r="D214" s="7">
-        <v>132021.65</v>
+        <v>103773.6</v>
       </c>
       <c r="E214" s="8">
-        <v>6.27</v>
+        <v>6.07</v>
       </c>
       <c r="F214" s="8">
-        <v>11.88</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B215" s="6">
-        <v>43115</v>
+        <v>43131</v>
       </c>
       <c r="C215" s="9">
-        <v>469648.71</v>
+        <v>457498.66</v>
       </c>
       <c r="D215" s="9">
-        <v>91320.5</v>
+        <v>132021.65</v>
       </c>
       <c r="E215" s="10">
-        <v>5.48</v>
+        <v>6.27</v>
       </c>
       <c r="F215" s="10">
-        <v>9.65</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="216" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B216" s="6">
-        <v>43100</v>
+        <v>43115</v>
       </c>
       <c r="C216" s="7">
-        <v>409053.31</v>
+        <v>469648.71</v>
       </c>
       <c r="D216" s="7">
-        <v>91603.6</v>
+        <v>91320.5</v>
       </c>
       <c r="E216" s="8">
-        <v>6.22</v>
+        <v>5.48</v>
       </c>
       <c r="F216" s="8">
-        <v>10.76</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="217" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B217" s="6">
-        <v>43084</v>
+        <v>43100</v>
       </c>
       <c r="C217" s="9">
-        <v>481528.71</v>
+        <v>409053.31</v>
       </c>
       <c r="D217" s="9">
-        <v>96187.96</v>
+        <v>91603.6</v>
       </c>
       <c r="E217" s="10">
-        <v>5.98</v>
+        <v>6.22</v>
       </c>
       <c r="F217" s="10">
-        <v>11.19</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="218" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B218" s="6">
-        <v>43069</v>
+        <v>43084</v>
       </c>
       <c r="C218" s="7">
-        <v>473679.8</v>
+        <v>481528.71</v>
       </c>
       <c r="D218" s="7">
-        <v>96022.9</v>
+        <v>96187.96</v>
       </c>
       <c r="E218" s="8">
-        <v>6.01</v>
+        <v>5.98</v>
       </c>
       <c r="F218" s="8">
-        <v>37.73</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B219" s="6">
-        <v>43054</v>
+        <v>43069</v>
       </c>
       <c r="C219" s="9">
-        <v>481581.9</v>
+        <v>473679.8</v>
       </c>
       <c r="D219" s="9">
-        <v>103409.5</v>
+        <v>96022.9</v>
       </c>
       <c r="E219" s="10">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="F219" s="10">
-        <v>11.26</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="220" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B220" s="6">
-        <v>43039</v>
+        <v>43054</v>
       </c>
       <c r="C220" s="7">
-        <v>489231.8</v>
+        <v>481581.9</v>
       </c>
       <c r="D220" s="7">
-        <v>135588.45</v>
+        <v>103409.5</v>
       </c>
       <c r="E220" s="8">
-        <v>6.06</v>
+        <v>6.08</v>
       </c>
       <c r="F220" s="8">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="221" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B221" s="6">
-        <v>43023</v>
+        <v>43039</v>
       </c>
       <c r="C221" s="9">
-        <v>479675.75</v>
+        <v>489231.8</v>
       </c>
       <c r="D221" s="9">
-        <v>106985.1</v>
+        <v>135588.45</v>
       </c>
       <c r="E221" s="10">
-        <v>5.98</v>
+        <v>6.06</v>
       </c>
       <c r="F221" s="10">
-        <v>11.79</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B222" s="6">
-        <v>43008</v>
+        <v>43023</v>
       </c>
       <c r="C222" s="7">
-        <v>393214.35</v>
+        <v>479675.75</v>
       </c>
       <c r="D222" s="7">
-        <v>116294.1</v>
+        <v>106985.1</v>
       </c>
       <c r="E222" s="8">
-        <v>5.89</v>
+        <v>5.98</v>
       </c>
       <c r="F222" s="8">
-        <v>11</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B223" s="6">
-        <v>42993</v>
+        <v>43008</v>
       </c>
       <c r="C223" s="9">
-        <v>442386.25</v>
+        <v>393214.35</v>
       </c>
       <c r="D223" s="9">
-        <v>125068.65</v>
+        <v>116294.1</v>
       </c>
       <c r="E223" s="10">
-        <v>5.59</v>
+        <v>5.89</v>
       </c>
       <c r="F223" s="10">
-        <v>11.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B224" s="6">
-        <v>42978</v>
+        <v>42993</v>
       </c>
       <c r="C224" s="7">
-        <v>369579.3</v>
+        <v>442386.25</v>
       </c>
       <c r="D224" s="7">
-        <v>99649</v>
+        <v>125068.65</v>
       </c>
       <c r="E224" s="8">
-        <v>6.05</v>
+        <v>5.59</v>
       </c>
       <c r="F224" s="8">
-        <v>11.25</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B225" s="6">
-        <v>42962</v>
+        <v>42978</v>
       </c>
       <c r="C225" s="9">
-        <v>359502.8</v>
+        <v>369579.3</v>
       </c>
       <c r="D225" s="9">
-        <v>119593.2</v>
+        <v>99649</v>
       </c>
       <c r="E225" s="10">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="F225" s="10">
-        <v>13.92</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B226" s="6">
-        <v>42947</v>
+        <v>42962</v>
       </c>
       <c r="C226" s="7">
-        <v>325524.6</v>
+        <v>359502.8</v>
       </c>
       <c r="D226" s="7">
-        <v>32936.85</v>
+        <v>119593.2</v>
       </c>
       <c r="E226" s="8">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="F226" s="8">
-        <v>11.96</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="227" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B227" s="6">
-        <v>42931</v>
+        <v>42947</v>
       </c>
       <c r="C227" s="9">
-        <v>358397.15</v>
+        <v>325524.6</v>
       </c>
       <c r="D227" s="9">
-        <v>84592</v>
+        <v>32936.85</v>
       </c>
       <c r="E227" s="10">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="F227" s="10">
-        <v>11.97</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="228" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B228" s="6">
-        <v>42916</v>
+        <v>42931</v>
       </c>
       <c r="C228" s="7">
-        <v>329415.75</v>
+        <v>358397.15</v>
       </c>
       <c r="D228" s="7">
-        <v>97242</v>
+        <v>84592</v>
       </c>
       <c r="E228" s="8">
-        <v>6.23</v>
+        <v>6.02</v>
       </c>
       <c r="F228" s="8">
-        <v>11.95</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B229" s="6">
-        <v>42901</v>
+        <v>42916</v>
       </c>
       <c r="C229" s="9">
-        <v>388518.85</v>
+        <v>329415.75</v>
       </c>
       <c r="D229" s="9">
-        <v>72564</v>
+        <v>97242</v>
       </c>
       <c r="E229" s="10">
-        <v>6.18</v>
+        <v>6.23</v>
       </c>
       <c r="F229" s="10">
-        <v>11.97</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="230" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B230" s="6">
-        <v>42886</v>
+        <v>42901</v>
       </c>
       <c r="C230" s="7">
-        <v>391326.85</v>
+        <v>388518.85</v>
       </c>
       <c r="D230" s="7">
-        <v>75756.6</v>
+        <v>72564</v>
       </c>
       <c r="E230" s="8">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="F230" s="8">
-        <v>11.94</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="231" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B231" s="6">
-        <v>42870</v>
+        <v>42886</v>
       </c>
       <c r="C231" s="9">
-        <v>467221.55</v>
+        <v>391326.85</v>
       </c>
       <c r="D231" s="9">
-        <v>94181</v>
+        <v>75756.6</v>
       </c>
       <c r="E231" s="10">
-        <v>6.16</v>
+        <v>6.2</v>
       </c>
       <c r="F231" s="10">
-        <v>11.95</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="232" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B232" s="6">
-        <v>42855</v>
+        <v>42870</v>
       </c>
       <c r="C232" s="7">
-        <v>439982.55</v>
+        <v>467221.55</v>
       </c>
       <c r="D232" s="7">
-        <v>65523</v>
+        <v>94181</v>
       </c>
       <c r="E232" s="8">
-        <v>5.99</v>
+        <v>6.16</v>
       </c>
       <c r="F232" s="8">
-        <v>11.97</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="233" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B233" s="6">
-        <v>42840</v>
+        <v>42855</v>
       </c>
       <c r="C233" s="9">
-        <v>436739.7</v>
+        <v>439982.55</v>
       </c>
       <c r="D233" s="9">
-        <v>64479.6</v>
+        <v>65523</v>
       </c>
       <c r="E233" s="10">
-        <v>5.9</v>
+        <v>5.99</v>
       </c>
       <c r="F233" s="10">
         <v>11.97</v>
@@ -4171,84 +4171,84 @@
     </row>
     <row r="234" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B234" s="6">
-        <v>42825</v>
+        <v>42840</v>
       </c>
       <c r="C234" s="7">
-        <v>397965.25</v>
+        <v>436739.7</v>
       </c>
       <c r="D234" s="7">
-        <v>109409.15</v>
+        <v>64479.6</v>
       </c>
       <c r="E234" s="8">
-        <v>5.99</v>
+        <v>5.9</v>
       </c>
       <c r="F234" s="8">
-        <v>13.33</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="235" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B235" s="6">
-        <v>42809</v>
+        <v>42825</v>
       </c>
       <c r="C235" s="9">
-        <v>459050.25</v>
+        <v>397965.25</v>
       </c>
       <c r="D235" s="9">
-        <v>150024.5</v>
+        <v>109409.15</v>
       </c>
       <c r="E235" s="10">
-        <v>5.9</v>
+        <v>5.99</v>
       </c>
       <c r="F235" s="10">
-        <v>14.92</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="236" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B236" s="6">
-        <v>42794</v>
+        <v>42809</v>
       </c>
       <c r="C236" s="7">
-        <v>372671.25</v>
+        <v>459050.25</v>
       </c>
       <c r="D236" s="7">
-        <v>77225.3</v>
+        <v>150024.5</v>
       </c>
       <c r="E236" s="8">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="F236" s="8">
-        <v>14.19</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="237" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B237" s="6">
-        <v>42781</v>
+        <v>42794</v>
       </c>
       <c r="C237" s="9">
-        <v>402032.7</v>
+        <v>372671.25</v>
       </c>
       <c r="D237" s="9">
-        <v>104433.5</v>
+        <v>77225.3</v>
       </c>
       <c r="E237" s="10">
-        <v>6.03</v>
+        <v>6.08</v>
       </c>
       <c r="F237" s="10">
-        <v>14.21</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="238" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B238" s="6">
-        <v>42766</v>
+        <v>42781</v>
       </c>
       <c r="C238" s="7">
-        <v>381371.95</v>
+        <v>402032.7</v>
       </c>
       <c r="D238" s="7">
-        <v>50462.25</v>
+        <v>104433.5</v>
       </c>
       <c r="E238" s="8">
-        <v>6.19</v>
+        <v>6.03</v>
       </c>
       <c r="F238" s="8">
         <v>14.21</v>
@@ -4256,1784 +4256,1784 @@
     </row>
     <row r="239" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B239" s="6">
-        <v>42750</v>
+        <v>42766</v>
       </c>
       <c r="C239" s="9">
-        <v>406587.95</v>
+        <v>381371.95</v>
       </c>
       <c r="D239" s="9">
-        <v>58292.45</v>
+        <v>50462.25</v>
       </c>
       <c r="E239" s="10">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="F239" s="10">
-        <v>14.19</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="240" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B240" s="6">
-        <v>42735</v>
+        <v>42750</v>
       </c>
       <c r="C240" s="7">
-        <v>361804</v>
+        <v>406587.95</v>
       </c>
       <c r="D240" s="7">
-        <v>90688.9</v>
+        <v>58292.45</v>
       </c>
       <c r="E240" s="8">
-        <v>6.02</v>
+        <v>6.15</v>
       </c>
       <c r="F240" s="8">
-        <v>12.66</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="241" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B241" s="6">
-        <v>42719</v>
+        <v>42735</v>
       </c>
       <c r="C241" s="9">
-        <v>397887.45</v>
+        <v>361804</v>
       </c>
       <c r="D241" s="9">
-        <v>77409.95</v>
+        <v>90688.9</v>
       </c>
       <c r="E241" s="10">
-        <v>5.86</v>
+        <v>6.02</v>
       </c>
       <c r="F241" s="10">
-        <v>13.95</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="242" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B242" s="6">
-        <v>42704</v>
+        <v>42719</v>
       </c>
       <c r="C242" s="7">
-        <v>385876</v>
+        <v>397887.45</v>
       </c>
       <c r="D242" s="7">
-        <v>81407</v>
+        <v>77409.95</v>
       </c>
       <c r="E242" s="8">
-        <v>5.68</v>
+        <v>5.86</v>
       </c>
       <c r="F242" s="8">
-        <v>13.94</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="243" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B243" s="6">
-        <v>42689</v>
+        <v>42704</v>
       </c>
       <c r="C243" s="9">
-        <v>409848.5</v>
+        <v>385876</v>
       </c>
       <c r="D243" s="9">
-        <v>83559.6</v>
+        <v>81407</v>
       </c>
       <c r="E243" s="10">
-        <v>6.07</v>
+        <v>5.68</v>
       </c>
       <c r="F243" s="10">
-        <v>12.62</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="244" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B244" s="6">
-        <v>42674</v>
+        <v>42689</v>
       </c>
       <c r="C244" s="7">
-        <v>396117.5</v>
+        <v>409848.5</v>
       </c>
       <c r="D244" s="7">
-        <v>53585.85</v>
+        <v>83559.6</v>
       </c>
       <c r="E244" s="8">
-        <v>6.31</v>
+        <v>6.07</v>
       </c>
       <c r="F244" s="8">
-        <v>11.97</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="245" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B245" s="6">
-        <v>42658</v>
+        <v>42674</v>
       </c>
       <c r="C245" s="9">
-        <v>411595</v>
+        <v>396117.5</v>
       </c>
       <c r="D245" s="9">
-        <v>85365</v>
+        <v>53585.85</v>
       </c>
       <c r="E245" s="10">
-        <v>6.28</v>
+        <v>6.31</v>
       </c>
       <c r="F245" s="10">
-        <v>13.84</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="246" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B246" s="6">
-        <v>42643</v>
+        <v>42658</v>
       </c>
       <c r="C246" s="7">
-        <v>348761</v>
+        <v>411595</v>
       </c>
       <c r="D246" s="7">
-        <v>99339</v>
+        <v>85365</v>
       </c>
       <c r="E246" s="8">
-        <v>6.32</v>
+        <v>6.28</v>
       </c>
       <c r="F246" s="8">
-        <v>13.94</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="247" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B247" s="6">
-        <v>42628</v>
+        <v>42643</v>
       </c>
       <c r="C247" s="9">
-        <v>397577</v>
+        <v>348761</v>
       </c>
       <c r="D247" s="9">
-        <v>85613</v>
+        <v>99339</v>
       </c>
       <c r="E247" s="10">
-        <v>6.28</v>
+        <v>6.32</v>
       </c>
       <c r="F247" s="10">
-        <v>12.61</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="248" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B248" s="6">
-        <v>42613</v>
+        <v>42628</v>
       </c>
       <c r="C248" s="7">
-        <v>388311</v>
+        <v>397577</v>
       </c>
       <c r="D248" s="7">
-        <v>114988</v>
+        <v>85613</v>
       </c>
       <c r="E248" s="8">
-        <v>6.51</v>
+        <v>6.28</v>
       </c>
       <c r="F248" s="8">
-        <v>13.92</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="249" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B249" s="6">
-        <v>42597</v>
+        <v>42613</v>
       </c>
       <c r="C249" s="9">
-        <v>386189.6</v>
+        <v>388311</v>
       </c>
       <c r="D249" s="9">
-        <v>81444.9</v>
+        <v>114988</v>
       </c>
       <c r="E249" s="10">
-        <v>6.44</v>
+        <v>6.51</v>
       </c>
       <c r="F249" s="10">
-        <v>12.78</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="250" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B250" s="6">
-        <v>42582</v>
+        <v>42597</v>
       </c>
       <c r="C250" s="7">
-        <v>381190</v>
+        <v>386189.6</v>
       </c>
       <c r="D250" s="7">
-        <v>56626</v>
+        <v>81444.9</v>
       </c>
       <c r="E250" s="8">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
       <c r="F250" s="8">
-        <v>13.84</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="251" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B251" s="6">
-        <v>42566</v>
+        <v>42582</v>
       </c>
       <c r="C251" s="9">
-        <v>403112.2</v>
+        <v>381190</v>
       </c>
       <c r="D251" s="9">
-        <v>93210.1</v>
+        <v>56626</v>
       </c>
       <c r="E251" s="10">
         <v>6.42</v>
       </c>
       <c r="F251" s="10">
-        <v>11.95</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B252" s="6">
-        <v>42551</v>
+        <v>42566</v>
       </c>
       <c r="C252" s="7">
-        <v>337642</v>
+        <v>403112.2</v>
       </c>
       <c r="D252" s="7">
-        <v>95943</v>
+        <v>93210.1</v>
       </c>
       <c r="E252" s="8">
-        <v>6.54</v>
+        <v>6.42</v>
       </c>
       <c r="F252" s="8">
-        <v>13.84</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B253" s="6">
-        <v>42536</v>
+        <v>42551</v>
       </c>
       <c r="C253" s="9">
-        <v>383171</v>
+        <v>337642</v>
       </c>
       <c r="D253" s="9">
-        <v>89944</v>
+        <v>95943</v>
       </c>
       <c r="E253" s="10">
-        <v>6.69</v>
+        <v>6.54</v>
       </c>
       <c r="F253" s="10">
-        <v>13.3</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="254" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B254" s="6">
-        <v>42521</v>
+        <v>42536</v>
       </c>
       <c r="C254" s="7">
-        <v>363204.8</v>
+        <v>383171</v>
       </c>
       <c r="D254" s="7">
-        <v>91114.1</v>
+        <v>89944</v>
       </c>
       <c r="E254" s="8">
-        <v>6.77</v>
+        <v>6.69</v>
       </c>
       <c r="F254" s="8">
-        <v>12.75</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B255" s="6">
-        <v>42505</v>
+        <v>42521</v>
       </c>
       <c r="C255" s="9">
-        <v>377474.8</v>
+        <v>363204.8</v>
       </c>
       <c r="D255" s="9">
-        <v>103293.6</v>
+        <v>91114.1</v>
       </c>
       <c r="E255" s="10">
-        <v>7.08</v>
+        <v>6.77</v>
       </c>
       <c r="F255" s="10">
-        <v>13.29</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="256" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B256" s="6">
-        <v>42490</v>
+        <v>42505</v>
       </c>
       <c r="C256" s="7">
-        <v>335679</v>
+        <v>377474.8</v>
       </c>
       <c r="D256" s="7">
-        <v>56459</v>
+        <v>103293.6</v>
       </c>
       <c r="E256" s="8">
-        <v>6.88</v>
+        <v>7.08</v>
       </c>
       <c r="F256" s="8">
-        <v>13.23</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="257" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B257" s="6">
-        <v>42475</v>
+        <v>42490</v>
       </c>
       <c r="C257" s="9">
-        <v>340617</v>
+        <v>335679</v>
       </c>
       <c r="D257" s="9">
-        <v>91806</v>
+        <v>56459</v>
       </c>
       <c r="E257" s="10">
-        <v>6.84</v>
+        <v>6.88</v>
       </c>
       <c r="F257" s="10">
-        <v>11.22</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="258" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B258" s="6">
-        <v>42460</v>
+        <v>42475</v>
       </c>
       <c r="C258" s="7">
-        <v>260244</v>
+        <v>340617</v>
       </c>
       <c r="D258" s="7">
-        <v>67364</v>
+        <v>91806</v>
       </c>
       <c r="E258" s="8">
-        <v>7.35</v>
+        <v>6.84</v>
       </c>
       <c r="F258" s="8">
-        <v>13.14</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="259" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B259" s="6">
-        <v>42444</v>
+        <v>42460</v>
       </c>
       <c r="C259" s="9">
-        <v>345590</v>
+        <v>260244</v>
       </c>
       <c r="D259" s="9">
-        <v>82656</v>
+        <v>67364</v>
       </c>
       <c r="E259" s="10">
-        <v>7.27</v>
+        <v>7.35</v>
       </c>
       <c r="F259" s="10">
-        <v>13.09</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="260" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B260" s="6">
-        <v>42429</v>
+        <v>42444</v>
       </c>
       <c r="C260" s="7">
-        <v>355783</v>
+        <v>345590</v>
       </c>
       <c r="D260" s="7">
-        <v>67177</v>
+        <v>82656</v>
       </c>
       <c r="E260" s="8">
-        <v>7.33</v>
+        <v>7.27</v>
       </c>
       <c r="F260" s="8">
-        <v>12</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="261" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B261" s="6">
-        <v>42415</v>
+        <v>42429</v>
       </c>
       <c r="C261" s="9">
-        <v>387605</v>
+        <v>355783</v>
       </c>
       <c r="D261" s="9">
-        <v>91182</v>
+        <v>67177</v>
       </c>
       <c r="E261" s="10">
-        <v>7.14</v>
+        <v>7.33</v>
       </c>
       <c r="F261" s="10">
-        <v>11.31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="262" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B262" s="6">
-        <v>42400</v>
+        <v>42415</v>
       </c>
       <c r="C262" s="7">
-        <v>355380</v>
+        <v>387605</v>
       </c>
       <c r="D262" s="7">
-        <v>51390</v>
+        <v>91182</v>
       </c>
       <c r="E262" s="8">
-        <v>7.3</v>
+        <v>7.14</v>
       </c>
       <c r="F262" s="8">
-        <v>11.18</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="263" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B263" s="6">
-        <v>42384</v>
+        <v>42400</v>
       </c>
       <c r="C263" s="9">
-        <v>364372</v>
+        <v>355380</v>
       </c>
       <c r="D263" s="9">
-        <v>71832</v>
+        <v>51390</v>
       </c>
       <c r="E263" s="10">
-        <v>6.89</v>
+        <v>7.3</v>
       </c>
       <c r="F263" s="10">
-        <v>11.42</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="264" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B264" s="6">
-        <v>42369</v>
+        <v>42384</v>
       </c>
       <c r="C264" s="7">
-        <v>308509</v>
+        <v>364372</v>
       </c>
       <c r="D264" s="7">
-        <v>66591</v>
+        <v>71832</v>
       </c>
       <c r="E264" s="8">
-        <v>7.23</v>
+        <v>6.89</v>
       </c>
       <c r="F264" s="8">
-        <v>11.79</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="265" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B265" s="6">
-        <v>42353</v>
+        <v>42369</v>
       </c>
       <c r="C265" s="9">
-        <v>380280</v>
+        <v>308509</v>
       </c>
       <c r="D265" s="9">
-        <v>115129</v>
+        <v>66591</v>
       </c>
       <c r="E265" s="10">
-        <v>7.08</v>
+        <v>7.23</v>
       </c>
       <c r="F265" s="10">
-        <v>12.13</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="266" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B266" s="6">
-        <v>42338</v>
+        <v>42353</v>
       </c>
       <c r="C266" s="7">
-        <v>327379</v>
+        <v>380280</v>
       </c>
       <c r="D266" s="7">
-        <v>62470</v>
+        <v>115129</v>
       </c>
       <c r="E266" s="8">
-        <v>7.07</v>
+        <v>7.08</v>
       </c>
       <c r="F266" s="8">
-        <v>11.66</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="267" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B267" s="6">
-        <v>42323</v>
+        <v>42338</v>
       </c>
       <c r="C267" s="9">
-        <v>344360</v>
+        <v>327379</v>
       </c>
       <c r="D267" s="9">
-        <v>70153</v>
+        <v>62470</v>
       </c>
       <c r="E267" s="10">
-        <v>6.52</v>
+        <v>7.07</v>
       </c>
       <c r="F267" s="10">
-        <v>11.18</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="268" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B268" s="6">
-        <v>42308</v>
+        <v>42323</v>
       </c>
       <c r="C268" s="7">
-        <v>323101</v>
+        <v>344360</v>
       </c>
       <c r="D268" s="7">
-        <v>63483</v>
+        <v>70153</v>
       </c>
       <c r="E268" s="8">
-        <v>7.02</v>
+        <v>6.52</v>
       </c>
       <c r="F268" s="8">
-        <v>11.55</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="269" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B269" s="6">
-        <v>42292</v>
+        <v>42308</v>
       </c>
       <c r="C269" s="9">
-        <v>322635</v>
+        <v>323101</v>
       </c>
       <c r="D269" s="9">
-        <v>76246</v>
+        <v>63483</v>
       </c>
       <c r="E269" s="10">
-        <v>6.99</v>
+        <v>7.02</v>
       </c>
       <c r="F269" s="10">
-        <v>11.54</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B270" s="6">
-        <v>42277</v>
+        <v>42292</v>
       </c>
       <c r="C270" s="7">
-        <v>268423</v>
+        <v>322635</v>
       </c>
       <c r="D270" s="7">
-        <v>43153</v>
+        <v>76246</v>
       </c>
       <c r="E270" s="8">
-        <v>7.29</v>
+        <v>6.99</v>
       </c>
       <c r="F270" s="8">
-        <v>11.53</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="271" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B271" s="6">
-        <v>42262</v>
+        <v>42277</v>
       </c>
       <c r="C271" s="9">
-        <v>325595</v>
+        <v>268423</v>
       </c>
       <c r="D271" s="9">
-        <v>63842</v>
+        <v>43153</v>
       </c>
       <c r="E271" s="10">
-        <v>7.19</v>
+        <v>7.29</v>
       </c>
       <c r="F271" s="10">
-        <v>13.06</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="272" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B272" s="6">
-        <v>42247</v>
+        <v>42262</v>
       </c>
       <c r="C272" s="7">
-        <v>309464</v>
+        <v>325595</v>
       </c>
       <c r="D272" s="7">
-        <v>59946</v>
+        <v>63842</v>
       </c>
       <c r="E272" s="8">
-        <v>7.33</v>
+        <v>7.19</v>
       </c>
       <c r="F272" s="8">
-        <v>12.29</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="273" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B273" s="6">
-        <v>42231</v>
+        <v>42247</v>
       </c>
       <c r="C273" s="9">
-        <v>323258</v>
+        <v>309464</v>
       </c>
       <c r="D273" s="9">
-        <v>67881</v>
+        <v>59946</v>
       </c>
       <c r="E273" s="10">
-        <v>7.09</v>
+        <v>7.33</v>
       </c>
       <c r="F273" s="10">
-        <v>12.24</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="274" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B274" s="6">
-        <v>42216</v>
+        <v>42231</v>
       </c>
       <c r="C274" s="7">
-        <v>314939</v>
+        <v>323258</v>
       </c>
       <c r="D274" s="7">
-        <v>57188</v>
+        <v>67881</v>
       </c>
       <c r="E274" s="8">
-        <v>7.36</v>
+        <v>7.09</v>
       </c>
       <c r="F274" s="8">
-        <v>11.76</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="275" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B275" s="6">
-        <v>42200</v>
+        <v>42216</v>
       </c>
       <c r="C275" s="9">
-        <v>318593</v>
+        <v>314939</v>
       </c>
       <c r="D275" s="9">
-        <v>61667</v>
+        <v>57188</v>
       </c>
       <c r="E275" s="10">
-        <v>7.45</v>
+        <v>7.36</v>
       </c>
       <c r="F275" s="10">
-        <v>11.52</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="276" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B276" s="6">
-        <v>42185</v>
+        <v>42200</v>
       </c>
       <c r="C276" s="7">
-        <v>270613</v>
+        <v>318593</v>
       </c>
       <c r="D276" s="7">
-        <v>59339</v>
+        <v>61667</v>
       </c>
       <c r="E276" s="8">
-        <v>7.39</v>
+        <v>7.45</v>
       </c>
       <c r="F276" s="8">
-        <v>11.56</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="277" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B277" s="6">
-        <v>42170</v>
+        <v>42185</v>
       </c>
       <c r="C277" s="9">
-        <v>312692</v>
+        <v>270613</v>
       </c>
       <c r="D277" s="9">
-        <v>71260</v>
+        <v>59339</v>
       </c>
       <c r="E277" s="10">
-        <v>7.07</v>
+        <v>7.39</v>
       </c>
       <c r="F277" s="10">
-        <v>13.06</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="278" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B278" s="6">
-        <v>42155</v>
+        <v>42170</v>
       </c>
       <c r="C278" s="7">
-        <v>298668</v>
+        <v>312692</v>
       </c>
       <c r="D278" s="7">
-        <v>68390.5</v>
+        <v>71260</v>
       </c>
       <c r="E278" s="8">
-        <v>7.79</v>
+        <v>7.07</v>
       </c>
       <c r="F278" s="8">
-        <v>12.11</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="279" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B279" s="6">
-        <v>42139</v>
+        <v>42155</v>
       </c>
       <c r="C279" s="9">
-        <v>290512</v>
+        <v>298668</v>
       </c>
       <c r="D279" s="9">
-        <v>54051</v>
+        <v>68390.5</v>
       </c>
       <c r="E279" s="10">
-        <v>8</v>
+        <v>7.79</v>
       </c>
       <c r="F279" s="10">
-        <v>11.91</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="280" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B280" s="6">
-        <v>42124</v>
+        <v>42139</v>
       </c>
       <c r="C280" s="7">
-        <v>268272</v>
+        <v>290512</v>
       </c>
       <c r="D280" s="7">
-        <v>67893</v>
+        <v>54051</v>
       </c>
       <c r="E280" s="8">
-        <v>7.84</v>
+        <v>8</v>
       </c>
       <c r="F280" s="8">
-        <v>12.03</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="281" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B281" s="6">
-        <v>42109</v>
+        <v>42124</v>
       </c>
       <c r="C281" s="9">
-        <v>244318</v>
+        <v>268272</v>
       </c>
       <c r="D281" s="9">
-        <v>68479</v>
+        <v>67893</v>
       </c>
       <c r="E281" s="10">
-        <v>7.78</v>
+        <v>7.84</v>
       </c>
       <c r="F281" s="10">
-        <v>11.36</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="282" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B282" s="6">
-        <v>42094</v>
+        <v>42109</v>
       </c>
       <c r="C282" s="7">
-        <v>193268</v>
+        <v>244318</v>
       </c>
       <c r="D282" s="7">
-        <v>69425</v>
+        <v>68479</v>
       </c>
       <c r="E282" s="8">
-        <v>7.44</v>
+        <v>7.78</v>
       </c>
       <c r="F282" s="8">
-        <v>14.92</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="283" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B283" s="6">
-        <v>42078</v>
+        <v>42094</v>
       </c>
       <c r="C283" s="9">
-        <v>256115</v>
+        <v>193268</v>
       </c>
       <c r="D283" s="9">
-        <v>59652</v>
+        <v>69425</v>
       </c>
       <c r="E283" s="10">
-        <v>7.91</v>
+        <v>7.44</v>
       </c>
       <c r="F283" s="10">
-        <v>13.06</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="284" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B284" s="6">
-        <v>42063</v>
+        <v>42078</v>
       </c>
       <c r="C284" s="7">
-        <v>249351</v>
+        <v>256115</v>
       </c>
       <c r="D284" s="7">
-        <v>51780.15</v>
+        <v>59652</v>
       </c>
       <c r="E284" s="8">
-        <v>8.04</v>
+        <v>7.91</v>
       </c>
       <c r="F284" s="8">
-        <v>12.19</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="285" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B285" s="6">
-        <v>42050</v>
+        <v>42063</v>
       </c>
       <c r="C285" s="9">
-        <v>257485</v>
+        <v>249351</v>
       </c>
       <c r="D285" s="9">
-        <v>54443</v>
+        <v>51780.15</v>
       </c>
       <c r="E285" s="10">
-        <v>7.86</v>
+        <v>8.04</v>
       </c>
       <c r="F285" s="10">
-        <v>12.21</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="286" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B286" s="6">
-        <v>42035</v>
+        <v>42050</v>
       </c>
       <c r="C286" s="7">
-        <v>237612</v>
+        <v>257485</v>
       </c>
       <c r="D286" s="7">
-        <v>37341.35</v>
+        <v>54443</v>
       </c>
       <c r="E286" s="8">
-        <v>7.95</v>
+        <v>7.86</v>
       </c>
       <c r="F286" s="8">
-        <v>13.21</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="287" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B287" s="6">
-        <v>42019</v>
+        <v>42035</v>
       </c>
       <c r="C287" s="9">
-        <v>252871</v>
+        <v>237612</v>
       </c>
       <c r="D287" s="9">
-        <v>56531</v>
+        <v>37341.35</v>
       </c>
       <c r="E287" s="10">
-        <v>8.06</v>
+        <v>7.95</v>
       </c>
       <c r="F287" s="10">
-        <v>11.73</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="288" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B288" s="6">
-        <v>42004</v>
+        <v>42019</v>
       </c>
       <c r="C288" s="7">
-        <v>208248</v>
+        <v>252871</v>
       </c>
       <c r="D288" s="7">
-        <v>43642</v>
+        <v>56531</v>
       </c>
       <c r="E288" s="8">
-        <v>7.98</v>
+        <v>8.06</v>
       </c>
       <c r="F288" s="8">
-        <v>12.61</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="289" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B289" s="6">
-        <v>41988</v>
+        <v>42004</v>
       </c>
       <c r="C289" s="9">
-        <v>234233</v>
+        <v>208248</v>
       </c>
       <c r="D289" s="9">
-        <v>56210</v>
+        <v>43642</v>
       </c>
       <c r="E289" s="10">
-        <v>8.02</v>
+        <v>7.98</v>
       </c>
       <c r="F289" s="10">
-        <v>11.58</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="290" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B290" s="6">
-        <v>41973</v>
+        <v>41988</v>
       </c>
       <c r="C290" s="7">
-        <v>225380</v>
+        <v>234233</v>
       </c>
       <c r="D290" s="7">
-        <v>47702</v>
+        <v>56210</v>
       </c>
       <c r="E290" s="8">
-        <v>8.05</v>
+        <v>8.02</v>
       </c>
       <c r="F290" s="8">
-        <v>12.48</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="291" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B291" s="6">
-        <v>41958</v>
+        <v>41973</v>
       </c>
       <c r="C291" s="9">
-        <v>228747</v>
+        <v>225380</v>
       </c>
       <c r="D291" s="9">
-        <v>36340</v>
+        <v>47702</v>
       </c>
       <c r="E291" s="10">
-        <v>8.13</v>
+        <v>8.05</v>
       </c>
       <c r="F291" s="10">
-        <v>11.76</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="292" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B292" s="6">
-        <v>41943</v>
+        <v>41958</v>
       </c>
       <c r="C292" s="7">
-        <v>218526</v>
+        <v>228747</v>
       </c>
       <c r="D292" s="7">
-        <v>34645</v>
+        <v>36340</v>
       </c>
       <c r="E292" s="8">
-        <v>7.55</v>
+        <v>8.13</v>
       </c>
       <c r="F292" s="8">
-        <v>11.75</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="293" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B293" s="6">
-        <v>41927</v>
+        <v>41943</v>
       </c>
       <c r="C293" s="9">
-        <v>224177</v>
+        <v>218526</v>
       </c>
       <c r="D293" s="9">
-        <v>50160</v>
+        <v>34645</v>
       </c>
       <c r="E293" s="10">
-        <v>8.34</v>
+        <v>7.55</v>
       </c>
       <c r="F293" s="10">
-        <v>11.62</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="294" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B294" s="6">
-        <v>41912</v>
+        <v>41927</v>
       </c>
       <c r="C294" s="7">
-        <v>184353</v>
+        <v>224177</v>
       </c>
       <c r="D294" s="7">
-        <v>51579</v>
+        <v>50160</v>
       </c>
       <c r="E294" s="8">
-        <v>8.44</v>
+        <v>8.34</v>
       </c>
       <c r="F294" s="8">
-        <v>12.6</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="295" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B295" s="6">
-        <v>41897</v>
+        <v>41912</v>
       </c>
       <c r="C295" s="9">
-        <v>232987</v>
+        <v>184353</v>
       </c>
       <c r="D295" s="9">
-        <v>68527</v>
+        <v>51579</v>
       </c>
       <c r="E295" s="10">
-        <v>8.26</v>
+        <v>8.44</v>
       </c>
       <c r="F295" s="10">
-        <v>12</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="296" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B296" s="6">
-        <v>41882</v>
+        <v>41897</v>
       </c>
       <c r="C296" s="7">
-        <v>211195</v>
+        <v>232987</v>
       </c>
       <c r="D296" s="7">
-        <v>35859</v>
+        <v>68527</v>
       </c>
       <c r="E296" s="8">
         <v>8.26</v>
       </c>
       <c r="F296" s="8">
-        <v>12.62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B297" s="6">
-        <v>41866</v>
+        <v>41882</v>
       </c>
       <c r="C297" s="9">
-        <v>218463</v>
+        <v>211195</v>
       </c>
       <c r="D297" s="9">
-        <v>47474</v>
+        <v>35859</v>
       </c>
       <c r="E297" s="10">
-        <v>7.36</v>
+        <v>8.26</v>
       </c>
       <c r="F297" s="10">
-        <v>11.96</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="298" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B298" s="6">
-        <v>41851</v>
+        <v>41866</v>
       </c>
       <c r="C298" s="7">
-        <v>201500</v>
+        <v>218463</v>
       </c>
       <c r="D298" s="7">
-        <v>39744</v>
+        <v>47474</v>
       </c>
       <c r="E298" s="8">
-        <v>8.12</v>
+        <v>7.36</v>
       </c>
       <c r="F298" s="8">
-        <v>11.77</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="299" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B299" s="6">
-        <v>41835</v>
+        <v>41851</v>
       </c>
       <c r="C299" s="9">
-        <v>202423</v>
+        <v>201500</v>
       </c>
       <c r="D299" s="9">
-        <v>46457</v>
+        <v>39744</v>
       </c>
       <c r="E299" s="10">
-        <v>8.16</v>
+        <v>8.12</v>
       </c>
       <c r="F299" s="10">
-        <v>12.42</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="300" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B300" s="6">
-        <v>41820</v>
+        <v>41835</v>
       </c>
       <c r="C300" s="7">
-        <v>170570</v>
+        <v>202423</v>
       </c>
       <c r="D300" s="7">
-        <v>50460</v>
+        <v>46457</v>
       </c>
       <c r="E300" s="8">
-        <v>8.29</v>
+        <v>8.16</v>
       </c>
       <c r="F300" s="8">
-        <v>14.02</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="301" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B301" s="6">
-        <v>41805</v>
+        <v>41820</v>
       </c>
       <c r="C301" s="9">
-        <v>196922</v>
+        <v>170570</v>
       </c>
       <c r="D301" s="9">
-        <v>48518</v>
+        <v>50460</v>
       </c>
       <c r="E301" s="10">
-        <v>8.14</v>
+        <v>8.29</v>
       </c>
       <c r="F301" s="10">
-        <v>12.54</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="302" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B302" s="6">
-        <v>41790</v>
+        <v>41805</v>
       </c>
       <c r="C302" s="7">
-        <v>182419</v>
+        <v>196922</v>
       </c>
       <c r="D302" s="7">
-        <v>38696</v>
+        <v>48518</v>
       </c>
       <c r="E302" s="8">
-        <v>8.35</v>
+        <v>8.14</v>
       </c>
       <c r="F302" s="8">
-        <v>12.87</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="303" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B303" s="6">
-        <v>41774</v>
+        <v>41790</v>
       </c>
       <c r="C303" s="9">
-        <v>182592</v>
+        <v>182419</v>
       </c>
       <c r="D303" s="9">
-        <v>46273</v>
+        <v>38696</v>
       </c>
       <c r="E303" s="10">
-        <v>8.48</v>
+        <v>8.35</v>
       </c>
       <c r="F303" s="10">
-        <v>12.65</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="304" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B304" s="6">
-        <v>41759</v>
+        <v>41774</v>
       </c>
       <c r="C304" s="7">
-        <v>153812.3</v>
+        <v>182592</v>
       </c>
       <c r="D304" s="7">
-        <v>34908.3</v>
+        <v>46273</v>
       </c>
       <c r="E304" s="8">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="F304" s="8">
-        <v>13.3</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B305" s="6">
-        <v>41744</v>
+        <v>41759</v>
       </c>
       <c r="C305" s="9">
-        <v>142134</v>
+        <v>153812.3</v>
       </c>
       <c r="D305" s="9">
-        <v>43694</v>
+        <v>34908.3</v>
       </c>
       <c r="E305" s="10">
-        <v>8.44</v>
+        <v>8.58</v>
       </c>
       <c r="F305" s="10">
-        <v>12</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="306" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B306" s="6">
-        <v>41729</v>
+        <v>41744</v>
       </c>
       <c r="C306" s="7">
-        <v>106613.6</v>
+        <v>142134</v>
       </c>
       <c r="D306" s="7">
-        <v>25037</v>
+        <v>43694</v>
       </c>
       <c r="E306" s="8">
-        <v>8.64</v>
+        <v>8.44</v>
       </c>
       <c r="F306" s="8">
-        <v>12.61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B307" s="6">
-        <v>41713</v>
+        <v>41729</v>
       </c>
       <c r="C307" s="9">
-        <v>165343</v>
+        <v>106613.6</v>
       </c>
       <c r="D307" s="9">
-        <v>41424</v>
+        <v>25037</v>
       </c>
       <c r="E307" s="10">
-        <v>7.96</v>
+        <v>8.64</v>
       </c>
       <c r="F307" s="10">
-        <v>14.18</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="308" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B308" s="6">
-        <v>41698</v>
+        <v>41713</v>
       </c>
       <c r="C308" s="7">
-        <v>164603</v>
+        <v>165343</v>
       </c>
       <c r="D308" s="7">
-        <v>29195</v>
+        <v>41424</v>
       </c>
       <c r="E308" s="8">
-        <v>7.84</v>
+        <v>7.96</v>
       </c>
       <c r="F308" s="8">
-        <v>13.06</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="309" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B309" s="6">
-        <v>41685</v>
+        <v>41698</v>
       </c>
       <c r="C309" s="9">
-        <v>176709</v>
+        <v>164603</v>
       </c>
       <c r="D309" s="9">
-        <v>35133</v>
+        <v>29195</v>
       </c>
       <c r="E309" s="10">
-        <v>8.33</v>
+        <v>7.84</v>
       </c>
       <c r="F309" s="10">
-        <v>12.7</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="310" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B310" s="6">
-        <v>41670</v>
+        <v>41685</v>
       </c>
       <c r="C310" s="7">
-        <v>164173</v>
+        <v>176709</v>
       </c>
       <c r="D310" s="7">
-        <v>29072</v>
+        <v>35133</v>
       </c>
       <c r="E310" s="8">
-        <v>7.99</v>
+        <v>8.33</v>
       </c>
       <c r="F310" s="8">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="311" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B311" s="6">
-        <v>41654</v>
+        <v>41670</v>
       </c>
       <c r="C311" s="9">
-        <v>172103.48</v>
+        <v>164173</v>
       </c>
       <c r="D311" s="9">
-        <v>39208.6</v>
+        <v>29072</v>
       </c>
       <c r="E311" s="10">
-        <v>8.33</v>
+        <v>7.99</v>
       </c>
       <c r="F311" s="10">
-        <v>12.52</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="312" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B312" s="6">
-        <v>41639</v>
+        <v>41654</v>
       </c>
       <c r="C312" s="7">
-        <v>140358</v>
+        <v>172103.48</v>
       </c>
       <c r="D312" s="7">
-        <v>29986</v>
+        <v>39208.6</v>
       </c>
       <c r="E312" s="8">
-        <v>8.38</v>
+        <v>8.33</v>
       </c>
       <c r="F312" s="8">
-        <v>12.63</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B313" s="6">
-        <v>41623</v>
+        <v>41639</v>
       </c>
       <c r="C313" s="9">
-        <v>187536</v>
+        <v>140358</v>
       </c>
       <c r="D313" s="9">
-        <v>43304</v>
+        <v>29986</v>
       </c>
       <c r="E313" s="10">
-        <v>8.05</v>
+        <v>8.38</v>
       </c>
       <c r="F313" s="10">
-        <v>12.7</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="314" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B314" s="6">
-        <v>41608</v>
+        <v>41623</v>
       </c>
       <c r="C314" s="7">
-        <v>175637</v>
+        <v>187536</v>
       </c>
       <c r="D314" s="7">
-        <v>32295</v>
+        <v>43304</v>
       </c>
       <c r="E314" s="8">
-        <v>8.74</v>
+        <v>8.05</v>
       </c>
       <c r="F314" s="8">
-        <v>12.46</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="315" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B315" s="6">
-        <v>41593</v>
+        <v>41608</v>
       </c>
       <c r="C315" s="9">
-        <v>172515</v>
+        <v>175637</v>
       </c>
       <c r="D315" s="9">
-        <v>30309</v>
+        <v>32295</v>
       </c>
       <c r="E315" s="10">
-        <v>8.44</v>
+        <v>8.74</v>
       </c>
       <c r="F315" s="10">
-        <v>12.75</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="316" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B316" s="6">
-        <v>41578</v>
+        <v>41593</v>
       </c>
       <c r="C316" s="7">
-        <v>157449</v>
+        <v>172515</v>
       </c>
       <c r="D316" s="7">
-        <v>33724</v>
+        <v>30309</v>
       </c>
       <c r="E316" s="8">
-        <v>8.63</v>
+        <v>8.44</v>
       </c>
       <c r="F316" s="8">
-        <v>12.39</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="317" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B317" s="6">
-        <v>41562</v>
+        <v>41578</v>
       </c>
       <c r="C317" s="9">
-        <v>136312</v>
+        <v>157449</v>
       </c>
       <c r="D317" s="9">
-        <v>45270</v>
+        <v>33724</v>
       </c>
       <c r="E317" s="10">
-        <v>8.03</v>
+        <v>8.63</v>
       </c>
       <c r="F317" s="10">
-        <v>12.53</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="318" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B318" s="6">
-        <v>41547</v>
+        <v>41562</v>
       </c>
       <c r="C318" s="7">
-        <v>98638</v>
+        <v>136312</v>
       </c>
       <c r="D318" s="7">
-        <v>26778</v>
+        <v>45270</v>
       </c>
       <c r="E318" s="8">
-        <v>9.5</v>
+        <v>8.03</v>
       </c>
       <c r="F318" s="8">
-        <v>13.57</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="319" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B319" s="6">
-        <v>41532</v>
+        <v>41547</v>
       </c>
       <c r="C319" s="9">
-        <v>108187</v>
+        <v>98638</v>
       </c>
       <c r="D319" s="9">
-        <v>17027</v>
+        <v>26778</v>
       </c>
       <c r="E319" s="10">
-        <v>8.17</v>
+        <v>9.5</v>
       </c>
       <c r="F319" s="10">
-        <v>13.8</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="320" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B320" s="6">
-        <v>41517</v>
+        <v>41532</v>
       </c>
       <c r="C320" s="7">
-        <v>118290</v>
+        <v>108187</v>
       </c>
       <c r="D320" s="7">
-        <v>9760</v>
+        <v>17027</v>
       </c>
       <c r="E320" s="8">
-        <v>9.5</v>
+        <v>8.17</v>
       </c>
       <c r="F320" s="8">
-        <v>14.31</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B321" s="6">
-        <v>41501</v>
+        <v>41517</v>
       </c>
       <c r="C321" s="9">
-        <v>136340</v>
+        <v>118290</v>
       </c>
       <c r="D321" s="9">
-        <v>8390</v>
+        <v>9760</v>
       </c>
       <c r="E321" s="10">
-        <v>7.82</v>
+        <v>9.5</v>
       </c>
       <c r="F321" s="10">
-        <v>12.84</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B322" s="6">
-        <v>41486</v>
+        <v>41501</v>
       </c>
       <c r="C322" s="7">
-        <v>149581</v>
+        <v>136340</v>
       </c>
       <c r="D322" s="7">
-        <v>6600</v>
+        <v>8390</v>
       </c>
       <c r="E322" s="8">
-        <v>7.43</v>
+        <v>7.82</v>
       </c>
       <c r="F322" s="8">
-        <v>12.36</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B323" s="6">
-        <v>41470</v>
+        <v>41486</v>
       </c>
       <c r="C323" s="9">
-        <v>169426</v>
+        <v>149581</v>
       </c>
       <c r="D323" s="9">
-        <v>42812</v>
+        <v>6600</v>
       </c>
       <c r="E323" s="10">
-        <v>7.36</v>
+        <v>7.43</v>
       </c>
       <c r="F323" s="10">
-        <v>12.62</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B324" s="6">
-        <v>41455</v>
+        <v>41470</v>
       </c>
       <c r="C324" s="7">
-        <v>135588</v>
+        <v>169426</v>
       </c>
       <c r="D324" s="7">
-        <v>26364</v>
+        <v>42812</v>
       </c>
       <c r="E324" s="8">
-        <v>7.58</v>
+        <v>7.36</v>
       </c>
       <c r="F324" s="8">
-        <v>12.71</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B325" s="6">
-        <v>41440</v>
+        <v>41455</v>
       </c>
       <c r="C325" s="9">
-        <v>170246</v>
+        <v>135588</v>
       </c>
       <c r="D325" s="9">
-        <v>40806</v>
+        <v>26364</v>
       </c>
       <c r="E325" s="10">
-        <v>7.57</v>
+        <v>7.58</v>
       </c>
       <c r="F325" s="10">
-        <v>12.79</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B326" s="6">
-        <v>41425</v>
+        <v>41440</v>
       </c>
       <c r="C326" s="7">
-        <v>173248</v>
+        <v>170246</v>
       </c>
       <c r="D326" s="7">
-        <v>27475</v>
+        <v>40806</v>
       </c>
       <c r="E326" s="8">
-        <v>7.7</v>
+        <v>7.57</v>
       </c>
       <c r="F326" s="8">
-        <v>13.3</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="327" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B327" s="6">
-        <v>41409</v>
+        <v>41425</v>
       </c>
       <c r="C327" s="9">
-        <v>175575</v>
+        <v>173248</v>
       </c>
       <c r="D327" s="9">
-        <v>29479</v>
+        <v>27475</v>
       </c>
       <c r="E327" s="10">
         <v>7.7</v>
       </c>
       <c r="F327" s="10">
-        <v>12.77</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="328" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B328" s="6">
-        <v>41394</v>
+        <v>41409</v>
       </c>
       <c r="C328" s="7">
-        <v>157491</v>
+        <v>175575</v>
       </c>
       <c r="D328" s="7">
-        <v>27717</v>
+        <v>29479</v>
       </c>
       <c r="E328" s="8">
-        <v>7.85</v>
+        <v>7.7</v>
       </c>
       <c r="F328" s="8">
-        <v>13.3</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B329" s="6">
-        <v>41379</v>
+        <v>41394</v>
       </c>
       <c r="C329" s="9">
-        <v>150355</v>
+        <v>157491</v>
       </c>
       <c r="D329" s="9">
-        <v>50980</v>
+        <v>27717</v>
       </c>
       <c r="E329" s="10">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="F329" s="10">
-        <v>13.25</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="330" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B330" s="6">
-        <v>41364</v>
+        <v>41379</v>
       </c>
       <c r="C330" s="7">
-        <v>109255</v>
+        <v>150355</v>
       </c>
       <c r="D330" s="7">
-        <v>19273</v>
+        <v>50980</v>
       </c>
       <c r="E330" s="8">
-        <v>8.05</v>
+        <v>7.8</v>
       </c>
       <c r="F330" s="8">
-        <v>13.42</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="331" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B331" s="6">
-        <v>41348</v>
+        <v>41364</v>
       </c>
       <c r="C331" s="9">
-        <v>181072</v>
+        <v>109255</v>
       </c>
       <c r="D331" s="9">
-        <v>30874</v>
+        <v>19273</v>
       </c>
       <c r="E331" s="10">
-        <v>7.9</v>
+        <v>8.05</v>
       </c>
       <c r="F331" s="10">
-        <v>13.61</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B332" s="6">
-        <v>41333</v>
+        <v>41348</v>
       </c>
       <c r="C332" s="7">
-        <v>192340</v>
+        <v>181072</v>
       </c>
       <c r="D332" s="7">
-        <v>26305</v>
+        <v>30874</v>
       </c>
       <c r="E332" s="8">
-        <v>8.02</v>
+        <v>7.9</v>
       </c>
       <c r="F332" s="8">
-        <v>13.96</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B333" s="6">
-        <v>41320</v>
+        <v>41333</v>
       </c>
       <c r="C333" s="9">
-        <v>209558</v>
+        <v>192340</v>
       </c>
       <c r="D333" s="9">
-        <v>43003</v>
+        <v>26305</v>
       </c>
       <c r="E333" s="10">
-        <v>7.88</v>
+        <v>8.02</v>
       </c>
       <c r="F333" s="10">
-        <v>14.96</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="334" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B334" s="6">
-        <v>41305</v>
+        <v>41320</v>
       </c>
       <c r="C334" s="7">
-        <v>199841.55</v>
+        <v>209558</v>
       </c>
       <c r="D334" s="7">
-        <v>27556.5</v>
+        <v>43003</v>
       </c>
       <c r="E334" s="8">
-        <v>7.97</v>
+        <v>7.88</v>
       </c>
       <c r="F334" s="8">
-        <v>13.37</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="335" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B335" s="6">
-        <v>41289</v>
+        <v>41305</v>
       </c>
       <c r="C335" s="9">
-        <v>211750</v>
+        <v>199841.55</v>
       </c>
       <c r="D335" s="9">
-        <v>47228</v>
+        <v>27556.5</v>
       </c>
       <c r="E335" s="10">
-        <v>8.05</v>
+        <v>7.97</v>
       </c>
       <c r="F335" s="10">
-        <v>13.45</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B336" s="6">
-        <v>41274</v>
+        <v>41289</v>
       </c>
       <c r="C336" s="7">
-        <v>181766</v>
+        <v>211750</v>
       </c>
       <c r="D336" s="7">
-        <v>27893</v>
+        <v>47228</v>
       </c>
       <c r="E336" s="8">
-        <v>8.36</v>
+        <v>8.05</v>
       </c>
       <c r="F336" s="8">
-        <v>14.6</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="337" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B337" s="6">
-        <v>41258</v>
+        <v>41274</v>
       </c>
       <c r="C337" s="9">
-        <v>215239</v>
+        <v>181766</v>
       </c>
       <c r="D337" s="9">
-        <v>54826</v>
+        <v>27893</v>
       </c>
       <c r="E337" s="10">
-        <v>8.05</v>
+        <v>8.36</v>
       </c>
       <c r="F337" s="10">
-        <v>14.46</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="338" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B338" s="6">
-        <v>41243</v>
+        <v>41258</v>
       </c>
       <c r="C338" s="7">
-        <v>199433</v>
+        <v>215239</v>
       </c>
       <c r="D338" s="7">
-        <v>42364</v>
+        <v>54826</v>
       </c>
       <c r="E338" s="8">
-        <v>7.92</v>
+        <v>8.05</v>
       </c>
       <c r="F338" s="8">
-        <v>14</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B339" s="6">
-        <v>41228</v>
+        <v>41243</v>
       </c>
       <c r="C339" s="9">
-        <v>204009.1</v>
+        <v>199433</v>
       </c>
       <c r="D339" s="9">
-        <v>26849.5</v>
+        <v>42364</v>
       </c>
       <c r="E339" s="10">
-        <v>7.64</v>
+        <v>7.92</v>
       </c>
       <c r="F339" s="10">
-        <v>12.67</v>
+        <v>14</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B340" s="6">
-        <v>41213</v>
+        <v>41228</v>
       </c>
       <c r="C340" s="7">
-        <v>194106</v>
+        <v>204009.1</v>
       </c>
       <c r="D340" s="7">
-        <v>24424</v>
+        <v>26849.5</v>
       </c>
       <c r="E340" s="8">
-        <v>8.05</v>
+        <v>7.64</v>
       </c>
       <c r="F340" s="8">
-        <v>12.59</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B341" s="6">
-        <v>41197</v>
+        <v>41213</v>
       </c>
       <c r="C341" s="9">
-        <v>196129.2</v>
+        <v>194106</v>
       </c>
       <c r="D341" s="9">
-        <v>33991</v>
+        <v>24424</v>
       </c>
       <c r="E341" s="10">
-        <v>7.99</v>
+        <v>8.05</v>
       </c>
       <c r="F341" s="10">
-        <v>14.47</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="342" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B342" s="6">
-        <v>41182</v>
+        <v>41197</v>
       </c>
       <c r="C342" s="7">
-        <v>170577.65</v>
+        <v>196129.2</v>
       </c>
       <c r="D342" s="7">
-        <v>27920.5</v>
+        <v>33991</v>
       </c>
       <c r="E342" s="8">
-        <v>8.33</v>
+        <v>7.99</v>
       </c>
       <c r="F342" s="8">
-        <v>14.5</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B343" s="6">
-        <v>41167</v>
+        <v>41182</v>
       </c>
       <c r="C343" s="9">
-        <v>194793.15</v>
+        <v>170577.65</v>
       </c>
       <c r="D343" s="9">
-        <v>41460</v>
+        <v>27920.5</v>
       </c>
       <c r="E343" s="10">
-        <v>7.37</v>
+        <v>8.33</v>
       </c>
       <c r="F343" s="10">
         <v>14.5</v>
@@ -6041,135 +6041,135 @@
     </row>
     <row r="344" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B344" s="6">
-        <v>41152</v>
+        <v>41167</v>
       </c>
       <c r="C344" s="7">
-        <v>187890</v>
+        <v>194793.15</v>
       </c>
       <c r="D344" s="7">
-        <v>30770</v>
+        <v>41460</v>
       </c>
       <c r="E344" s="8">
-        <v>8.21</v>
+        <v>7.37</v>
       </c>
       <c r="F344" s="8">
-        <v>13.96</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B345" s="6">
-        <v>41136</v>
+        <v>41152</v>
       </c>
       <c r="C345" s="9">
-        <v>183021.7</v>
+        <v>187890</v>
       </c>
       <c r="D345" s="9">
-        <v>24976.05</v>
+        <v>30770</v>
       </c>
       <c r="E345" s="10">
-        <v>8.35</v>
+        <v>8.21</v>
       </c>
       <c r="F345" s="10">
-        <v>14.23</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="346" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B346" s="6">
-        <v>41121</v>
+        <v>41136</v>
       </c>
       <c r="C346" s="7">
-        <v>173225</v>
+        <v>183021.7</v>
       </c>
       <c r="D346" s="7">
-        <v>29003</v>
+        <v>24976.05</v>
       </c>
       <c r="E346" s="8">
-        <v>7.43</v>
+        <v>8.35</v>
       </c>
       <c r="F346" s="8">
-        <v>14.5</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="347" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B347" s="6">
-        <v>41105</v>
+        <v>41121</v>
       </c>
       <c r="C347" s="9">
-        <v>164728</v>
+        <v>173225</v>
       </c>
       <c r="D347" s="9">
-        <v>43941</v>
+        <v>29003</v>
       </c>
       <c r="E347" s="10">
-        <v>8.43</v>
+        <v>7.43</v>
       </c>
       <c r="F347" s="10">
-        <v>14.38</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="348" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B348" s="6">
-        <v>41090</v>
+        <v>41105</v>
       </c>
       <c r="C348" s="7">
-        <v>125811</v>
+        <v>164728</v>
       </c>
       <c r="D348" s="7">
-        <v>27600</v>
+        <v>43941</v>
       </c>
       <c r="E348" s="8">
-        <v>8.24</v>
+        <v>8.43</v>
       </c>
       <c r="F348" s="8">
-        <v>15.25</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="349" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B349" s="6">
-        <v>41075</v>
+        <v>41090</v>
       </c>
       <c r="C349" s="9">
-        <v>163481</v>
+        <v>125811</v>
       </c>
       <c r="D349" s="9">
-        <v>32887</v>
+        <v>27600</v>
       </c>
       <c r="E349" s="10">
-        <v>8.85</v>
+        <v>8.24</v>
       </c>
       <c r="F349" s="10">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="350" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B350" s="6">
-        <v>41060</v>
+        <v>41075</v>
       </c>
       <c r="C350" s="7">
-        <v>149801</v>
+        <v>163481</v>
       </c>
       <c r="D350" s="7">
-        <v>21489</v>
+        <v>32887</v>
       </c>
       <c r="E350" s="8">
-        <v>7.9</v>
+        <v>8.85</v>
       </c>
       <c r="F350" s="8">
-        <v>15</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B351" s="6">
-        <v>41044</v>
+        <v>41060</v>
       </c>
       <c r="C351" s="9">
-        <v>144345</v>
+        <v>149801</v>
       </c>
       <c r="D351" s="9">
-        <v>21844</v>
+        <v>21489</v>
       </c>
       <c r="E351" s="10">
-        <v>8.68</v>
+        <v>7.9</v>
       </c>
       <c r="F351" s="10">
         <v>15</v>
@@ -6177,186 +6177,186 @@
     </row>
     <row r="352" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B352" s="6">
-        <v>41029</v>
+        <v>41044</v>
       </c>
       <c r="C352" s="7">
-        <v>131003</v>
+        <v>144345</v>
       </c>
       <c r="D352" s="7">
-        <v>35328</v>
+        <v>21844</v>
       </c>
       <c r="E352" s="8">
-        <v>8.02</v>
+        <v>8.68</v>
       </c>
       <c r="F352" s="8">
-        <v>14.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="353" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B353" s="6">
-        <v>41014</v>
+        <v>41029</v>
       </c>
       <c r="C353" s="9">
-        <v>110350</v>
+        <v>131003</v>
       </c>
       <c r="D353" s="9">
-        <v>23547</v>
+        <v>35328</v>
       </c>
       <c r="E353" s="10">
-        <v>8.51</v>
+        <v>8.02</v>
       </c>
       <c r="F353" s="10">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="354" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B354" s="6">
-        <v>40999</v>
+        <v>41014</v>
       </c>
       <c r="C354" s="7">
-        <v>91188</v>
+        <v>110350</v>
       </c>
       <c r="D354" s="7">
-        <v>17630</v>
+        <v>23547</v>
       </c>
       <c r="E354" s="8">
-        <v>9.75</v>
+        <v>8.51</v>
       </c>
       <c r="F354" s="8">
-        <v>15.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="355" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B355" s="6">
-        <v>40983</v>
+        <v>40999</v>
       </c>
       <c r="C355" s="9">
-        <v>133527</v>
+        <v>91188</v>
       </c>
       <c r="D355" s="9">
-        <v>21110</v>
+        <v>17630</v>
       </c>
       <c r="E355" s="10">
-        <v>9.63</v>
+        <v>9.75</v>
       </c>
       <c r="F355" s="10">
-        <v>14.9</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="356" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B356" s="6">
-        <v>40968</v>
+        <v>40983</v>
       </c>
       <c r="C356" s="7">
-        <v>161759</v>
+        <v>133527</v>
       </c>
       <c r="D356" s="7">
-        <v>25494</v>
+        <v>21110</v>
       </c>
       <c r="E356" s="8">
-        <v>8.47</v>
+        <v>9.63</v>
       </c>
       <c r="F356" s="8">
-        <v>14.75</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="357" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B357" s="6">
-        <v>40954</v>
+        <v>40968</v>
       </c>
       <c r="C357" s="9">
-        <v>161394</v>
+        <v>161759</v>
       </c>
       <c r="D357" s="9">
-        <v>31420</v>
+        <v>25494</v>
       </c>
       <c r="E357" s="10">
-        <v>7.75</v>
+        <v>8.47</v>
       </c>
       <c r="F357" s="10">
-        <v>14.65</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="358" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B358" s="6">
-        <v>40939</v>
+        <v>40954</v>
       </c>
       <c r="C358" s="7">
-        <v>149883</v>
+        <v>161394</v>
       </c>
       <c r="D358" s="7">
-        <v>15968</v>
+        <v>31420</v>
       </c>
       <c r="E358" s="8">
-        <v>8.66</v>
+        <v>7.75</v>
       </c>
       <c r="F358" s="8">
-        <v>13.25</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="359" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B359" s="6">
-        <v>40923</v>
+        <v>40939</v>
       </c>
       <c r="C359" s="9">
-        <v>152829</v>
+        <v>149883</v>
       </c>
       <c r="D359" s="9">
-        <v>27467</v>
+        <v>15968</v>
       </c>
       <c r="E359" s="10">
-        <v>9</v>
+        <v>8.66</v>
       </c>
       <c r="F359" s="10">
-        <v>14.5</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="360" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B360" s="6">
-        <v>40908</v>
+        <v>40923</v>
       </c>
       <c r="C360" s="7">
-        <v>134148.5</v>
+        <v>152829</v>
       </c>
       <c r="D360" s="7">
-        <v>22437</v>
+        <v>27467</v>
       </c>
       <c r="E360" s="8">
-        <v>8.38</v>
+        <v>9</v>
       </c>
       <c r="F360" s="8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="361" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B361" s="6">
-        <v>40892</v>
+        <v>40908</v>
       </c>
       <c r="C361" s="9">
-        <v>177521</v>
+        <v>134148.5</v>
       </c>
       <c r="D361" s="9">
-        <v>34006</v>
+        <v>22437</v>
       </c>
       <c r="E361" s="10">
-        <v>9.1</v>
+        <v>8.38</v>
       </c>
       <c r="F361" s="10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="362" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B362" s="6">
-        <v>40877</v>
+        <v>40892</v>
       </c>
       <c r="C362" s="7">
-        <v>173476</v>
+        <v>177521</v>
       </c>
       <c r="D362" s="7">
-        <v>18811</v>
+        <v>34006</v>
       </c>
       <c r="E362" s="8">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="F362" s="8">
         <v>14.5</v>
@@ -6364,219 +6364,236 @@
     </row>
     <row r="363" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B363" s="6">
-        <v>40862</v>
+        <v>40877</v>
       </c>
       <c r="C363" s="9">
-        <v>176069</v>
+        <v>173476</v>
       </c>
       <c r="D363" s="9">
-        <v>24944</v>
+        <v>18811</v>
       </c>
       <c r="E363" s="10">
-        <v>8.78</v>
+        <v>8</v>
       </c>
       <c r="F363" s="10">
-        <v>13.55</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="364" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B364" s="6">
-        <v>40847</v>
+        <v>40862</v>
       </c>
       <c r="C364" s="7">
-        <v>168769</v>
+        <v>176069</v>
       </c>
       <c r="D364" s="7">
-        <v>16179</v>
+        <v>24944</v>
       </c>
       <c r="E364" s="8">
-        <v>7.75</v>
+        <v>8.78</v>
       </c>
       <c r="F364" s="8">
-        <v>14.5</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="365" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B365" s="6">
-        <v>40831</v>
+        <v>40847</v>
       </c>
       <c r="C365" s="9">
-        <v>166462</v>
+        <v>168769</v>
       </c>
       <c r="D365" s="9">
-        <v>29243</v>
+        <v>16179</v>
       </c>
       <c r="E365" s="10">
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
       <c r="F365" s="10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="366" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B366" s="6">
-        <v>40816</v>
+        <v>40831</v>
       </c>
       <c r="C366" s="7">
-        <v>144621</v>
+        <v>166462</v>
       </c>
       <c r="D366" s="7">
-        <v>37926</v>
+        <v>29243</v>
       </c>
       <c r="E366" s="8">
-        <v>7.83</v>
+        <v>8.75</v>
       </c>
       <c r="F366" s="8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="367" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B367" s="6">
-        <v>40801</v>
+        <v>40816</v>
       </c>
       <c r="C367" s="9">
-        <v>159701</v>
+        <v>144621</v>
       </c>
       <c r="D367" s="9">
-        <v>31045</v>
+        <v>37926</v>
       </c>
       <c r="E367" s="10">
-        <v>8.47</v>
+        <v>7.83</v>
       </c>
       <c r="F367" s="10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="368" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B368" s="6">
-        <v>40786</v>
+        <v>40801</v>
       </c>
       <c r="C368" s="7">
-        <v>148812</v>
+        <v>159701</v>
       </c>
       <c r="D368" s="7">
-        <v>21797</v>
+        <v>31045</v>
       </c>
       <c r="E368" s="8">
-        <v>7.67</v>
+        <v>8.47</v>
       </c>
       <c r="F368" s="8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="369" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B369" s="6">
-        <v>40770</v>
+        <v>40786</v>
       </c>
       <c r="C369" s="9">
-        <v>142452</v>
+        <v>148812</v>
       </c>
       <c r="D369" s="9">
-        <v>19445</v>
+        <v>21797</v>
       </c>
       <c r="E369" s="10">
-        <v>8.5</v>
+        <v>7.67</v>
       </c>
       <c r="F369" s="10">
-        <v>13.85</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="370" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B370" s="6">
-        <v>40755</v>
+        <v>40770</v>
       </c>
       <c r="C370" s="7">
-        <v>133691</v>
+        <v>142452</v>
       </c>
       <c r="D370" s="7">
-        <v>16868</v>
+        <v>19445</v>
       </c>
       <c r="E370" s="8">
-        <v>7.06</v>
+        <v>8.5</v>
       </c>
       <c r="F370" s="8">
-        <v>14.5</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="371" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B371" s="6">
-        <v>40739</v>
+        <v>40755</v>
       </c>
       <c r="C371" s="9">
-        <v>128347</v>
+        <v>133691</v>
       </c>
       <c r="D371" s="9">
-        <v>29818</v>
+        <v>16868</v>
       </c>
       <c r="E371" s="10">
-        <v>8.1</v>
+        <v>7.06</v>
       </c>
       <c r="F371" s="10">
-        <v>13.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="372" s="1" customFormat="1" ht="19.1988" customHeight="1">
       <c r="B372" s="6">
+        <v>40739</v>
+      </c>
+      <c r="C372" s="7">
+        <v>128347</v>
+      </c>
+      <c r="D372" s="7">
+        <v>29818</v>
+      </c>
+      <c r="E372" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="F372" s="8">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="373" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B373" s="6">
         <v>40724</v>
       </c>
-      <c r="C372" s="7">
+      <c r="C373" s="9">
         <v>104689</v>
       </c>
-      <c r="D372" s="7">
+      <c r="D373" s="9">
         <v>30290</v>
       </c>
-      <c r="E372" s="8">
+      <c r="E373" s="10">
         <v>8.35</v>
       </c>
-      <c r="F372" s="8">
+      <c r="F373" s="10">
         <v>13.5</v>
       </c>
     </row>
-    <row r="373" s="1" customFormat="1" ht="19.1988" customHeight="1">
-      <c r="B373" s="11">
+    <row r="374" s="1" customFormat="1" ht="19.1988" customHeight="1">
+      <c r="B374" s="11">
         <v>40709</v>
       </c>
-      <c r="C373" s="12">
+      <c r="C374" s="12">
         <v>123400</v>
       </c>
-      <c r="D373" s="12">
+      <c r="D374" s="12">
         <v>20522</v>
       </c>
-      <c r="E373" s="13">
+      <c r="E374" s="13">
         <v>8.25</v>
       </c>
-      <c r="F373" s="13">
+      <c r="F374" s="13">
         <v>13</v>
       </c>
     </row>
-    <row r="374" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
-    <row r="375" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="B375" s="14" t="s">
+    <row r="375" s="1" customFormat="1" ht="1.0666" customHeight="1"/>
+    <row r="376" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B376" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C375" s="15" t="s">
+      <c r="C376" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D375" s="15"/>
-      <c r="E375" s="15"/>
-      <c r="F375" s="15"/>
-    </row>
-    <row r="376" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="B376" s="18" t="s">
+      <c r="D376" s="15"/>
+      <c r="E376" s="15"/>
+      <c r="F376" s="15"/>
+    </row>
+    <row r="377" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B377" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C376" s="18"/>
-      <c r="D376" s="18"/>
-      <c r="E376" s="18"/>
-      <c r="F376" s="18"/>
-    </row>
-    <row r="377" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
+      <c r="C377" s="18"/>
+      <c r="D377" s="18"/>
+      <c r="E377" s="18"/>
+      <c r="F377" s="18"/>
+    </row>
+    <row r="378" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="B377:F377"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C375:F375"/>
+    <mergeCell ref="C376:F376"/>
   </mergeCells>
   <pageSetup paperSize="120" scale="100" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
